--- a/docs/content-input/RITA-website-content-to-fill.xlsx
+++ b/docs/content-input/RITA-website-content-to-fill.xlsx
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Resources Policy 116</t>
+          <t>Resources Policy 116, 105900</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>Nwaila, Avenyo, et al.</t>
+          <t>Nwaila, et al.</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0301420726000723</t>
+          <t>https://doi.org/10.1016/j.resourpol.2026.105900</t>
         </is>
       </c>
       <c r="J4" s="17" t="inlineStr">
@@ -3728,9 +3728,17 @@
         </is>
       </c>
       <c r="K4" s="16" t="inlineStr"/>
-      <c r="L4" s="16" t="inlineStr"/>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M4" s="16" t="inlineStr"/>
-      <c r="N4" s="16" t="inlineStr"/>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>The paper proposes an Adaptive Royalty Architecture for critical minerals: a statutory ad valorem floor, a margin- or price-linked escalator, a downside price-variance buffer and a rules-based community dividend. It stress-tests the design on lithium, nickel and rare earth cases.</t>
+        </is>
+      </c>
       <c r="O4" s="16" t="inlineStr"/>
       <c r="P4" s="16" t="inlineStr"/>
       <c r="Q4" s="16" t="inlineStr"/>
@@ -3739,7 +3747,7 @@
       <c r="T4" s="16" t="inlineStr"/>
       <c r="U4" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V4" s="16" t="inlineStr"/>
@@ -3763,7 +3771,7 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Ndubuisi</t>
+          <t>Ndubuisi, Avenyo</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -3779,7 +3787,7 @@
       <c r="H5" s="15" t="inlineStr"/>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>https://unu-merit.nl/publications/abstract.php?id=10442</t>
+          <t>https://cris.maastrichtuniversity.nl/en/publications/gendering-green-transition-in-africa-implications-of-transformati/</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
@@ -3788,7 +3796,11 @@
         </is>
       </c>
       <c r="K5" s="16" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M5" s="16" t="inlineStr"/>
       <c r="N5" s="16" t="inlineStr"/>
       <c r="O5" s="16" t="inlineStr"/>
@@ -3810,12 +3822,12 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Jobs, investments and exporting: the real effects of electricity crises in South Africa</t>
+          <t>Jobs, investments, and exporting: the real effects of electricity crisis in South Africa</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Energy Economics 157</t>
+          <t>Energy Economics 157, 109234</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
@@ -3852,7 +3864,11 @@
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr"/>
-      <c r="L6" s="16" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M6" s="16" t="inlineStr"/>
       <c r="N6" s="16" t="inlineStr">
         <is>
@@ -3883,7 +3899,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>The World Economy</t>
+          <t>The World Economy 49(3), 539–569</t>
         </is>
       </c>
       <c r="D7" s="15" t="n">
@@ -3907,7 +3923,7 @@
       <c r="H7" s="15" t="inlineStr"/>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/epdf/10.1111/twec.70049</t>
+          <t>https://doi.org/10.1111/twec.70049</t>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr">
@@ -3916,9 +3932,17 @@
         </is>
       </c>
       <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M7" s="16" t="inlineStr"/>
-      <c r="N7" s="16" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines how imported capital and intermediate inputs from the Global North and the Global South affect structural change in African economies, and how domestic absorptive capacity moderates those effects.</t>
+        </is>
+      </c>
       <c r="O7" s="16" t="inlineStr"/>
       <c r="P7" s="16" t="inlineStr"/>
       <c r="Q7" s="16" t="inlineStr"/>
@@ -3938,25 +3962,25 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>African Transformation Report 2025 (contribution)</t>
+          <t>Taking stock of Africa’s economic transformation: rethinking sources of productivity growth</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>ACET</t>
+          <t>The World Bank Research Observer (advance article)</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Gollin, McMillan, Mensah, Ndubuisi, Owusu</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -3967,18 +3991,26 @@
       <c r="H8" s="15" t="inlineStr"/>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>https://acetforafrica.org/atr2025/</t>
+          <t>https://doi.org/10.1093/wbro/lkag001</t>
         </is>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/african-transformation-report-2025-contribution</t>
+          <t>https://rita-woad.vercel.app/research/publications/taking-stock-of-africas-economic-transformation-rethinking-sources-of</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M8" s="16" t="inlineStr"/>
-      <c r="N8" s="16" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>Recent structural change in Africa has boosted growth, but overall labour productivity growth remains modest. Manufacturing has played a limited role since the 1990s, while services, especially wholesale and retail trade, have driven the gains.</t>
+        </is>
+      </c>
       <c r="O8" s="16" t="inlineStr"/>
       <c r="P8" s="16" t="inlineStr"/>
       <c r="Q8" s="16" t="inlineStr"/>
@@ -3998,12 +4030,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Chinese economic ties and low-carbon industrialization in Africa</t>
+          <t>African Transformation Report 2025 (contribution)</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Energy Economics 144</t>
+          <t>ACET</t>
         </is>
       </c>
       <c r="D9" s="15" t="n">
@@ -4011,12 +4043,12 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu, Tang</t>
+          <t>Ndubuisi</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -4024,25 +4056,25 @@
           <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+      <c r="H9" s="15" t="inlineStr"/>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0140988325001768</t>
+          <t>https://acetforafrica.org/atr2025/</t>
         </is>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/chinese-economic-ties-and-low-carbon-industrialization-in-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/african-transformation-report-2025-contribution</t>
         </is>
       </c>
       <c r="K9" s="16" t="inlineStr"/>
       <c r="L9" s="16" t="inlineStr"/>
       <c r="M9" s="16" t="inlineStr"/>
-      <c r="N9" s="16" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>ACET's 2025 African Transformation Report explores how closing gender gaps fuels Africa's economic transformation, using the African Transformation Index and the Gender Inequality Index to highlight persistent barriers and the policies that work.</t>
+        </is>
+      </c>
       <c r="O9" s="16" t="inlineStr"/>
       <c r="P9" s="16" t="inlineStr"/>
       <c r="Q9" s="16" t="inlineStr"/>
@@ -4062,12 +4094,12 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Dancing on the grid: electricity crises, manufacturing energy vulnerability and jobs in South Africa</t>
+          <t>Chinese ties and low-carbon industrialization in Africa</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Energy Policy 202</t>
+          <t>Energy Economics 144, 108352</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
@@ -4075,7 +4107,7 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Asiama, Avenyo</t>
+          <t>Owusu, Tang, Ndubuisi</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -4085,7 +4117,7 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>03 Energy &amp; industry</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
@@ -4095,18 +4127,26 @@
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.enpol.2025.114534</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0140988325001768</t>
         </is>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/dancing-on-the-grid-electricity-crises-manufacturing-energy</t>
+          <t>https://rita-woad.vercel.app/research/publications/chinese-economic-ties-and-low-carbon-industrialization-in-africa</t>
         </is>
       </c>
       <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M10" s="16" t="inlineStr"/>
-      <c r="N10" s="16" t="inlineStr"/>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines how Chinese greenfield investment in African manufacturing affects industrial carbon emissions. It finds that Chinese FDI inflows increased industrial emissions, especially when they targeted labour- and resource-intensive sectors.</t>
+        </is>
+      </c>
       <c r="O10" s="16" t="inlineStr"/>
       <c r="P10" s="16" t="inlineStr"/>
       <c r="Q10" s="16" t="inlineStr"/>
@@ -4115,7 +4155,7 @@
       <c r="T10" s="16" t="inlineStr"/>
       <c r="U10" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V10" s="16" t="inlineStr"/>
@@ -4126,12 +4166,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Dependence of transition minerals on global clean energy and technology stocks</t>
+          <t>Dancing on the grid: Electricity crises, energy vulnerability, and manufacturing jobs in South Africa</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Finance Research Letters 85(A)</t>
+          <t>Energy Policy 202, 114534</t>
         </is>
       </c>
       <c r="D11" s="15" t="n">
@@ -4139,7 +4179,7 @@
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom</t>
+          <t>Ndubuisi, Avenyo, Asiama</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -4149,24 +4189,36 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>02 Transition minerals &amp; value chains</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr"/>
+          <t>03 Energy &amp; industry</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S1544612325010670</t>
+          <t>https://doi.org/10.1016/j.enpol.2025.114534</t>
         </is>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/dependence-of-transition-minerals-on-global-clean-energy-and-technology</t>
+          <t>https://rita-woad.vercel.app/research/publications/dancing-on-the-grid-electricity-crises-manufacturing-energy</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M11" s="16" t="inlineStr"/>
-      <c r="N11" s="16" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>The paper builds an index of manufacturing sub-sector energy vulnerability from South Africa's input–output matrices and uses it to estimate how electricity crises affect manufacturing jobs. Electricity crises are linked to significant job losses, and the damage is greater in more energy-vulnerable sectors.</t>
+        </is>
+      </c>
       <c r="O11" s="16" t="inlineStr"/>
       <c r="P11" s="16" t="inlineStr"/>
       <c r="Q11" s="16" t="inlineStr"/>
@@ -4175,7 +4227,7 @@
       <c r="T11" s="16" t="inlineStr"/>
       <c r="U11" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V11" s="16" t="inlineStr"/>
@@ -4186,12 +4238,12 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Global value chains and the innovativeness of firms in Africa</t>
+          <t>Dependence of transition minerals on global clean energy and technology stocks</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Technovation 146</t>
+          <t>Finance Research Letters 85(A), 107809</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
@@ -4199,7 +4251,7 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Avenyo, Mensah, Sakyi</t>
+          <t>Ndubuisi, Urom</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -4209,28 +4261,32 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+          <t>02 Transition minerals &amp; value chains</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr"/>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0166497225001087</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S1544612325010670</t>
         </is>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/global-value-chains-and-the-innovativeness-of-firms-in-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/dependence-of-transition-minerals-on-global-clean-energy-and-technology</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="16" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M12" s="16" t="inlineStr"/>
-      <c r="N12" s="16" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>The paper investigates the dynamic dependence of transition minerals on global clean energy and technology markets. Minerals respond asymmetrically, and their link to the technology market is stronger and more consistent.</t>
+        </is>
+      </c>
       <c r="O12" s="16" t="inlineStr"/>
       <c r="P12" s="16" t="inlineStr"/>
       <c r="Q12" s="16" t="inlineStr"/>
@@ -4239,7 +4295,7 @@
       <c r="T12" s="16" t="inlineStr"/>
       <c r="U12" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V12" s="16" t="inlineStr"/>
@@ -4250,12 +4306,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Regionalizing green transition minerals for structural transformation in Africa</t>
+          <t>Firm volatility in an era of global value chain: the role of product quality</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>AERC Working Paper GVC-II-007</t>
         </is>
       </c>
       <c r="D13" s="15" t="n">
@@ -4263,32 +4319,28 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Avenyo, Owusu, Kassa</t>
+          <t>Ndubuisi, Owusu</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>02 Transition minerals &amp; value chains</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+          <t>04 Innovation, firms &amp; work</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr"/>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>https://documents.worldbank.org/en/publication/documents-reports/documentdetail/099620011192519026</t>
+          <t>https://publication.aercafricalibrary.org/items/9705d6c4-3a3e-4eb9-b4d7-ed909f8ebd4c</t>
         </is>
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/regionalizing-green-transition-minerals-for-structural-transformation</t>
+          <t>https://rita-woad.vercel.app/research/publications/firm-volatility-in-an-era-of-global-value-chains-the-role-of-product</t>
         </is>
       </c>
       <c r="K13" s="16" t="inlineStr"/>
@@ -4300,7 +4352,7 @@
       <c r="M13" s="16" t="inlineStr"/>
       <c r="N13" s="16" t="inlineStr">
         <is>
-          <t>A World Bank report on how African countries can coordinate across borders to turn transition-mineral deposits into regional value chains, processing and manufacturing.</t>
+          <t>More than half of global trade now runs through global value chains (GVCs), yet the literature on trade and volatility has not considered them. This paper studies how GVC participation affects the volatility of firms' job growth, and whether product quality changes that relationship.</t>
         </is>
       </c>
       <c r="O13" s="16" t="inlineStr"/>
@@ -4311,7 +4363,7 @@
       <c r="T13" s="16" t="inlineStr"/>
       <c r="U13" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V13" s="16" t="inlineStr"/>
@@ -4322,12 +4374,12 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>The future of industrialization in sub-Saharan Africa: bottlenecks and sectoral opportunities</t>
+          <t>Global value chains and the innovativeness of firms in Africa</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>UNIDO, Industrial Development Report 2026 (background report, ch. 5)</t>
+          <t>Technovation 146, 103276</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
@@ -4335,34 +4387,46 @@
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Tregenna, Asiama, Ncube</t>
+          <t>Ndubuisi, Mensah, Avenyo, Sakyi</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Background paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
-        </is>
-      </c>
-      <c r="H14" s="15" t="inlineStr"/>
+          <t>04 Innovation, firms &amp; work</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>https://www.unido.org/idr/idr2026</t>
+          <t>https://doi.org/10.1016/j.technovation.2025.103276</t>
         </is>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/the-future-of-industrialization-in-sub-saharan-africa-bottlenecks-and</t>
+          <t>https://rita-woad.vercel.app/research/publications/global-value-chains-and-the-innovativeness-of-firms-in-africa</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="16" t="inlineStr"/>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M14" s="16" t="inlineStr"/>
-      <c r="N14" s="16" t="inlineStr"/>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>The paper tests whether participation in global value chains is linked to firm innovation in Africa. African GVC firms are highly innovative: they are more likely to introduce new products and processes, to introduce both together, and to introduce radical innovations.</t>
+        </is>
+      </c>
       <c r="O14" s="16" t="inlineStr"/>
       <c r="P14" s="16" t="inlineStr"/>
       <c r="Q14" s="16" t="inlineStr"/>
@@ -4382,12 +4446,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>‘Learning to export’ and ‘learning by exporting’: innovation and exports in African firms</t>
+          <t>Regionalizing green transition minerals for structural transformation in Africa</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>African Development Review 37</t>
+          <t>World Bank Group, Office of the Chief Economist for the Africa Region</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
@@ -4395,34 +4459,46 @@
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Tregenna</t>
+          <t>Ndubuisi, Avenyo, Owusu, Kassa</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="inlineStr"/>
+          <t>02 Transition minerals &amp; value chains</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/1467-8268.70001</t>
+          <t>https://documents.worldbank.org/en/publication/documents-reports/documentdetail/099620011192519026</t>
         </is>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/learning-to-export-and-learning-by-exporting-innovation-and-exports-in</t>
+          <t>https://rita-woad.vercel.app/research/publications/regionalizing-green-transition-minerals-for-structural-transformation</t>
         </is>
       </c>
       <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M15" s="16" t="inlineStr"/>
-      <c r="N15" s="16" t="inlineStr"/>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>Africa is rich in transition minerals but still exports most of them raw, which limits how much value the continent keeps. The report argues that regional cooperation, shared infrastructure and coordinated policy are needed to turn mineral wealth into regional value chains and broad prosperity.</t>
+        </is>
+      </c>
       <c r="O15" s="16" t="inlineStr"/>
       <c r="P15" s="16" t="inlineStr"/>
       <c r="Q15" s="16" t="inlineStr"/>
@@ -4442,25 +4518,25 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>African Economic Outlook 2024 (contribution)</t>
+          <t>The future of industrialization in sub-Saharan Africa: bottlenecks and sectoral opportunities</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>African Development Bank</t>
+          <t>UNIDO, Industrial Development Report 2026 (background report, ch. 5)</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Avenyo, Tregenna, Asiama, Ncube</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Background paper</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -4471,12 +4547,12 @@
       <c r="H16" s="15" t="inlineStr"/>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>https://www.afdb.org/en/documents/african-economic-outlook-2024</t>
+          <t>https://www.unido.org/idr/idr2026</t>
         </is>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/african-economic-outlook-2024-contribution</t>
+          <t>https://rita-woad.vercel.app/research/publications/the-future-of-industrialization-in-sub-saharan-africa-bottlenecks-and</t>
         </is>
       </c>
       <c r="K16" s="16" t="inlineStr"/>
@@ -4502,47 +4578,55 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Chinese manufacturing import penetration and firm performance: Belt and Road countries</t>
+          <t>‘Learning to export’ and ‘learning by exporting’: revisiting the relationship between innovation and exports in African firms</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>SARChI Industrial Development Working Paper 2024-06</t>
+          <t>African Development Review 37(1)</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Spinola, Tregenna</t>
+          <t>Avenyo, Tregenna</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr"/>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>https://www.uj.ac.za/wp-content/uploads/2021/10/wp2024-06-avenyo-spinola-tregenna-chinese-manufacturing-import-penetration.pdf</t>
+          <t>https://doi.org/10.1111/1467-8268.70001</t>
         </is>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/chinese-manufacturing-import-penetration-and-firm-performance-belt-and</t>
+          <t>https://rita-woad.vercel.app/research/publications/learning-to-export-and-learning-by-exporting-innovation-and-exports-in</t>
         </is>
       </c>
       <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr"/>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M17" s="16" t="inlineStr"/>
-      <c r="N17" s="16" t="inlineStr"/>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>The paper revisits the relationship between innovation and exports in African firms and finds a positive link running both ways. Innovation affects both whether a firm exports and how much it exports, and exporting makes innovation more likely.</t>
+        </is>
+      </c>
       <c r="O17" s="16" t="inlineStr"/>
       <c r="P17" s="16" t="inlineStr"/>
       <c r="Q17" s="16" t="inlineStr"/>
@@ -4551,7 +4635,7 @@
       <c r="T17" s="16" t="inlineStr"/>
       <c r="U17" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V17" s="16" t="inlineStr"/>
@@ -4562,12 +4646,12 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Determinants of digital technologies’ adoption in South African manufacturing</t>
+          <t>African Economic Outlook 2024: Driving Africa’s Transformation: The Reform of the Global Financial Architecture</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>South African Journal of Economics</t>
+          <t>African Development Bank</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
@@ -4575,38 +4659,38 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Bell, Nyamwena</t>
+          <t>Ndubuisi</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+          <t>01 Green industrialisation &amp; policy</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr"/>
       <c r="I18" s="17" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1111/saje.12378</t>
+          <t>https://www.afdb.org/en/documents/african-economic-outlook-2024</t>
         </is>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/determinants-of-digital-technologies-adoption-in-south-african</t>
+          <t>https://rita-woad.vercel.app/research/publications/african-economic-outlook-2024-contribution</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr"/>
       <c r="L18" s="16" t="inlineStr"/>
       <c r="M18" s="16" t="inlineStr"/>
-      <c r="N18" s="16" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>The African Development Bank's 2024 flagship report calls for reform of the global financial architecture to drive Africa's structural transformation, including a greater voice for Africa in multilateral development banks and international financial institutions. Gideon Ndubuisi contributed to the report (contributor role not confirmed in sources).</t>
+        </is>
+      </c>
       <c r="O18" s="16" t="inlineStr"/>
       <c r="P18" s="16" t="inlineStr"/>
       <c r="Q18" s="16" t="inlineStr"/>
@@ -4615,7 +4699,7 @@
       <c r="T18" s="16" t="inlineStr"/>
       <c r="U18" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V18" s="16" t="inlineStr"/>
@@ -4626,12 +4710,12 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Escaping corruption in the demand for public services in Africa: the dual nature of civic networks</t>
+          <t>Chinese development finance and labor productivity growth in developing countries</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>World Development 177</t>
+          <t>SSRN Working Paper 4989817</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
@@ -4639,34 +4723,42 @@
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Osei, Konte</t>
+          <t>Konte, Ndubuisi</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H19" s="15" t="inlineStr"/>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=4989817</t>
         </is>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/escaping-corruption-in-the-demand-for-public-services-in-africa-the</t>
+          <t>https://rita-woad.vercel.app/research/publications/chinese-development-finance-and-labour-productivity-growth-in</t>
         </is>
       </c>
       <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M19" s="16" t="inlineStr"/>
-      <c r="N19" s="16" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>Does Chinese development finance raise labour productivity growth in developing countries, and through which channel? Using concessional and commercial Chinese project finance, the paper finds that productivity gains work mainly within sectors rather than through labour moving between sectors.</t>
+        </is>
+      </c>
       <c r="O19" s="16" t="inlineStr"/>
       <c r="P19" s="16" t="inlineStr"/>
       <c r="Q19" s="16" t="inlineStr"/>
@@ -4675,7 +4767,7 @@
       <c r="T19" s="16" t="inlineStr"/>
       <c r="U19" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V19" s="16" t="inlineStr"/>
@@ -4686,12 +4778,12 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>ICTs and employment in Ghana: the role of enterprise formality</t>
+          <t>Chinese manufacturing import penetration and firm performance: evidence from Belt and Road Initiative countries</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Scientific African 26</t>
+          <t>SARChI Industrial Development Working Paper 2024-06</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
@@ -4699,34 +4791,42 @@
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Fu</t>
+          <t>Avenyo, Spinola, Tregenna</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr"/>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S2468227624003363</t>
+          <t>https://ideas.repec.org/p/adz/wpaper/2024-06.html</t>
         </is>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/icts-and-employment-in-ghana-the-role-of-enterprise-formality</t>
+          <t>https://rita-woad.vercel.app/research/publications/chinese-manufacturing-import-penetration-and-firm-performance-belt-and</t>
         </is>
       </c>
       <c r="K20" s="16" t="inlineStr"/>
-      <c r="L20" s="16" t="inlineStr"/>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M20" s="16" t="inlineStr"/>
-      <c r="N20" s="16" t="inlineStr"/>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines how Chinese manufacturing import penetration affects the performance of manufacturing firms in Belt and Road Initiative countries. Chinese imports crowd out firms' productive capacity while acting as a catalyst for their internationalisation.</t>
+        </is>
+      </c>
       <c r="O20" s="16" t="inlineStr"/>
       <c r="P20" s="16" t="inlineStr"/>
       <c r="Q20" s="16" t="inlineStr"/>
@@ -4735,7 +4835,7 @@
       <c r="T20" s="16" t="inlineStr"/>
       <c r="U20" s="16" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V20" s="16" t="inlineStr"/>
@@ -4746,12 +4846,12 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Learning-by-exporting in South Africa: GVC participation and technological capability</t>
+          <t>Determinants of digital technologies’ adoption in South African manufacturing</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>African Journal of Science, Technology, Innovation and Development</t>
+          <t>South African Journal of Economics 92(2), 235–259</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
@@ -4759,7 +4859,7 @@
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Mazzi, Ndubuisi, Avenyo</t>
+          <t>Avenyo, Bell, Nyamwena</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -4772,21 +4872,33 @@
           <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr"/>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>https://www.tandfonline.com/doi/full/10.1080/20421338.2023.2295631</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1111/saje.12378</t>
         </is>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/learning-by-exporting-in-south-africa-gvc-participation-and</t>
+          <t>https://rita-woad.vercel.app/research/publications/determinants-of-digital-technologies-adoption-in-south-african</t>
         </is>
       </c>
       <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr"/>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M21" s="16" t="inlineStr"/>
-      <c r="N21" s="16" t="inlineStr"/>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>Adopting advanced digital technologies can raise firm productivity and competitiveness, but what drives adoption in developing-country manufacturing remains largely anecdotal. Using unique survey data on 516 South African manufacturing firms, the paper finds that innovation, foreign ownership, export exposure and skilled human capital propel adoption, while a lack of capital holds it back.</t>
+        </is>
+      </c>
       <c r="O21" s="16" t="inlineStr"/>
       <c r="P21" s="16" t="inlineStr"/>
       <c r="Q21" s="16" t="inlineStr"/>
@@ -4806,12 +4918,12 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Patent enforcement and the quality upgrading of exported products</t>
+          <t>Escaping corruption in the demand for public services in Africa: the dual nature of civic networks</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Journal of the Knowledge Economy</t>
+          <t>World Development 177, 106541</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
@@ -4819,7 +4931,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Osei, Konte, Avenyo</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
@@ -4833,20 +4945,28 @@
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr"/>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.worlddev.2024.106541</t>
         </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/patent-enforcement-and-the-quality-upgrading-of-exported-products</t>
+          <t>https://rita-woad.vercel.app/research/publications/escaping-corruption-in-the-demand-for-public-services-in-africa-the</t>
         </is>
       </c>
       <c r="K22" s="16" t="inlineStr"/>
-      <c r="L22" s="16" t="inlineStr"/>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M22" s="16" t="inlineStr"/>
-      <c r="N22" s="16" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>Not everyone is a victim of bribery-seeking officials: social networks serve as substitutes for, or exit options out of, corruption. But people facing multiple deprivations cannot use their networks to ease access, while those who already have access use networks to complement corrupt acts and get ahead.</t>
+        </is>
+      </c>
       <c r="O22" s="16" t="inlineStr"/>
       <c r="P22" s="16" t="inlineStr"/>
       <c r="Q22" s="16" t="inlineStr"/>
@@ -4855,7 +4975,7 @@
       <c r="T22" s="16" t="inlineStr"/>
       <c r="U22" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V22" s="16" t="inlineStr"/>
@@ -4866,12 +4986,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Remittance dependence, support for taxation and quality of public services in Africa</t>
+          <t>Gendering structural change and green transition in Africa: implications of transformative policies</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Journal of Institutional Economics</t>
+          <t>ACET background paper, African Transformation Report 4</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
@@ -4879,12 +4999,12 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Konte</t>
+          <t>Ndubuisi, Avenyo, Chisoro</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -4892,21 +5012,29 @@
           <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr"/>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>https://egc.yale.edu/sites/default/files/2024-10/ACET_Gendering_Structural_Change_and_Green_Transition_in_Africa.pdf</t>
         </is>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/remittance-dependence-support-for-taxation-and-quality-of-public</t>
+          <t>https://rita-woad.vercel.app/research/publications/gendering-structural-change-and-green-transition-in-africa-implications</t>
         </is>
       </c>
       <c r="K23" s="16" t="inlineStr"/>
       <c r="L23" s="16" t="inlineStr"/>
       <c r="M23" s="16" t="inlineStr"/>
-      <c r="N23" s="16" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines how structural change and the green transition affect gender employment gaps in Africa. Shifts in sectoral composition have tended to widen gender employment gaps, while green energy systems and transition technologies create chances for more gender-balanced employment.</t>
+        </is>
+      </c>
       <c r="O23" s="16" t="inlineStr"/>
       <c r="P23" s="16" t="inlineStr"/>
       <c r="Q23" s="16" t="inlineStr"/>
@@ -4926,12 +5054,12 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Solar photovoltaic manufacturing in Africa: opportunity or mirage?</t>
+          <t>Learning-by-exporting in South Africa: the influence of global value chain (GVC) participation and technological capability</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>APRI, Green &amp; Transition Minerals Collection</t>
+          <t>African Journal of Science, Technology, Innovation and Development 16(4), 459–476</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
@@ -4939,38 +5067,42 @@
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Avenyo</t>
+          <t>Mazzi, Ndubuisi, Avenyo</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>Policy paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>03 Energy &amp; industry</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+          <t>04 Innovation, firms &amp; work</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr"/>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>https://afripoli.org/solar-photovoltaic-manufacturing-in-africa-opportunity-or-mirage</t>
+          <t>https://doi.org/10.1080/20421338.2023.2295631</t>
         </is>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/solar-photovoltaic-manufacturing-in-africa-opportunity-or-mirage</t>
+          <t>https://rita-woad.vercel.app/research/publications/learning-by-exporting-in-south-africa-gvc-participation-and</t>
         </is>
       </c>
       <c r="K24" s="16" t="inlineStr"/>
-      <c r="L24" s="16" t="inlineStr"/>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M24" s="16" t="inlineStr"/>
-      <c r="N24" s="16" t="inlineStr"/>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines how trade related to global value chains affects the performance of manufacturing firms in South Africa. GVC-related trade carries a higher productivity premium than traditional trade, but only firms that also invest in R&amp;D appear to learn from exporting.</t>
+        </is>
+      </c>
       <c r="O24" s="16" t="inlineStr"/>
       <c r="P24" s="16" t="inlineStr"/>
       <c r="Q24" s="16" t="inlineStr"/>
@@ -4979,7 +5111,7 @@
       <c r="T24" s="16" t="inlineStr"/>
       <c r="U24" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V24" s="16" t="inlineStr"/>
@@ -4990,12 +5122,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Technology capability and industrialization in Africa</t>
+          <t>Patent enforcement and quality upgrading of exported products</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>SARChI Industrial Development Working Paper 03-2024</t>
+          <t>Journal of the Knowledge Economy 15, 13979–14011</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
@@ -5003,12 +5135,12 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Mensah</t>
+          <t>Ndubuisi</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -5019,18 +5151,26 @@
       <c r="H25" s="15" t="inlineStr"/>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>https://aec.afdb.org/en/papers/technological-capability-and-industrialization-africa-711</t>
+          <t>https://ideas.repec.org/a/spr/jknowl/v15y2024i3d10.1007_s13132-023-01660-8.html</t>
         </is>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/technology-capability-and-industrialization-in-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/patent-enforcement-and-the-quality-upgrading-of-exported-products</t>
         </is>
       </c>
       <c r="K25" s="16" t="inlineStr"/>
-      <c r="L25" s="16" t="inlineStr"/>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M25" s="16" t="inlineStr"/>
-      <c r="N25" s="16" t="inlineStr"/>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>The paper evaluates how patent protection affects the quality of exported products across 43 advanced and emerging economies. R&amp;D-intensive industries in countries with stronger patent protection produce and export higher-quality goods at a greater rate than similar industries in weaker-protection countries.</t>
+        </is>
+      </c>
       <c r="O25" s="16" t="inlineStr"/>
       <c r="P25" s="16" t="inlineStr"/>
       <c r="Q25" s="16" t="inlineStr"/>
@@ -5039,7 +5179,7 @@
       <c r="T25" s="16" t="inlineStr"/>
       <c r="U25" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V25" s="16" t="inlineStr"/>
@@ -5050,47 +5190,55 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Critical minerals and routes to diversification in Africa: Batteries, fuel cells and mining equipment: the case of South Africa</t>
+          <t>Remittance dependence, support for taxation and quality of public services in Africa</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>UNCTAD, Economic Development in Africa Report 2023, background paper 3</t>
+          <t>Journal of Institutional Economics 20, e7</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Andreoni, Avenyo</t>
+          <t>Konte, Ndubuisi</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>Background paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>02 Transition minerals &amp; value chains</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H26" s="15" t="inlineStr"/>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>https://unctad.org/system/files/non-official-document/edar2023_BP3_en.pdf</t>
+          <t>https://doi.org/10.1017/S1744137423000322</t>
         </is>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/critical-minerals-and-routes-to-diversification-in-africa-batteries</t>
+          <t>https://rita-woad.vercel.app/research/publications/remittance-dependence-support-for-taxation-and-quality-of-public</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr"/>
-      <c r="L26" s="16" t="inlineStr"/>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M26" s="16" t="inlineStr"/>
-      <c r="N26" s="16" t="inlineStr"/>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>The paper asks whether depending on remittances weakens citizens' support for taxation in Africa. For about two-thirds of citizens there is no significant effect, but for the remaining third remittance dependence significantly reduces support for taxation.</t>
+        </is>
+      </c>
       <c r="O26" s="16" t="inlineStr"/>
       <c r="P26" s="16" t="inlineStr"/>
       <c r="Q26" s="16" t="inlineStr"/>
@@ -5099,7 +5247,7 @@
       <c r="T26" s="16" t="inlineStr"/>
       <c r="U26" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V26" s="16" t="inlineStr"/>
@@ -5110,51 +5258,55 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Critical minerals and routes to diversification in Africa: Linkages, pulling dynamics and medium-high-tech supply chains</t>
+          <t>Revisiting the effect of information and communication technologies on employment growth in Ghana: the role of enterprise formality</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>UNCTAD, Economic Development in Africa Report 2023, background paper 1</t>
+          <t>Scientific African 26, e02394</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Andreoni, Avenyo</t>
+          <t>Fu, Avenyo</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>Background paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>02 Transition minerals &amp; value chains</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+          <t>04 Innovation, firms &amp; work</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr"/>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>https://unctad.org/system/files/non-official-document/edar2023_BP1_en.pdf</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S2468227624003363</t>
         </is>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/critical-minerals-and-routes-to-diversification-in-africa-linkages</t>
+          <t>https://rita-woad.vercel.app/research/publications/icts-and-employment-in-ghana-the-role-of-enterprise-formality</t>
         </is>
       </c>
       <c r="K27" s="16" t="inlineStr"/>
-      <c r="L27" s="16" t="inlineStr"/>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M27" s="16" t="inlineStr"/>
-      <c r="N27" s="16" t="inlineStr"/>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>The paper revisits how ICTs affect employment growth in Ghanaian manufacturing enterprises, across formal and informal firms. Internet access is associated with more jobs, especially in more formal firms, while informal enterprises remain small even when they use the internet.</t>
+        </is>
+      </c>
       <c r="O27" s="16" t="inlineStr"/>
       <c r="P27" s="16" t="inlineStr"/>
       <c r="Q27" s="16" t="inlineStr"/>
@@ -5163,7 +5315,7 @@
       <c r="T27" s="16" t="inlineStr"/>
       <c r="U27" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="V27" s="16" t="inlineStr"/>
@@ -5174,47 +5326,59 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Critical minerals and routes to diversification in Africa: Mobile phone technologies: the case of the DRC</t>
+          <t>Solar photovoltaic manufacturing in Africa: opportunity or mirage?</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>UNCTAD, Economic Development in Africa Report 2023, background paper 4</t>
+          <t>Africa Policy Research Institute (APRI), Green &amp; Transition Minerals Collection</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Andreoni, Avenyo</t>
+          <t>Ndubuisi, Avenyo</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>Background paper</t>
+          <t>Policy paper</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>02 Transition minerals &amp; value chains</t>
-        </is>
-      </c>
-      <c r="H28" s="15" t="inlineStr"/>
+          <t>03 Energy &amp; industry</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>https://unctad.org/system/files/non-official-document/edar2023_BP4_en.pdf</t>
+          <t>https://afripoli.org/solar-photovoltaic-manufacturing-in-africa-opportunity-or-mirage</t>
         </is>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/critical-minerals-and-routes-to-diversification-in-africa-mobile-phone</t>
+          <t>https://rita-woad.vercel.app/research/publications/solar-photovoltaic-manufacturing-in-africa-opportunity-or-mirage</t>
         </is>
       </c>
       <c r="K28" s="16" t="inlineStr"/>
-      <c r="L28" s="16" t="inlineStr"/>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M28" s="16" t="inlineStr"/>
-      <c r="N28" s="16" t="inlineStr"/>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>Africa holds key minerals for solar PV production, such as copper, tin and silicon, but most countries on their own lack the finance, technological capabilities and infrastructure to build a competitive PV manufacturing sector. The paper finds only scattered opportunities for local manufacturing and recommends a regionalised PV strategy to integrate into the global solar value chain.</t>
+        </is>
+      </c>
       <c r="O28" s="16" t="inlineStr"/>
       <c r="P28" s="16" t="inlineStr"/>
       <c r="Q28" s="16" t="inlineStr"/>
@@ -5234,47 +5398,55 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Critical minerals and routes to diversification in Africa: Renewable energy technologies: the case of Morocco</t>
+          <t>Technological capability and industrialization in Africa</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>UNCTAD, Economic Development in Africa Report 2023, background paper 2</t>
+          <t>SARChI Industrial Development Working Paper 2024-03</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Andreoni, Avenyo</t>
+          <t>Mensah, Ndubuisi</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>Background paper</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>02 Transition minerals &amp; value chains</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr"/>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>https://unctad.org/system/files/non-official-document/edar2023_BP2_en.pdf</t>
+          <t>https://aec.afdb.org/en/papers/technological-capability-and-industrialization-africa-711</t>
         </is>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/critical-minerals-and-routes-to-diversification-in-africa-renewable</t>
+          <t>https://rita-woad.vercel.app/research/publications/technology-capability-and-industrialization-in-africa</t>
         </is>
       </c>
       <c r="K29" s="16" t="inlineStr"/>
-      <c r="L29" s="16" t="inlineStr"/>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M29" s="16" t="inlineStr"/>
-      <c r="N29" s="16" t="inlineStr"/>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines the spatial dynamics of technological capability in Africa and its interdependence with industrial development, using a framework that measures capability along four dimensions: technology precondition, technology infrastructure, technology import and technology effort.</t>
+        </is>
+      </c>
       <c r="O29" s="16" t="inlineStr"/>
       <c r="P29" s="16" t="inlineStr"/>
       <c r="Q29" s="16" t="inlineStr"/>
@@ -5283,7 +5455,7 @@
       <c r="T29" s="16" t="inlineStr"/>
       <c r="U29" s="16" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V29" s="16" t="inlineStr"/>
@@ -5294,12 +5466,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Digital capabilities in South African manufacturing firms: what matters?</t>
+          <t>Critical minerals and routes to diversification in Africa: Linkages, pulling dynamics and medium-high-tech supply chains</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>CCRED-IDTT Working Paper 2023/06</t>
+          <t>Background paper commissioned by the UNCTAD secretariat for the Economic Development in Africa Report 2023</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
@@ -5307,32 +5479,40 @@
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Nyamwena</t>
+          <t>Andreoni, Avenyo</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Background paper</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="inlineStr"/>
+          <t>02 Transition minerals &amp; value chains</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>https://www.competition.org.za/s/IDTT-2022-2023-WP6_Digital-Capabilities-in-SA.pdf</t>
+          <t>https://unctad.org/system/files/non-official-document/edar2023_BP1_en.pdf</t>
         </is>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/digital-capabilities-in-south-african-manufacturing-firms-what-matters</t>
+          <t>https://rita-woad.vercel.app/research/publications/critical-minerals-and-routes-to-diversification-in-africa-linkages</t>
         </is>
       </c>
       <c r="K30" s="16" t="inlineStr"/>
-      <c r="L30" s="16" t="inlineStr"/>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M30" s="16" t="inlineStr"/>
       <c r="N30" s="16" t="inlineStr"/>
       <c r="O30" s="16" t="inlineStr"/>
@@ -5343,7 +5523,7 @@
       <c r="T30" s="16" t="inlineStr"/>
       <c r="U30" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V30" s="16" t="inlineStr"/>
@@ -5354,12 +5534,12 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Drivers of services sector growth acceleration in developing countries</t>
+          <t>Critical minerals and routes to diversification in Africa: Opportunities for diversification into mobile phone technologies – the case of Democratic Republic of Congo</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>WIDER Working Paper 2023/87</t>
+          <t>UNCTAD, Economic Development in Africa Report 2023, background paper 4</t>
         </is>
       </c>
       <c r="D31" s="15" t="n">
@@ -5367,34 +5547,42 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu, Asiama, Avenyo</t>
+          <t>Andreoni, Avenyo</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Background paper</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>02 Transition minerals &amp; value chains</t>
         </is>
       </c>
       <c r="H31" s="15" t="inlineStr"/>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>https://www.wider.unu.edu/publication/drivers-services-sector-growth-acceleration-developing-countries</t>
+          <t>https://unctad.org/node/42296</t>
         </is>
       </c>
       <c r="J31" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/drivers-of-services-sector-growth-acceleration-in-developing-countries</t>
+          <t>https://rita-woad.vercel.app/research/publications/critical-minerals-and-routes-to-diversification-in-africa-mobile-phone</t>
         </is>
       </c>
       <c r="K31" s="16" t="inlineStr"/>
-      <c r="L31" s="16" t="inlineStr"/>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M31" s="16" t="inlineStr"/>
-      <c r="N31" s="16" t="inlineStr"/>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>This background paper maps the global value chain for mobile phone technologies and examines how the Democratic Republic of Congo could use its mineral resources to localise and capture value in that chain. It also sets out the country's routes to diversification and technological deepening, including opportunities for regional coordination and industrial development.</t>
+        </is>
+      </c>
       <c r="O31" s="16" t="inlineStr"/>
       <c r="P31" s="16" t="inlineStr"/>
       <c r="Q31" s="16" t="inlineStr"/>
@@ -5403,7 +5591,7 @@
       <c r="T31" s="16" t="inlineStr"/>
       <c r="U31" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V31" s="16" t="inlineStr"/>
@@ -5414,12 +5602,12 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Industrial diagnostic study</t>
+          <t>Critical minerals and routes to diversification in Africa: opportunities for diversification into batteries and fuel cells and mining equipment technologies. The case of South Africa</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>UNIDO</t>
+          <t>UNCTAD, Economic Development in Africa Report 2023, background paper</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
@@ -5427,41 +5615,53 @@
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Andreoni, Avenyo</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Background paper</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>02 Transition minerals &amp; value chains</t>
         </is>
       </c>
       <c r="H32" s="15" t="inlineStr"/>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>https://www.unido.org/sites/default/files/unido-publications/2024-02/Industrial%20diagnostic%20study_2023_0.pdf</t>
+          <t>https://unctad.org/node/42295</t>
         </is>
       </c>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/industrial-diagnostic-study</t>
+          <t>https://rita-woad.vercel.app/research/publications/critical-minerals-and-routes-to-diversification-in-africa-batteries</t>
         </is>
       </c>
       <c r="K32" s="16" t="inlineStr"/>
-      <c r="L32" s="16" t="inlineStr"/>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M32" s="16" t="inlineStr"/>
-      <c r="N32" s="16" t="inlineStr"/>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>The paper maps the global battery and fuel cells value chain and analyses how South Africa can leverage its mineral resources to localise and capture value in mining equipment technologies. It draws industrial policy lessons for productive transformation across Africa.</t>
+        </is>
+      </c>
       <c r="O32" s="16" t="inlineStr"/>
       <c r="P32" s="16" t="inlineStr"/>
       <c r="Q32" s="16" t="inlineStr"/>
       <c r="R32" s="16" t="inlineStr"/>
       <c r="S32" s="16" t="inlineStr"/>
       <c r="T32" s="16" t="inlineStr"/>
-      <c r="U32" s="16" t="inlineStr"/>
+      <c r="U32" s="16" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
       <c r="V32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5470,12 +5670,12 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Learning to innovate in urban informal enterprises of Ghana</t>
+          <t>Critical minerals and routes to diversification in Africa: opportunities for diversification into renewable energy technologies – the case of Morocco</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Scientific African 20</t>
+          <t>UNCTAD, background paper for the Economic Development in Africa Report 2023</t>
         </is>
       </c>
       <c r="D33" s="15" t="n">
@@ -5483,34 +5683,42 @@
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Andreoni, Avenyo</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Background paper</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>02 Transition minerals &amp; value chains</t>
         </is>
       </c>
       <c r="H33" s="15" t="inlineStr"/>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S2468227623001965</t>
+          <t>https://unctad.org/system/files/non-official-document/edar2023_BP2_en.pdf</t>
         </is>
       </c>
       <c r="J33" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/learning-to-innovate-in-urban-informal-enterprises-of-ghana</t>
+          <t>https://rita-woad.vercel.app/research/publications/critical-minerals-and-routes-to-diversification-in-africa-renewable</t>
         </is>
       </c>
       <c r="K33" s="16" t="inlineStr"/>
-      <c r="L33" s="16" t="inlineStr"/>
+      <c r="L33" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M33" s="16" t="inlineStr"/>
-      <c r="N33" s="16" t="inlineStr"/>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>The paper maps the opportunities and challenges for Morocco to diversify into renewable energy technology value chains, and sets out a framework for how the country could localise and capture value in those supply networks.</t>
+        </is>
+      </c>
       <c r="O33" s="16" t="inlineStr"/>
       <c r="P33" s="16" t="inlineStr"/>
       <c r="Q33" s="16" t="inlineStr"/>
@@ -5519,7 +5727,7 @@
       <c r="T33" s="16" t="inlineStr"/>
       <c r="U33" s="16" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="V33" s="16" t="inlineStr"/>
@@ -5530,12 +5738,12 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Localisation in South Africa: analysis of key emerging issues</t>
+          <t>Digital capabilities in South African manufacturing firms: what matters?</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>CCRED-IDTT Working Paper 2023/01</t>
+          <t>CCRED-IDTT Working Paper 2023/06</t>
         </is>
       </c>
       <c r="D34" s="15" t="n">
@@ -5543,7 +5751,7 @@
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Bosiu, Nyamwena</t>
+          <t>Avenyo, Nyamwena</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
@@ -5553,22 +5761,26 @@
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H34" s="15" t="inlineStr"/>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>https://www.competition.org.za/s/IDTT-2022-2023-WP6_Digital-Capabilities-in-SA.pdf</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/localisation-in-south-africa-analysis-of-key-emerging-issues</t>
+          <t>https://rita-woad.vercel.app/research/publications/digital-capabilities-in-south-african-manufacturing-firms-what-matters</t>
         </is>
       </c>
       <c r="K34" s="16" t="inlineStr"/>
-      <c r="L34" s="16" t="inlineStr"/>
+      <c r="L34" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M34" s="16" t="inlineStr"/>
       <c r="N34" s="16" t="inlineStr"/>
       <c r="O34" s="16" t="inlineStr"/>
@@ -5590,12 +5802,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Navigating the EU Green Deal in at-risk agro-food sectors in South Africa: citrus and wine</t>
+          <t>Drivers of services sector growth acceleration in developing countries</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>CCRED Working Paper 2023/02</t>
+          <t>WIDER Working Paper 2023/87</t>
         </is>
       </c>
       <c r="D35" s="15" t="n">
@@ -5603,7 +5815,7 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Bell, Goga, Muzyamba, Nyamwena</t>
+          <t>Ndubuisi, Owusu, Asiama, Avenyo</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
@@ -5619,18 +5831,26 @@
       <c r="H35" s="15" t="inlineStr"/>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>https://www.competition.org.za/s/TIPS-EGD-WP-August-2023.pdf</t>
+          <t>https://www.wider.unu.edu/publication/drivers-services-sector-growth-acceleration-developing-countries</t>
         </is>
       </c>
       <c r="J35" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/navigating-the-eu-green-deal-in-at-risk-agro-food-sectors-in-south</t>
+          <t>https://rita-woad.vercel.app/research/publications/drivers-of-services-sector-growth-acceleration-in-developing-countries</t>
         </is>
       </c>
       <c r="K35" s="16" t="inlineStr"/>
-      <c r="L35" s="16" t="inlineStr"/>
+      <c r="L35" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M35" s="16" t="inlineStr"/>
-      <c r="N35" s="16" t="inlineStr"/>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>The services sector is dominant and still growing fast in many developing economies, yet in-depth evidence on what drives services growth accelerations is limited. This paper identifies the underlying factors, separately for market and non-market services.</t>
+        </is>
+      </c>
       <c r="O35" s="16" t="inlineStr"/>
       <c r="P35" s="16" t="inlineStr"/>
       <c r="Q35" s="16" t="inlineStr"/>
@@ -5639,7 +5859,7 @@
       <c r="T35" s="16" t="inlineStr"/>
       <c r="U35" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V35" s="16" t="inlineStr"/>
@@ -5650,12 +5870,12 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Too big to be ignored: how energy poverty undermines productive efficiency</t>
+          <t>Global value chains, job creation and job destruction among firms in South Africa</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Energy Policy 181</t>
+          <t>STEG Working Paper WP073 (CEPR)</t>
         </is>
       </c>
       <c r="D36" s="15" t="n">
@@ -5663,34 +5883,42 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Yuni, Urom, Abid</t>
+          <t>Ndubuisi, Owusu</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>03 Energy &amp; industry</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H36" s="15" t="inlineStr"/>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S030142152300318X</t>
+          <t>https://cepr.org/publications/wp073</t>
         </is>
       </c>
       <c r="J36" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/too-big-to-be-ignored-how-energy-poverty-undermines-productive</t>
+          <t>https://rita-woad.vercel.app/research/publications/global-value-chains-job-creation-and-job-destruction-among-firms-in</t>
         </is>
       </c>
       <c r="K36" s="16" t="inlineStr"/>
-      <c r="L36" s="16" t="inlineStr"/>
+      <c r="L36" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M36" s="16" t="inlineStr"/>
-      <c r="N36" s="16" t="inlineStr"/>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>Using data on all formal firms in South Africa, the paper finds that integration into global value chains is linked to a net gain in jobs at the firm level. The net gain is mostly driven by firms entering GVCs, while continuing GVC firms show an overall net job loss.</t>
+        </is>
+      </c>
       <c r="O36" s="16" t="inlineStr"/>
       <c r="P36" s="16" t="inlineStr"/>
       <c r="Q36" s="16" t="inlineStr"/>
@@ -5699,7 +5927,7 @@
       <c r="T36" s="16" t="inlineStr"/>
       <c r="U36" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V36" s="16" t="inlineStr"/>
@@ -5710,12 +5938,12 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Trade exposure and social cohesion: evidence from Uganda</t>
+          <t>Industrial diagnostic study</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>STEG Working Paper 2023-069</t>
+          <t>UNIDO</t>
         </is>
       </c>
       <c r="D37" s="15" t="n">
@@ -5723,12 +5951,12 @@
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Vrolijk</t>
+          <t>Ndubuisi</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
@@ -5737,14 +5965,14 @@
         </is>
       </c>
       <c r="H37" s="15" t="inlineStr"/>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>https://www.unido.org/sites/default/files/unido-publications/2024-02/Industrial%20diagnostic%20study_2023_0.pdf</t>
         </is>
       </c>
       <c r="J37" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/trade-exposure-and-social-cohesion-evidence-from-uganda</t>
+          <t>https://rita-woad.vercel.app/research/publications/industrial-diagnostic-study</t>
         </is>
       </c>
       <c r="K37" s="16" t="inlineStr"/>
@@ -5757,11 +5985,7 @@
       <c r="R37" s="16" t="inlineStr"/>
       <c r="S37" s="16" t="inlineStr"/>
       <c r="T37" s="16" t="inlineStr"/>
-      <c r="U37" s="16" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
+      <c r="U37" s="16" t="inlineStr"/>
       <c r="V37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
@@ -5770,12 +5994,12 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Trade for catch-up: how GVC participation affects productive efficiency</t>
+          <t>Learning to innovate in urban informal enterprises of Ghana: role of apprenticeship and formal interaction</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Journal of Productivity Analysis 59</t>
+          <t>Scientific African 20, e01740</t>
         </is>
       </c>
       <c r="D38" s="15" t="n">
@@ -5783,7 +6007,7 @@
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu</t>
+          <t>Avenyo</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
@@ -5799,18 +6023,26 @@
       <c r="H38" s="15" t="inlineStr"/>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>https://link.springer.com/article/10.1007/s11123-023-00663-6</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S2468227623001965</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/trade-for-catch-up-how-gvc-participation-affects-productive-efficiency</t>
+          <t>https://rita-woad.vercel.app/research/publications/learning-to-innovate-in-urban-informal-enterprises-of-ghana</t>
         </is>
       </c>
       <c r="K38" s="16" t="inlineStr"/>
-      <c r="L38" s="16" t="inlineStr"/>
+      <c r="L38" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M38" s="16" t="inlineStr"/>
-      <c r="N38" s="16" t="inlineStr"/>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>The study looks at how two learning routes, apprenticeship and formal interactions, affect the product innovativeness of informal firms in Ghana. Apprenticeship builds technological capability that leads to product innovativeness, while competitive formal interactions supply market feedback that improves it.</t>
+        </is>
+      </c>
       <c r="O38" s="16" t="inlineStr"/>
       <c r="P38" s="16" t="inlineStr"/>
       <c r="Q38" s="16" t="inlineStr"/>
@@ -5819,7 +6051,7 @@
       <c r="T38" s="16" t="inlineStr"/>
       <c r="U38" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="V38" s="16" t="inlineStr"/>
@@ -5830,20 +6062,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Disruptive technologies and manufacturing performance in South Africa</t>
+          <t>Localisation in South Africa: analysis of key emerging issues</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>AERC Working Paper 2022/004</t>
+          <t>CCRED Working Paper Series 2023/01</t>
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Bell</t>
+          <t>Avenyo, Bosiu, Nyamwena</t>
         </is>
       </c>
       <c r="F39" s="15" t="inlineStr">
@@ -5853,22 +6085,26 @@
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr"/>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>http://publication.aercafricalibrary.org/handle/123456789/3444</t>
+          <t>https://competition.org.za/working-papers</t>
         </is>
       </c>
       <c r="J39" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/disruptive-technologies-and-manufacturing-performance-in-south-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/localisation-in-south-africa-analysis-of-key-emerging-issues</t>
         </is>
       </c>
       <c r="K39" s="16" t="inlineStr"/>
-      <c r="L39" s="16" t="inlineStr"/>
+      <c r="L39" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M39" s="16" t="inlineStr"/>
       <c r="N39" s="16" t="inlineStr"/>
       <c r="O39" s="16" t="inlineStr"/>
@@ -5890,20 +6126,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Fibre processing &amp; manufacturing SETA and Industry 4.0</t>
+          <t>Navigating the EU Green Deal in at-risk agro-food sectors in South Africa: citrus and wine</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>CCRED-IDTT Working Paper 2022/08</t>
+          <t>CCRED Working Paper 2023/02</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Bell, Goga, Muzyamba, Nyamwena, Avenyo</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -5913,22 +6149,26 @@
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H40" s="15" t="inlineStr"/>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>https://www.competition.org.za/s/TIPS-EGD-WP-August-2023.pdf</t>
         </is>
       </c>
       <c r="J40" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/fibre-processing-and-manufacturing-seta-and-industry-4-0</t>
+          <t>https://rita-woad.vercel.app/research/publications/navigating-the-eu-green-deal-in-at-risk-agro-food-sectors-in-south</t>
         </is>
       </c>
       <c r="K40" s="16" t="inlineStr"/>
-      <c r="L40" s="16" t="inlineStr"/>
+      <c r="L40" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M40" s="16" t="inlineStr"/>
       <c r="N40" s="16" t="inlineStr"/>
       <c r="O40" s="16" t="inlineStr"/>
@@ -5950,47 +6190,55 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>GVC participation and innovation: firm-level evidence from Africa</t>
+          <t>Too big to be ignored: how energy poverty undermines productive efficiency</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>AERC Working Paper 2022/012</t>
+          <t>Energy Policy 181, 113733</t>
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Mensah, Ndubuisi, Sakyi</t>
+          <t>Ndubuisi, Yuni, Urom, Abid</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>03 Energy &amp; industry</t>
         </is>
       </c>
       <c r="H41" s="15" t="inlineStr"/>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.enpol.2023.113733</t>
         </is>
       </c>
       <c r="J41" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/gvc-participation-and-innovation-firm-level-evidence-from-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/too-big-to-be-ignored-how-energy-poverty-undermines-productive</t>
         </is>
       </c>
       <c r="K41" s="16" t="inlineStr"/>
-      <c r="L41" s="16" t="inlineStr"/>
+      <c r="L41" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M41" s="16" t="inlineStr"/>
-      <c r="N41" s="16" t="inlineStr"/>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>The large literature on the drivers of productive efficiency has not considered energy poverty, even though it affects efficiency on several fronts. This paper finds that energy poverty negatively affects productive efficiency.</t>
+        </is>
+      </c>
       <c r="O41" s="16" t="inlineStr"/>
       <c r="P41" s="16" t="inlineStr"/>
       <c r="Q41" s="16" t="inlineStr"/>
@@ -5999,7 +6247,7 @@
       <c r="T41" s="16" t="inlineStr"/>
       <c r="U41" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V41" s="16" t="inlineStr"/>
@@ -6010,25 +6258,25 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Greening manufacturing: technology intensity and CO₂ emissions in developing countries</t>
+          <t>Trade exposure and social cohesion: evidence from Uganda</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Applied Energy 324</t>
+          <t>STEG Working Paper 069</t>
         </is>
       </c>
       <c r="D42" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Tregenna</t>
+          <t>Vrolijk, Ndubuisi</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -6036,25 +6284,29 @@
           <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
-      <c r="H42" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+      <c r="H42" s="15" t="inlineStr"/>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261922010169</t>
+          <t>https://cepr.org/publications/wp069</t>
         </is>
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/greening-manufacturing-technology-intensity-and-co2-emissions-in</t>
+          <t>https://rita-woad.vercel.app/research/publications/trade-exposure-and-social-cohesion-evidence-from-uganda</t>
         </is>
       </c>
       <c r="K42" s="16" t="inlineStr"/>
-      <c r="L42" s="16" t="inlineStr"/>
+      <c r="L42" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M42" s="16" t="inlineStr"/>
-      <c r="N42" s="16" t="inlineStr"/>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>Does trade exposure change social cohesion? Using Uganda's exchange rate liberalisation as a natural experiment, the paper finds significant, though economically small, effects on trust, participation and identity.</t>
+        </is>
+      </c>
       <c r="O42" s="16" t="inlineStr"/>
       <c r="P42" s="16" t="inlineStr"/>
       <c r="Q42" s="16" t="inlineStr"/>
@@ -6063,7 +6315,7 @@
       <c r="T42" s="16" t="inlineStr"/>
       <c r="U42" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="V42" s="16" t="inlineStr"/>
@@ -6074,20 +6326,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>ICTs quality and technical efficiency</t>
+          <t>Trade for catch-up: examining how global value chains participation affects productive efficiency</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Telecommunications Policy 46(10)</t>
+          <t>Journal of Productivity Analysis 59(2), 195–215</t>
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Otioma, Owusu, Tetteh</t>
+          <t>Ndubuisi, Owusu</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
@@ -6103,18 +6355,26 @@
       <c r="H43" s="15" t="inlineStr"/>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0308596122001410</t>
+          <t>https://link.springer.com/article/10.1007/s11123-023-00663-6</t>
         </is>
       </c>
       <c r="J43" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/icts-quality-and-technical-efficiency</t>
+          <t>https://rita-woad.vercel.app/research/publications/trade-for-catch-up-how-gvc-participation-affects-productive-efficiency</t>
         </is>
       </c>
       <c r="K43" s="16" t="inlineStr"/>
-      <c r="L43" s="16" t="inlineStr"/>
+      <c r="L43" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M43" s="16" t="inlineStr"/>
-      <c r="N43" s="16" t="inlineStr"/>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>Earlier studies of trade-driven catch-up overlooked global value chain participation as a way to speed up efficiency gains. The paper finds that GVC participation helps technology-lagging countries become more efficient and close the gap to the frontier.</t>
+        </is>
+      </c>
       <c r="O43" s="16" t="inlineStr"/>
       <c r="P43" s="16" t="inlineStr"/>
       <c r="Q43" s="16" t="inlineStr"/>
@@ -6134,12 +6394,12 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Import penetration and manufacturing employment: evidence from Africa</t>
+          <t>Disruptive technologies and manufacturing performance in South Africa: firm-level evidence</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>UNU-MERIT Working Paper 2022-007</t>
+          <t>AERC Working Paper 2022/004</t>
         </is>
       </c>
       <c r="D44" s="15" t="n">
@@ -6147,7 +6407,7 @@
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Mensah, Owusu</t>
+          <t>Avenyo, Bell</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -6163,18 +6423,26 @@
       <c r="H44" s="15" t="inlineStr"/>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>https://unu-merit.nl/publications/wppdf/2022/wp2022-007.pdf</t>
+          <t>https://publication.aercafricalibrary.org/handle/123456789/3444</t>
         </is>
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/import-penetration-and-manufacturing-employment-evidence-from-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/disruptive-technologies-and-manufacturing-performance-in-south-africa</t>
         </is>
       </c>
       <c r="K44" s="16" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
+      <c r="L44" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M44" s="16" t="inlineStr"/>
-      <c r="N44" s="16" t="inlineStr"/>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>The paper tests whether adopting disruptive digital technologies improves the performance of South African manufacturing firms. It addresses a thin evidence base on technology adoption and digital skills in developing countries and discusses implications for national Fourth Industrial Revolution policy.</t>
+        </is>
+      </c>
       <c r="O44" s="16" t="inlineStr"/>
       <c r="P44" s="16" t="inlineStr"/>
       <c r="Q44" s="16" t="inlineStr"/>
@@ -6183,7 +6451,7 @@
       <c r="T44" s="16" t="inlineStr"/>
       <c r="U44" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V44" s="16" t="inlineStr"/>
@@ -6194,12 +6462,12 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Industrial policy, the manufacturing sector and black empowerment in South Africa</t>
+          <t>Fibre processing &amp; manufacturing SETA and Industry 4.0</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Transformation 109</t>
+          <t>CCRED-IDTT Working Paper 2022/08</t>
         </is>
       </c>
       <c r="D45" s="15" t="n">
@@ -6207,32 +6475,36 @@
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Goga</t>
+          <t>Avenyo</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr"/>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>https://muse.jhu.edu/pub/99/article/871140/summary</t>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>TBC</t>
         </is>
       </c>
       <c r="J45" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/industrial-policy-the-manufacturing-sector-and-black-empowerment-in</t>
+          <t>https://rita-woad.vercel.app/research/publications/fibre-processing-and-manufacturing-seta-and-industry-4-0</t>
         </is>
       </c>
       <c r="K45" s="16" t="inlineStr"/>
-      <c r="L45" s="16" t="inlineStr"/>
+      <c r="L45" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M45" s="16" t="inlineStr"/>
       <c r="N45" s="16" t="inlineStr"/>
       <c r="O45" s="16" t="inlineStr"/>
@@ -6254,12 +6526,12 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Renewable energy consumption, globalization and economic growth shocks: evidence from G7 countries</t>
+          <t>Global value chain participation and innovation: firm-level evidence from Africa</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Journal of International Trade &amp; Economic Development 31(2)</t>
+          <t>AERC Working Paper GVC-012</t>
         </is>
       </c>
       <c r="D46" s="15" t="n">
@@ -6267,34 +6539,42 @@
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Abid, Guesmi</t>
+          <t>Avenyo, Mensah, Ndubuisi, Sakyi</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
         <is>
-          <t>03 Energy &amp; industry</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H46" s="15" t="inlineStr"/>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>https://www.tandfonline.com/doi/full/10.1080/09638199.2021.1961845</t>
+          <t>https://publication.aercafricalibrary.org/items/d47bb03f-a59d-4429-9b5e-d0a6c0ffb27f</t>
         </is>
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/renewable-energy-consumption-globalization-and-economic-growth-shocks</t>
+          <t>https://rita-woad.vercel.app/research/publications/gvc-participation-and-innovation-firm-level-evidence-from-africa</t>
         </is>
       </c>
       <c r="K46" s="16" t="inlineStr"/>
-      <c r="L46" s="16" t="inlineStr"/>
+      <c r="L46" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M46" s="16" t="inlineStr"/>
-      <c r="N46" s="16" t="inlineStr"/>
+      <c r="N46" s="16" t="inlineStr">
+        <is>
+          <t>The paper asks whether engagement in global value chains (GVCs) is linked to the innovative capabilities of firms in Africa.</t>
+        </is>
+      </c>
       <c r="O46" s="16" t="inlineStr"/>
       <c r="P46" s="16" t="inlineStr"/>
       <c r="Q46" s="16" t="inlineStr"/>
@@ -6303,7 +6583,7 @@
       <c r="T46" s="16" t="inlineStr"/>
       <c r="U46" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V46" s="16" t="inlineStr"/>
@@ -6314,12 +6594,12 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>State of the chemical industry: an Industry 4.0 perspective</t>
+          <t>Greening manufacturing: technology intensity and carbon dioxide emissions in developing countries</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>CCRED-IDTT Working Paper 2022/07</t>
+          <t>Applied Energy 324, 119726</t>
         </is>
       </c>
       <c r="D47" s="15" t="n">
@@ -6327,34 +6607,46 @@
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Avenyo, Tregenna</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="inlineStr"/>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+          <t>01 Green industrialisation &amp; policy</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.apenergy.2022.119726</t>
         </is>
       </c>
       <c r="J47" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/state-of-the-chemical-industry-an-industry-4-0-perspective</t>
+          <t>https://rita-woad.vercel.app/research/publications/greening-manufacturing-technology-intensity-and-co2-emissions-in</t>
         </is>
       </c>
       <c r="K47" s="16" t="inlineStr"/>
-      <c r="L47" s="16" t="inlineStr"/>
+      <c r="L47" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M47" s="16" t="inlineStr"/>
-      <c r="N47" s="16" t="inlineStr"/>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>The paper asks whether medium- and high-technology manufacturing industries are less emissions-intensive than low-technology ones in developing countries. It finds that medium- and high-technology industries are associated with lower CO₂ emissions, with differences that vary by countries' income levels.</t>
+        </is>
+      </c>
       <c r="O47" s="16" t="inlineStr"/>
       <c r="P47" s="16" t="inlineStr"/>
       <c r="Q47" s="16" t="inlineStr"/>
@@ -6363,7 +6655,7 @@
       <c r="T47" s="16" t="inlineStr"/>
       <c r="U47" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V47" s="16" t="inlineStr"/>
@@ -6374,12 +6666,12 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa’s prospect of economic development through global supply chains</t>
+          <t>ICTs quality and technical efficiency: an empirical analysis</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Sustainable Global Supply Chains Report 2022 (IDOS)</t>
+          <t>Telecommunications Policy 46(10), 102439</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
@@ -6387,34 +6679,42 @@
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu</t>
+          <t>Ndubuisi, Otioma, Owusu, Tetteh</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>Book chapter</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H48" s="15" t="inlineStr"/>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>https://www.die-gdi.de/fileadmin/user_upload/pdfs/projekt/20220407_SustainableGlobalSupplyChains-Report2022_lowres.pdf</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0308596122001410</t>
         </is>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/sub-saharan-africas-prospect-of-economic-development-through-global</t>
+          <t>https://rita-woad.vercel.app/research/publications/icts-quality-and-technical-efficiency</t>
         </is>
       </c>
       <c r="K48" s="16" t="inlineStr"/>
-      <c r="L48" s="16" t="inlineStr"/>
+      <c r="L48" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M48" s="16" t="inlineStr"/>
-      <c r="N48" s="16" t="inlineStr"/>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>Earlier work on ICTs and technical efficiency relied mainly on quantity-based ICT measures, which have come under severe criticism. This paper shifts the focus to quality-based measures, in this case Internet quality, and finds a positive effect on technical efficiency.</t>
+        </is>
+      </c>
       <c r="O48" s="16" t="inlineStr"/>
       <c r="P48" s="16" t="inlineStr"/>
       <c r="Q48" s="16" t="inlineStr"/>
@@ -6423,7 +6723,7 @@
       <c r="T48" s="16" t="inlineStr"/>
       <c r="U48" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V48" s="16" t="inlineStr"/>
@@ -6434,12 +6734,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Trust, efficient contracting and export upgrading</t>
+          <t>Import penetration and manufacturing employment: evidence from Africa</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>European Journal of Development Research 34</t>
+          <t>UNU-MERIT Working Paper 2022-007</t>
         </is>
       </c>
       <c r="D49" s="15" t="n">
@@ -6447,12 +6747,12 @@
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu</t>
+          <t>Owusu, Ndubuisi, Mensah</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr">
@@ -6461,20 +6761,28 @@
         </is>
       </c>
       <c r="H49" s="15" t="inlineStr"/>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>https://merit.unu.edu/publications/working-papers/abstract/?id=9242</t>
         </is>
       </c>
       <c r="J49" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/trust-efficient-contracting-and-export-upgrading</t>
+          <t>https://rita-woad.vercel.app/research/publications/import-penetration-and-manufacturing-employment-evidence-from-africa</t>
         </is>
       </c>
       <c r="K49" s="16" t="inlineStr"/>
-      <c r="L49" s="16" t="inlineStr"/>
+      <c r="L49" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M49" s="16" t="inlineStr"/>
-      <c r="N49" s="16" t="inlineStr"/>
+      <c r="N49" s="16" t="inlineStr">
+        <is>
+          <t>Cross-country evidence on the labour market effects of import penetration in Africa is scarce. This paper studies how imports of intermediate and final goods affect manufacturing employment across African countries.</t>
+        </is>
+      </c>
       <c r="O49" s="16" t="inlineStr"/>
       <c r="P49" s="16" t="inlineStr"/>
       <c r="Q49" s="16" t="inlineStr"/>
@@ -6483,7 +6791,7 @@
       <c r="T49" s="16" t="inlineStr"/>
       <c r="U49" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V49" s="16" t="inlineStr"/>
@@ -6494,12 +6802,12 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Wage effects of GVC participation and position</t>
+          <t>Industrial policy, the manufacturing sector and black empowerment in South Africa</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Journal of International Trade &amp; Economic Development 31(7)</t>
+          <t>Transformation: Critical Perspectives on Southern Africa 109, 80–111</t>
         </is>
       </c>
       <c r="D50" s="15" t="n">
@@ -6507,7 +6815,7 @@
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu</t>
+          <t>Goga, Avenyo</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -6517,24 +6825,32 @@
       </c>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H50" s="15" t="inlineStr"/>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>https://www.tandfonline.com/doi/full/10.1080/09638199.2022.2058068</t>
+          <t>https://muse.jhu.edu/article/871140</t>
         </is>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/wage-effects-of-gvc-participation-and-position</t>
+          <t>https://rita-woad.vercel.app/research/publications/industrial-policy-the-manufacturing-sector-and-black-empowerment-in</t>
         </is>
       </c>
       <c r="K50" s="16" t="inlineStr"/>
-      <c r="L50" s="16" t="inlineStr"/>
+      <c r="L50" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M50" s="16" t="inlineStr"/>
-      <c r="N50" s="16" t="inlineStr"/>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>Black Economic Empowerment has been an ambitious project, but results in key sectors have fallen short. The paper asks why South Africa has not seen the emergence of a large, economically significant black industrialist class, and whether industrial policy has helped or undermined deep transformation.</t>
+        </is>
+      </c>
       <c r="O50" s="16" t="inlineStr"/>
       <c r="P50" s="16" t="inlineStr"/>
       <c r="Q50" s="16" t="inlineStr"/>
@@ -6543,7 +6859,7 @@
       <c r="T50" s="16" t="inlineStr"/>
       <c r="U50" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V50" s="16" t="inlineStr"/>
@@ -6554,20 +6870,20 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Digital infrastructure and employment in services: evidence from sub-Saharan Africa</t>
+          <t>Renewable energy consumption, globalization, and economic growth shocks: evidence from G7 countries</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Telecommunications Policy 45(8)</t>
+          <t>Journal of International Trade &amp; Economic Development 31(2), 204–232</t>
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Otioma, Tetteh</t>
+          <t>Urom, Abid, Guesmi, Ndubuisi</t>
         </is>
       </c>
       <c r="F51" s="15" t="inlineStr">
@@ -6577,24 +6893,32 @@
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>03 Energy &amp; industry</t>
         </is>
       </c>
       <c r="H51" s="15" t="inlineStr"/>
       <c r="I51" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0308596121000574</t>
+          <t>https://www.tandfonline.com/doi/full/10.1080/09638199.2021.1961845</t>
         </is>
       </c>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/digital-infrastructure-and-employment-in-services-evidence-from-sub</t>
+          <t>https://rita-woad.vercel.app/research/publications/renewable-energy-consumption-globalization-and-economic-growth-shocks</t>
         </is>
       </c>
       <c r="K51" s="16" t="inlineStr"/>
-      <c r="L51" s="16" t="inlineStr"/>
+      <c r="L51" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M51" s="16" t="inlineStr"/>
-      <c r="N51" s="16" t="inlineStr"/>
+      <c r="N51" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines asymmetric responses of renewable energy consumption to globalisation and economic growth shocks across the G7. Responses differ by country, but renewable energy deployment in the G7 is mainly driven by positive shocks to income, globalisation and capital.</t>
+        </is>
+      </c>
       <c r="O51" s="16" t="inlineStr"/>
       <c r="P51" s="16" t="inlineStr"/>
       <c r="Q51" s="16" t="inlineStr"/>
@@ -6603,7 +6927,7 @@
       <c r="T51" s="16" t="inlineStr"/>
       <c r="U51" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V51" s="16" t="inlineStr"/>
@@ -6614,25 +6938,25 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Digital platforms and development: a survey of the literature</t>
+          <t>State of the chemical industry: an Industry 4.0 perspective</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Innovation &amp; Development 11</t>
+          <t>CCRED-IDTT Working Paper 2022/07</t>
         </is>
       </c>
       <c r="D52" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Fu, Ghauri</t>
+          <t>Avenyo</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -6641,14 +6965,14 @@
         </is>
       </c>
       <c r="H52" s="15" t="inlineStr"/>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/2157930X.2021.1975361</t>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>TBC</t>
         </is>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/digital-platforms-and-development-a-survey-of-the-literature</t>
+          <t>https://rita-woad.vercel.app/research/publications/state-of-the-chemical-industry-an-industry-4-0-perspective</t>
         </is>
       </c>
       <c r="K52" s="16" t="inlineStr"/>
@@ -6663,7 +6987,7 @@
       <c r="T52" s="16" t="inlineStr"/>
       <c r="U52" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V52" s="16" t="inlineStr"/>
@@ -6674,47 +6998,55 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Do productive capabilities affect export performance? Evidence from African firms</t>
+          <t>Sub-Saharan Africa’s prospect of economic development through global supply chains</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>European Journal of Development Research 33</t>
+          <t>Sustainable Global Supply Chains Report 2022, German Development Institute (DIE/IDOS), special section, p. 126</t>
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Tregenna, Kraemer-Mbula</t>
+          <t>Ndubuisi, Owusu</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Book chapter</t>
         </is>
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr"/>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>https://link.springer.com/article/10.1057/s41287-021-00364-6</t>
+          <t>https://www.oxfordmartin.ox.ac.uk/publications/sub-saharan-africas-prospect-of-economic-development-through-global-supply-chains</t>
         </is>
       </c>
       <c r="J53" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/do-productive-capabilities-affect-export-performance-evidence-from</t>
+          <t>https://rita-woad.vercel.app/research/publications/sub-saharan-africas-prospect-of-economic-development-through-global</t>
         </is>
       </c>
       <c r="K53" s="16" t="inlineStr"/>
-      <c r="L53" s="16" t="inlineStr"/>
+      <c r="L53" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M53" s="16" t="inlineStr"/>
-      <c r="N53" s="16" t="inlineStr"/>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>The chapter discusses the prospects of a global supply chain-led development strategy for Africa amid four megatrends, to identify research gaps. Global supply chains remain an important vehicle for Africa's development, but the megatrends have profound implications for that prospect.</t>
+        </is>
+      </c>
       <c r="O53" s="16" t="inlineStr"/>
       <c r="P53" s="16" t="inlineStr"/>
       <c r="Q53" s="16" t="inlineStr"/>
@@ -6734,20 +7066,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Effects of COVID-19 on the labour market in sub-Saharan Africa: informality in Burkina Faso, Mali and Senegal</t>
+          <t>Trust, efficient contracting and export upgrading</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Revue d'économie du développement 29</t>
+          <t>European Journal of Development Research 34(6), 2708–2729</t>
         </is>
       </c>
       <c r="D54" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Balde, Boly</t>
+          <t>Ndubuisi, Owusu</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -6763,18 +7095,26 @@
       <c r="H54" s="15" t="inlineStr"/>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>https://www.cairn.info/revue-d-economie-du-developpement-2021-1-page-43.htm</t>
+          <t>https://ideas.repec.org/a/pal/eurjdr/v34y2022i6d10.1057_s41287-021-00486-x.html</t>
         </is>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/effects-of-covid-19-on-the-labour-market-in-sub-saharan-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/trust-efficient-contracting-and-export-upgrading</t>
         </is>
       </c>
       <c r="K54" s="16" t="inlineStr"/>
-      <c r="L54" s="16" t="inlineStr"/>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M54" s="16" t="inlineStr"/>
-      <c r="N54" s="16" t="inlineStr"/>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>Research on contracting institutions and export quality has largely overlooked informal institutions. The paper tests whether trust drives product-quality upgrading by easing contractual frictions, and finds that contract-intensive industries in high-trust countries upgrade more.</t>
+        </is>
+      </c>
       <c r="O54" s="16" t="inlineStr"/>
       <c r="P54" s="16" t="inlineStr"/>
       <c r="Q54" s="16" t="inlineStr"/>
@@ -6783,7 +7123,7 @@
       <c r="T54" s="16" t="inlineStr"/>
       <c r="U54" s="16" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V54" s="16" t="inlineStr"/>
@@ -6794,20 +7134,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Financial constraints, trust and export performance: firm-level evidence from Africa</t>
+          <t>Wage effects of global value chains participation and position: an industry-level analysis</t>
         </is>
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Journal of Institutional Economics 17(4)</t>
+          <t>Journal of International Trade &amp; Economic Development 31(7), 1086–1107</t>
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Konte</t>
+          <t>Ndubuisi, Owusu</t>
         </is>
       </c>
       <c r="F55" s="15" t="inlineStr">
@@ -6821,20 +7161,28 @@
         </is>
       </c>
       <c r="H55" s="15" t="inlineStr"/>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>https://www.tandfonline.com/doi/full/10.1080/09638199.2022.2058068</t>
         </is>
       </c>
       <c r="J55" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/financial-constraints-trust-and-export-performance-firm-level-evidence</t>
+          <t>https://rita-woad.vercel.app/research/publications/wage-effects-of-gvc-participation-and-position</t>
         </is>
       </c>
       <c r="K55" s="16" t="inlineStr"/>
-      <c r="L55" s="16" t="inlineStr"/>
+      <c r="L55" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M55" s="16" t="inlineStr"/>
-      <c r="N55" s="16" t="inlineStr"/>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>The paper studies how participation and position in global value chains (GVCs) affect wages, comparing developed and developing countries and different labour market regulations.</t>
+        </is>
+      </c>
       <c r="O55" s="16" t="inlineStr"/>
       <c r="P55" s="16" t="inlineStr"/>
       <c r="Q55" s="16" t="inlineStr"/>
@@ -6843,7 +7191,7 @@
       <c r="T55" s="16" t="inlineStr"/>
       <c r="U55" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V55" s="16" t="inlineStr"/>
@@ -6854,12 +7202,12 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>How important is GVC participation for export upgrading?</t>
+          <t>Digital infrastructure and employment in services: evidence from sub-Saharan African countries</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>The World Economy 44(10)</t>
+          <t>Telecommunications Policy 45(8), 102153</t>
         </is>
       </c>
       <c r="D56" s="15" t="n">
@@ -6867,7 +7215,7 @@
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu</t>
+          <t>Ndubuisi, Otioma, Tetteh</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -6883,18 +7231,26 @@
       <c r="H56" s="15" t="inlineStr"/>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/twec.13102</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0308596121000574</t>
         </is>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/how-important-is-gvc-participation-for-export-upgrading</t>
+          <t>https://rita-woad.vercel.app/research/publications/digital-infrastructure-and-employment-in-services-evidence-from-sub</t>
         </is>
       </c>
       <c r="K56" s="16" t="inlineStr"/>
-      <c r="L56" s="16" t="inlineStr"/>
+      <c r="L56" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M56" s="16" t="inlineStr"/>
-      <c r="N56" s="16" t="inlineStr"/>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines the link between digital infrastructure and employment in the services sector in sub-Saharan Africa, and the conditions under which the link is stronger or weaker.</t>
+        </is>
+      </c>
       <c r="O56" s="16" t="inlineStr"/>
       <c r="P56" s="16" t="inlineStr"/>
       <c r="Q56" s="16" t="inlineStr"/>
@@ -6903,7 +7259,7 @@
       <c r="T56" s="16" t="inlineStr"/>
       <c r="U56" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V56" s="16" t="inlineStr"/>
@@ -6914,12 +7270,12 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Identifying vulnerable and priority manufacturing sectors for economic recovery in South Africa</t>
+          <t>Digital platforms and development: a survey of the literature</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>CCRED-IDTT Working Paper 2021/05</t>
+          <t>Innovation and Development 11(2-3), 303–321</t>
         </is>
       </c>
       <c r="D57" s="15" t="n">
@@ -6927,34 +7283,42 @@
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Fu, Avenyo, Ghauri</t>
         </is>
       </c>
       <c r="F57" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H57" s="15" t="inlineStr"/>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/2157930X.2021.1975361</t>
         </is>
       </c>
       <c r="J57" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/identifying-vulnerable-and-priority-manufacturing-sectors-for-economic</t>
+          <t>https://rita-woad.vercel.app/research/publications/digital-platforms-and-development-a-survey-of-the-literature</t>
         </is>
       </c>
       <c r="K57" s="16" t="inlineStr"/>
-      <c r="L57" s="16" t="inlineStr"/>
+      <c r="L57" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M57" s="16" t="inlineStr"/>
-      <c r="N57" s="16" t="inlineStr"/>
+      <c r="N57" s="16" t="inlineStr">
+        <is>
+          <t>A systematic literature review of how digital technology and platforms affect development in the modern economy. The authors group the literature into three main themes and point to directions for future research.</t>
+        </is>
+      </c>
       <c r="O57" s="16" t="inlineStr"/>
       <c r="P57" s="16" t="inlineStr"/>
       <c r="Q57" s="16" t="inlineStr"/>
@@ -6963,7 +7327,7 @@
       <c r="T57" s="16" t="inlineStr"/>
       <c r="U57" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V57" s="16" t="inlineStr"/>
@@ -6974,12 +7338,12 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Innovation and performance of informal enterprises: a gender perspective</t>
+          <t>Do productive capabilities affect export performance? Evidence from African firms</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>International Journal of Gender and Entrepreneurship 13</t>
+          <t>European Journal of Development Research 33(2)</t>
         </is>
       </c>
       <c r="D58" s="15" t="n">
@@ -6987,7 +7351,7 @@
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Kraemer-Mbula</t>
+          <t>Avenyo, Tregenna, Kraemer-Mbula</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -7003,18 +7367,22 @@
       <c r="H58" s="15" t="inlineStr"/>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1108/IJGE-11-2020-0174</t>
+          <t>https://link.springer.com/article/10.1057/s41287-021-00364-6</t>
         </is>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/innovation-and-performance-of-informal-enterprises-a-gender-perspective</t>
+          <t>https://rita-woad.vercel.app/research/publications/do-productive-capabilities-affect-export-performance-evidence-from</t>
         </is>
       </c>
       <c r="K58" s="16" t="inlineStr"/>
       <c r="L58" s="16" t="inlineStr"/>
       <c r="M58" s="16" t="inlineStr"/>
-      <c r="N58" s="16" t="inlineStr"/>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>There is limited empirical evidence on productive capabilities and their effect on firm-level export performance in Africa. The paper builds indicators that treat productive capabilities as a mix of technological and production capabilities, and finds both significantly drive firms' direct export performance.</t>
+        </is>
+      </c>
       <c r="O58" s="16" t="inlineStr"/>
       <c r="P58" s="16" t="inlineStr"/>
       <c r="Q58" s="16" t="inlineStr"/>
@@ -7034,12 +7402,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Learning and product innovation in informal enterprises: urban Ghana</t>
+          <t>Export variety and imported intermediate inputs: industry-level evidence from Africa</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>MPRA Working Paper 108839</t>
+          <t>MPRA Paper No. 106008</t>
         </is>
       </c>
       <c r="D59" s="15" t="n">
@@ -7047,7 +7415,7 @@
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Ndubuisi, Mensah, Owusu</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr">
@@ -7061,20 +7429,28 @@
         </is>
       </c>
       <c r="H59" s="15" t="inlineStr"/>
-      <c r="I59" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>https://mpra.ub.uni-muenchen.de/106008/</t>
         </is>
       </c>
       <c r="J59" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/learning-and-product-innovation-in-informal-enterprises-urban-ghana</t>
+          <t>https://rita-woad.vercel.app/research/publications/export-variety-and-imported-intermediate-inputs-industry-level-evidence</t>
         </is>
       </c>
       <c r="K59" s="16" t="inlineStr"/>
-      <c r="L59" s="16" t="inlineStr"/>
+      <c r="L59" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M59" s="16" t="inlineStr"/>
-      <c r="N59" s="16" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>Using manufacturing industry-level data for 26 African countries, the paper finds strong evidence of a positive relationship between imported intermediate inputs and the variety of exported products. Imported inputs help because they are lower-priced and embody higher quality and technology.</t>
+        </is>
+      </c>
       <c r="O59" s="16" t="inlineStr"/>
       <c r="P59" s="16" t="inlineStr"/>
       <c r="Q59" s="16" t="inlineStr"/>
@@ -7083,7 +7459,7 @@
       <c r="T59" s="16" t="inlineStr"/>
       <c r="U59" s="16" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V59" s="16" t="inlineStr"/>
@@ -7094,12 +7470,12 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>On gender and spatial gaps in Africa’s informal sector: evidence from urban Ghana</t>
+          <t>Financial constraint, trust, and export performances: firm-level evidence from Africa</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Economics Letters 199</t>
+          <t>Journal of Institutional Economics 17(4), 583–605</t>
         </is>
       </c>
       <c r="D60" s="15" t="n">
@@ -7107,7 +7483,7 @@
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Francois, Zinyemba</t>
+          <t>Konte, Ndubuisi</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -7123,18 +7499,26 @@
       <c r="H60" s="15" t="inlineStr"/>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0165176521000094</t>
+          <t>https://ideas.repec.org/a/cup/jinsec/v17y2021i4p583-605_4.html</t>
         </is>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/on-gender-and-spatial-gaps-in-africas-informal-sector-evidence-from</t>
+          <t>https://rita-woad.vercel.app/research/publications/financial-constraints-trust-and-export-performance-firm-level-evidence</t>
         </is>
       </c>
       <c r="K60" s="16" t="inlineStr"/>
-      <c r="L60" s="16" t="inlineStr"/>
+      <c r="L60" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M60" s="16" t="inlineStr"/>
-      <c r="N60" s="16" t="inlineStr"/>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines the effect of financial constraints on exports in Africa and how the level of trust in the countries where firms are located shapes this relationship. Financial constraints reduce export activity, but the negative effect is weaker where trust is higher.</t>
+        </is>
+      </c>
       <c r="O60" s="16" t="inlineStr"/>
       <c r="P60" s="16" t="inlineStr"/>
       <c r="Q60" s="16" t="inlineStr"/>
@@ -7143,7 +7527,7 @@
       <c r="T60" s="16" t="inlineStr"/>
       <c r="U60" s="16" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V60" s="16" t="inlineStr"/>
@@ -7154,12 +7538,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Product innovations and informal market competition in sub-Saharan Africa</t>
+          <t>How important is GVC participation for export upgrading?</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Journal of Evolutionary Economics 31</t>
+          <t>The World Economy 44(10), 2886–2907</t>
         </is>
       </c>
       <c r="D61" s="15" t="n">
@@ -7167,7 +7551,7 @@
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Konte, Mohnen</t>
+          <t>Ndubuisi, Owusu</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
@@ -7183,18 +7567,26 @@
       <c r="H61" s="15" t="inlineStr"/>
       <c r="I61" s="17" t="inlineStr">
         <is>
-          <t>https://link.springer.com/article/10.1007/s00191-020-00688-2</t>
+          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/twec.13102</t>
         </is>
       </c>
       <c r="J61" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/product-innovations-and-informal-market-competition-in-sub-saharan</t>
+          <t>https://rita-woad.vercel.app/research/publications/how-important-is-gvc-participation-for-export-upgrading</t>
         </is>
       </c>
       <c r="K61" s="16" t="inlineStr"/>
-      <c r="L61" s="16" t="inlineStr"/>
+      <c r="L61" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M61" s="16" t="inlineStr"/>
-      <c r="N61" s="16" t="inlineStr"/>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>High-quality exports need knowledge-intensive production, quality inputs and advanced technology, and global value chains are one route to them. Using product-level export data, the paper finds that participation in backward and forward GVCs raises the quality of exported products.</t>
+        </is>
+      </c>
       <c r="O61" s="16" t="inlineStr"/>
       <c r="P61" s="16" t="inlineStr"/>
       <c r="Q61" s="16" t="inlineStr"/>
@@ -7203,7 +7595,7 @@
       <c r="T61" s="16" t="inlineStr"/>
       <c r="U61" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V61" s="16" t="inlineStr"/>
@@ -7214,12 +7606,12 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Technology intensity in manufacturing and CO₂ emissions</t>
+          <t>Identifying vulnerable and priority manufacturing sectors for economic recovery in South Africa</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>ERSA Working Paper 846</t>
+          <t>CCRED-IDTT Working Paper 2021/05</t>
         </is>
       </c>
       <c r="D62" s="15" t="n">
@@ -7227,7 +7619,7 @@
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Tregenna</t>
+          <t>Avenyo, Bell, Nyamwena, Robb</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -7241,18 +7633,22 @@
         </is>
       </c>
       <c r="H62" s="15" t="inlineStr"/>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>https://www.competition.org.za/s/IDTT-4_WP_Identifying_vulnerable_and_priority_manufacturing_sectors_for_economic_recovery_in_South_A.pdf</t>
         </is>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/technology-intensity-in-manufacturing-and-co2-emissions</t>
+          <t>https://rita-woad.vercel.app/research/publications/identifying-vulnerable-and-priority-manufacturing-sectors-for-economic</t>
         </is>
       </c>
       <c r="K62" s="16" t="inlineStr"/>
-      <c r="L62" s="16" t="inlineStr"/>
+      <c r="L62" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M62" s="16" t="inlineStr"/>
       <c r="N62" s="16" t="inlineStr"/>
       <c r="O62" s="16" t="inlineStr"/>
@@ -7263,7 +7659,7 @@
       <c r="T62" s="16" t="inlineStr"/>
       <c r="U62" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V62" s="16" t="inlineStr"/>
@@ -7274,25 +7670,25 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>COVID-19, lockdowns and Africa’s informal sector: lessons from Ghana</t>
+          <t>Innovation and the performance of informal enterprises in developing countries: a gender perspective</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>UNU-MERIT Working Paper 2020-028</t>
+          <t>International Journal of Gender and Entrepreneurship 13(4), 277–301</t>
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Avenyo, Kraemer-Mbula</t>
         </is>
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G63" s="15" t="inlineStr">
@@ -7301,20 +7697,28 @@
         </is>
       </c>
       <c r="H63" s="15" t="inlineStr"/>
-      <c r="I63" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1108/IJGE-11-2020-0174</t>
         </is>
       </c>
       <c r="J63" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/covid-19-lockdowns-and-africas-informal-sector-lessons-from-ghana</t>
+          <t>https://rita-woad.vercel.app/research/publications/innovation-and-performance-of-informal-enterprises-a-gender-perspective</t>
         </is>
       </c>
       <c r="K63" s="16" t="inlineStr"/>
-      <c r="L63" s="16" t="inlineStr"/>
+      <c r="L63" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M63" s="16" t="inlineStr"/>
-      <c r="N63" s="16" t="inlineStr"/>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>The study looks at product innovation in informal enterprises to understand how it affects employment in female- and male-owned firms. Product innovation has beneficial effects on job creation, and the authors conclude that innovation is gendered and needs a gendered policy lens.</t>
+        </is>
+      </c>
       <c r="O63" s="16" t="inlineStr"/>
       <c r="P63" s="16" t="inlineStr"/>
       <c r="Q63" s="16" t="inlineStr"/>
@@ -7334,20 +7738,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Coping during COVID-19: family businesses and social assistance in Nigeria</t>
+          <t>Labour market effects of COVID-19 in sub-Saharan Africa: an informality lens from Burkina Faso, Mali and Senegal</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Covid Economics 51 (CEPR)</t>
+          <t>Revue d'économie du développement 29</t>
         </is>
       </c>
       <c r="D64" s="15" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Ndubuisi</t>
+          <t>Balde, Boly, Avenyo</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
@@ -7363,18 +7767,26 @@
       <c r="H64" s="15" t="inlineStr"/>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>https://cepr.org/publications/covid-economics-issue-51</t>
+          <t>https://www.cairn.info/revue-d-economie-du-developpement-2021-1-page-43.htm</t>
         </is>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/coping-during-covid-19-family-businesses-and-social-assistance-in</t>
+          <t>https://rita-woad.vercel.app/research/publications/effects-of-covid-19-on-the-labour-market-in-sub-saharan-africa</t>
         </is>
       </c>
       <c r="K64" s="16" t="inlineStr"/>
-      <c r="L64" s="16" t="inlineStr"/>
+      <c r="L64" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M64" s="16" t="inlineStr"/>
-      <c r="N64" s="16" t="inlineStr"/>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>Using real-time survey evidence from Burkina Faso, Mali and Senegal, the paper shows that workers in the informal economy were hit harder by the COVID-19 pandemic. Informal workers were more likely to lose their jobs, see earnings fall and struggle to meet basic needs.</t>
+        </is>
+      </c>
       <c r="O64" s="16" t="inlineStr"/>
       <c r="P64" s="16" t="inlineStr"/>
       <c r="Q64" s="16" t="inlineStr"/>
@@ -7394,20 +7806,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Exporters and GVC participation: firm-level evidence from South Africa</t>
+          <t>Learning and product innovation performance in informal enterprises: evidence from urban Ghana</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>WIDER Working Paper 2020/145</t>
+          <t>MPRA Paper 108839</t>
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Mazzi, Ndubuisi</t>
+          <t>Avenyo</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
@@ -7421,20 +7833,28 @@
         </is>
       </c>
       <c r="H65" s="15" t="inlineStr"/>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>https://mpra.ub.uni-muenchen.de/108839/</t>
         </is>
       </c>
       <c r="J65" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/exporters-and-gvc-participation-firm-level-evidence-from-south-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/learning-and-product-innovation-in-informal-enterprises-urban-ghana</t>
         </is>
       </c>
       <c r="K65" s="16" t="inlineStr"/>
-      <c r="L65" s="16" t="inlineStr"/>
+      <c r="L65" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M65" s="16" t="inlineStr"/>
-      <c r="N65" s="16" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines how learning shapes product innovation in informal enterprises in urban Ghana. Apprenticeship enhances the technological capability of enterprises, leading to product innovativeness, and competitive interactions with formal firms provide market feedback that enhances innovation.</t>
+        </is>
+      </c>
       <c r="O65" s="16" t="inlineStr"/>
       <c r="P65" s="16" t="inlineStr"/>
       <c r="Q65" s="16" t="inlineStr"/>
@@ -7443,7 +7863,7 @@
       <c r="T65" s="16" t="inlineStr"/>
       <c r="U65" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="V65" s="16" t="inlineStr"/>
@@ -7454,20 +7874,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Fettered cross-border capital flows, external finance dependence and international trade</t>
+          <t>On gender and spatial gaps in Africa’s informal sector: evidence from urban Ghana</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>International Economics 164</t>
+          <t>Economics Letters 199, 109732</t>
         </is>
       </c>
       <c r="D66" s="15" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Zinyemba, Avenyo, Francois</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
@@ -7477,24 +7897,32 @@
       </c>
       <c r="G66" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr"/>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S2110701720302705</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0165176521000094</t>
         </is>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/fettered-cross-border-capital-flows-external-finance-dependence-and</t>
+          <t>https://rita-woad.vercel.app/research/publications/on-gender-and-spatial-gaps-in-africas-informal-sector-evidence-from</t>
         </is>
       </c>
       <c r="K66" s="16" t="inlineStr"/>
-      <c r="L66" s="16" t="inlineStr"/>
+      <c r="L66" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M66" s="16" t="inlineStr"/>
-      <c r="N66" s="16" t="inlineStr"/>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>Using 2016 survey data from Accra and Tema, the paper finds an unexplained spatial gap in sales between informal enterprise owners in the two cities. There are no gender gaps in sales or innovation, but there are gender gaps in how past sales affect current sales.</t>
+        </is>
+      </c>
       <c r="O66" s="16" t="inlineStr"/>
       <c r="P66" s="16" t="inlineStr"/>
       <c r="Q66" s="16" t="inlineStr"/>
@@ -7503,7 +7931,7 @@
       <c r="T66" s="16" t="inlineStr"/>
       <c r="U66" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="V66" s="16" t="inlineStr"/>
@@ -7514,47 +7942,55 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Remittances and bribery in Africa</t>
+          <t>Product innovation and informal market competition in sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Routledge (book chapter)</t>
+          <t>Journal of Evolutionary Economics 31, 605–637</t>
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Konte</t>
+          <t>Avenyo, Konte, Mohnen</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>Book chapter</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G67" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H67" s="15" t="inlineStr"/>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00191-020-00688-2</t>
         </is>
       </c>
       <c r="J67" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/remittances-and-bribery-in-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/product-innovations-and-informal-market-competition-in-sub-saharan</t>
         </is>
       </c>
       <c r="K67" s="16" t="inlineStr"/>
-      <c r="L67" s="16" t="inlineStr"/>
+      <c r="L67" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M67" s="16" t="inlineStr"/>
-      <c r="N67" s="16" t="inlineStr"/>
+      <c r="N67" s="16" t="inlineStr">
+        <is>
+          <t>Competition from informal enterprises is one of the top three obstacles formal businesses face in sub-Saharan Africa. The paper finds that local informal competition harms the performance of product innovation, but only for formal firms that lack strategic collaborative footholds in the informal economy.</t>
+        </is>
+      </c>
       <c r="O67" s="16" t="inlineStr"/>
       <c r="P67" s="16" t="inlineStr"/>
       <c r="Q67" s="16" t="inlineStr"/>
@@ -7574,51 +8010,55 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>The employment impact of product innovations in sub-Saharan Africa</t>
+          <t>The effects of technology intensity in manufacturing on CO2 emissions: evidence from developing countries</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Research Policy 48(9)</t>
+          <t>ERSA Working Paper 846</t>
         </is>
       </c>
       <c r="D68" s="15" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Mohnen, Konte</t>
+          <t>Avenyo, Tregenna</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+          <t>01 Green industrialisation &amp; policy</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="inlineStr"/>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S004873331930126X</t>
+          <t>https://econrsa.org/publications/the-effects-of-technology-intensity-in-manufacturing-on-co2-emissions-evidence-from-developing-countries/</t>
         </is>
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/the-employment-impact-of-product-innovations-in-sub-saharan-africa</t>
+          <t>https://rita-woad.vercel.app/research/publications/technology-intensity-in-manufacturing-and-co2-emissions</t>
         </is>
       </c>
       <c r="K68" s="16" t="inlineStr"/>
-      <c r="L68" s="16" t="inlineStr"/>
+      <c r="L68" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M68" s="16" t="inlineStr"/>
-      <c r="N68" s="16" t="inlineStr"/>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>The paper asks whether high-technology manufacturing emits less CO2 than medium- and low-technology manufacturing in developing economies. It concludes that a shift towards more technology-intensive manufacturing could be a more sustainable industrialisation path.</t>
+        </is>
+      </c>
       <c r="O68" s="16" t="inlineStr"/>
       <c r="P68" s="16" t="inlineStr"/>
       <c r="Q68" s="16" t="inlineStr"/>
@@ -7627,7 +8067,7 @@
       <c r="T68" s="16" t="inlineStr"/>
       <c r="U68" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V68" s="16" t="inlineStr"/>
@@ -7638,20 +8078,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Estimating the effects of robotization on exports</t>
+          <t>COVID-19, lockdowns and Africa’s informal sector: lessons from Ghana</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>UNU-MERIT Working Paper 2018-046</t>
+          <t>UNU-MERIT Working Paper 2020-028</t>
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>Avenyo, Ndubuisi</t>
+          <t>Avenyo, Francois, Zinyemba</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
@@ -7665,20 +8105,28 @@
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr"/>
-      <c r="I69" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>https://www.merit.unu.edu/publications/working-papers/abstract/?id=8534</t>
         </is>
       </c>
       <c r="J69" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/estimating-the-effects-of-robotization-on-exports</t>
+          <t>https://rita-woad.vercel.app/research/publications/covid-19-lockdowns-and-africas-informal-sector-lessons-from-ghana</t>
         </is>
       </c>
       <c r="K69" s="16" t="inlineStr"/>
-      <c r="L69" s="16" t="inlineStr"/>
+      <c r="L69" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M69" s="16" t="inlineStr"/>
-      <c r="N69" s="16" t="inlineStr"/>
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>Using survey data on informal enterprises in Accra and Tema, the paper estimates the likely effects of COVID-19 lockdowns on Ghana's informal sector. Because the lockdown affects business performance, COVID-19 may widen or create gender and spatial gaps in informal enterprise performance.</t>
+        </is>
+      </c>
       <c r="O69" s="16" t="inlineStr"/>
       <c r="P69" s="16" t="inlineStr"/>
       <c r="Q69" s="16" t="inlineStr"/>
@@ -7687,7 +8135,7 @@
       <c r="T69" s="16" t="inlineStr"/>
       <c r="U69" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="V69" s="16" t="inlineStr"/>
@@ -7698,25 +8146,25 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>UNESCO Science Report: Towards 2030, ch. 2 "Tracking trends in innovation and mobility"</t>
+          <t>Contractual frictions and the patterns of trade: the role of generalized trust</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Journal of International Trade &amp; Economic Development 29(7), 775–796</t>
         </is>
       </c>
       <c r="D70" s="15" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Ndubuisi</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>Book chapter</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -7727,18 +8175,26 @@
       <c r="H70" s="15" t="inlineStr"/>
       <c r="I70" s="17" t="inlineStr">
         <is>
-          <t>https://unesdoc.unesco.org/ark:/48223/pf0000235446</t>
+          <t>https://ideas.repec.org/a/taf/jitecd/v29y2020i7p775-796.html</t>
         </is>
       </c>
       <c r="J70" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/unesco-science-report-towards-2030-ch-2-tracking-trends-in-innovation</t>
+          <t>https://rita-woad.vercel.app/research/publications/contractual-frictions-and-the-patterns-of-trade-the-role-of-generalized</t>
         </is>
       </c>
       <c r="K70" s="16" t="inlineStr"/>
-      <c r="L70" s="16" t="inlineStr"/>
+      <c r="L70" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M70" s="16" t="inlineStr"/>
-      <c r="N70" s="16" t="inlineStr"/>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>The paper looks at informal contracting institutions, measured by generalised trust, as a source of comparative advantage. Countries with higher trust export relatively more in industries prone to contractual frictions, which may explain why countries with weak formal institutions can still hold a cost advantage in contract-intensive industries.</t>
+        </is>
+      </c>
       <c r="O70" s="16" t="inlineStr"/>
       <c r="P70" s="16" t="inlineStr"/>
       <c r="Q70" s="16" t="inlineStr"/>
@@ -7758,49 +8214,55 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Chinese development finance and labour productivity growth in developing countries</t>
+          <t>Coping during COVID-19: family businesses and social assistance in Nigeria</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>SSRN Working Paper 4989817</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>Covid Economics: Vetted and Real-Time Papers 51, 159–184 (CEPR)</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Konte</t>
+          <t>Avenyo, Ndubuisi</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G71" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr"/>
       <c r="I71" s="17" t="inlineStr">
         <is>
-          <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=4989817</t>
+          <t>https://cepr.org/publications/covid-economics-issue-51</t>
         </is>
       </c>
       <c r="J71" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/chinese-development-finance-and-labour-productivity-growth-in</t>
+          <t>https://rita-woad.vercel.app/research/publications/coping-during-covid-19-family-businesses-and-social-assistance-in</t>
         </is>
       </c>
       <c r="K71" s="16" t="inlineStr"/>
-      <c r="L71" s="16" t="inlineStr"/>
+      <c r="L71" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M71" s="16" t="inlineStr"/>
-      <c r="N71" s="16" t="inlineStr"/>
+      <c r="N71" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines how changes in income and social assistance during the COVID-19 pandemic relate to the coping strategies of family business owners in Nigeria.</t>
+        </is>
+      </c>
       <c r="O71" s="16" t="inlineStr"/>
       <c r="P71" s="16" t="inlineStr"/>
       <c r="Q71" s="16" t="inlineStr"/>
@@ -7809,7 +8271,7 @@
       <c r="T71" s="16" t="inlineStr"/>
       <c r="U71" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="V71" s="16" t="inlineStr"/>
@@ -7820,27 +8282,25 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Contractual frictions and the patterns of trade: the role of generalized trust</t>
+          <t>Exporters and global value chain participation: firm-level evidence from South Africa</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Journal of International Trade &amp; Economic Development 29(7)</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>WIDER Working Paper 2020/145</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Mazzi, Ndubuisi, Avenyo</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -7849,20 +8309,28 @@
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr"/>
-      <c r="I72" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>https://wider.unu.edu/publication/exporters-and-global-value-chain-participation</t>
         </is>
       </c>
       <c r="J72" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/contractual-frictions-and-the-patterns-of-trade-the-role-of-generalized</t>
+          <t>https://rita-woad.vercel.app/research/publications/exporters-and-gvc-participation-firm-level-evidence-from-south-africa</t>
         </is>
       </c>
       <c r="K72" s="16" t="inlineStr"/>
-      <c r="L72" s="16" t="inlineStr"/>
+      <c r="L72" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M72" s="16" t="inlineStr"/>
-      <c r="N72" s="16" t="inlineStr"/>
+      <c r="N72" s="16" t="inlineStr">
+        <is>
+          <t>The study examines how global value chain (GVC) trade affects the performance of South African manufacturing exporters, comparing the productivity premium of traders across GVC-related and traditional product categories and testing for learning-by-exporting.</t>
+        </is>
+      </c>
       <c r="O72" s="16" t="inlineStr"/>
       <c r="P72" s="16" t="inlineStr"/>
       <c r="Q72" s="16" t="inlineStr"/>
@@ -7871,7 +8339,7 @@
       <c r="T72" s="16" t="inlineStr"/>
       <c r="U72" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="V72" s="16" t="inlineStr"/>
@@ -7882,18 +8350,16 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Contribution (JRC111430)</t>
+          <t>Fettered cross-border capital flows, external finance dependence, and international trade</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>European Commission Joint Research Centre</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>International Economics 164, 206–216</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
@@ -7902,7 +8368,7 @@
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G73" s="15" t="inlineStr">
@@ -7913,25 +8379,37 @@
       <c r="H73" s="15" t="inlineStr"/>
       <c r="I73" s="17" t="inlineStr">
         <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC111430</t>
+          <t>https://doi.org/10.1016/j.inteco.2020.10.002</t>
         </is>
       </c>
       <c r="J73" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/contribution-jrc111430</t>
+          <t>https://rita-woad.vercel.app/research/publications/fettered-cross-border-capital-flows-external-finance-dependence-and</t>
         </is>
       </c>
       <c r="K73" s="16" t="inlineStr"/>
-      <c r="L73" s="16" t="inlineStr"/>
+      <c r="L73" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M73" s="16" t="inlineStr"/>
-      <c r="N73" s="16" t="inlineStr"/>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>The paper evaluates how capital controls affect exports, a link that has not been thoroughly examined empirically. It uses bilateral industry-level export data for a large number of countries.</t>
+        </is>
+      </c>
       <c r="O73" s="16" t="inlineStr"/>
       <c r="P73" s="16" t="inlineStr"/>
       <c r="Q73" s="16" t="inlineStr"/>
       <c r="R73" s="16" t="inlineStr"/>
       <c r="S73" s="16" t="inlineStr"/>
       <c r="T73" s="16" t="inlineStr"/>
-      <c r="U73" s="16" t="inlineStr"/>
+      <c r="U73" s="16" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="V73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
@@ -7940,49 +8418,55 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Domestic IPR protection and the margins of bilateral exports</t>
+          <t>Remittances and bribery in Africa</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>UNU-MERIT Working Paper</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>In Konte and Mbaye (eds), Migration, Remittances, and Sustainable Development in Africa, Routledge, ch. 10, 179–198</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Foster-McGregor</t>
+          <t>Konte, Ndubuisi</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Book chapter</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr"/>
-      <c r="I74" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4324/9780429288814-13</t>
         </is>
       </c>
       <c r="J74" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/domestic-ipr-protection-and-the-margins-of-bilateral-exports</t>
+          <t>https://rita-woad.vercel.app/research/publications/remittances-and-bribery-in-africa</t>
         </is>
       </c>
       <c r="K74" s="16" t="inlineStr"/>
-      <c r="L74" s="16" t="inlineStr"/>
+      <c r="L74" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M74" s="16" t="inlineStr"/>
-      <c r="N74" s="16" t="inlineStr"/>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>Using Afrobarometer surveys, the chapter finds that remittance receivers are more prone to bribe payment than non-receivers. Individuals in countries with higher remittances as a share of GDP are also more likely to pay bribes, in line with an income channel.</t>
+        </is>
+      </c>
       <c r="O74" s="16" t="inlineStr"/>
       <c r="P74" s="16" t="inlineStr"/>
       <c r="Q74" s="16" t="inlineStr"/>
@@ -7991,7 +8475,7 @@
       <c r="T74" s="16" t="inlineStr"/>
       <c r="U74" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V74" s="16" t="inlineStr"/>
@@ -8002,27 +8486,25 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Export variety and imported intermediate inputs: industry-level evidence from Africa</t>
+          <t>Trust and R&amp;D investments: evidence from OECD countries</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>MPRA Working Paper 106008</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>Journal of Institutional Economics 16(6), 809–830</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Mensah, Owusu</t>
+          <t>Ndubuisi</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G75" s="15" t="inlineStr">
@@ -8033,18 +8515,26 @@
       <c r="H75" s="15" t="inlineStr"/>
       <c r="I75" s="17" t="inlineStr">
         <is>
-          <t>https://mpra.ub.uni-muenchen.de/106008/</t>
+          <t>https://econpapers.repec.org/article/cupjinsec/v_3a16_3ay_3a2020_3ai_3a6_3ap_3a809-830_5f4.htm</t>
         </is>
       </c>
       <c r="J75" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/export-variety-and-imported-intermediate-inputs-industry-level-evidence</t>
+          <t>https://rita-woad.vercel.app/research/publications/trust-and-r-and-d-investment-evidence-from-oecd-countries</t>
         </is>
       </c>
       <c r="K75" s="16" t="inlineStr"/>
-      <c r="L75" s="16" t="inlineStr"/>
+      <c r="L75" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M75" s="16" t="inlineStr"/>
-      <c r="N75" s="16" t="inlineStr"/>
+      <c r="N75" s="16" t="inlineStr">
+        <is>
+          <t>Social trust can increase R&amp;D investment by expanding firms' access to external finance and by reducing relational risks that expose firms to hold-ups or expropriation.</t>
+        </is>
+      </c>
       <c r="O75" s="16" t="inlineStr"/>
       <c r="P75" s="16" t="inlineStr"/>
       <c r="Q75" s="16" t="inlineStr"/>
@@ -8053,7 +8543,7 @@
       <c r="T75" s="16" t="inlineStr"/>
       <c r="U75" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V75" s="16" t="inlineStr"/>
@@ -8064,27 +8554,25 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Firm volatility in an era of global value chains: the role of product quality</t>
+          <t>The employment impact of product innovations in sub-Saharan Africa: firm-level evidence</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>AERC Working Paper GVC-11-007</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>Research Policy 48(9), 103806</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="n">
+        <v>2019</v>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu</t>
+          <t>Avenyo, Konte, Mohnen</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -8092,21 +8580,33 @@
           <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
-      <c r="H76" s="15" t="inlineStr"/>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
-          <t>https://publication.aercafricalibrary.org/items/9705d6c4-3a3e-4eb9-b4d7-ed909f8ebd4c</t>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S004873331930126X</t>
         </is>
       </c>
       <c r="J76" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/firm-volatility-in-an-era-of-global-value-chains-the-role-of-product</t>
+          <t>https://rita-woad.vercel.app/research/publications/the-employment-impact-of-product-innovations-in-sub-saharan-africa</t>
         </is>
       </c>
       <c r="K76" s="16" t="inlineStr"/>
-      <c r="L76" s="16" t="inlineStr"/>
+      <c r="L76" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M76" s="16" t="inlineStr"/>
-      <c r="N76" s="16" t="inlineStr"/>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>The paper investigates the impact of product innovations on job creation in sub-Saharan African firms. Product innovations raise total employment, but only at specific intervals of innovation intensity, and the gains are larger for temporary and unskilled jobs.</t>
+        </is>
+      </c>
       <c r="O76" s="16" t="inlineStr"/>
       <c r="P76" s="16" t="inlineStr"/>
       <c r="Q76" s="16" t="inlineStr"/>
@@ -8126,22 +8626,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Gendering structural change and green transition in Africa: implications of transformative policies</t>
+          <t>Domestic intellectual property rights protection and the margins of bilateral exports</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>ACET Working Paper</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>UNU-MERIT Working Paper 2018-035</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Avenyo, Chisoro</t>
+          <t>Ndubuisi, Foster-McGregor</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
@@ -8151,28 +8649,32 @@
       </c>
       <c r="G77" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
-        </is>
-      </c>
-      <c r="H77" s="15" t="inlineStr">
-        <is>
-          <t>Flagship</t>
-        </is>
-      </c>
+          <t>04 Innovation, firms &amp; work</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr"/>
       <c r="I77" s="17" t="inlineStr">
         <is>
-          <t>https://ie.yale.edu/sites/default/files/2024-10/ACET_Gendering_Structural_Change_and_Green_Transition_in_Africa.pdf</t>
+          <t>https://merit.unu.edu/publications/working-papers/abstract/?id=7899</t>
         </is>
       </c>
       <c r="J77" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/gendering-structural-change-and-green-transition-in-africa-implications</t>
+          <t>https://rita-woad.vercel.app/research/publications/domestic-ipr-protection-and-the-margins-of-bilateral-exports</t>
         </is>
       </c>
       <c r="K77" s="16" t="inlineStr"/>
-      <c r="L77" s="16" t="inlineStr"/>
+      <c r="L77" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M77" s="16" t="inlineStr"/>
-      <c r="N77" s="16" t="inlineStr"/>
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>Earlier research on domestic intellectual property rights (IPR) protection and trade has looked mostly at imports. This paper turns to exports and finds that IPRs are trade-related and can help boost exports in both developed and developing countries.</t>
+        </is>
+      </c>
       <c r="O77" s="16" t="inlineStr"/>
       <c r="P77" s="16" t="inlineStr"/>
       <c r="Q77" s="16" t="inlineStr"/>
@@ -8181,7 +8683,7 @@
       <c r="T77" s="16" t="inlineStr"/>
       <c r="U77" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V77" s="16" t="inlineStr"/>
@@ -8192,22 +8694,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Global value chains, job creation and job destruction among firms in South Africa</t>
+          <t>Estimating the effects of robotization on exports</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>STEG-CEPR Working Paper 073</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>UNU-MERIT Working Paper 2018-046</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Owusu</t>
+          <t>Ndubuisi, Avenyo</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -8223,18 +8723,26 @@
       <c r="H78" s="15" t="inlineStr"/>
       <c r="I78" s="17" t="inlineStr">
         <is>
-          <t>https://steg.cepr.org/sites/default/files/2023-08/WP073%20NdubuisiOwusuGlobalValueChainsJobCreation.pdf</t>
+          <t>https://merit.unu.edu/publications/working-papers/abstract/?id=8031</t>
         </is>
       </c>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/global-value-chains-job-creation-and-job-destruction-among-firms-in</t>
+          <t>https://rita-woad.vercel.app/research/publications/estimating-the-effects-of-robotization-on-exports</t>
         </is>
       </c>
       <c r="K78" s="16" t="inlineStr"/>
-      <c r="L78" s="16" t="inlineStr"/>
+      <c r="L78" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M78" s="16" t="inlineStr"/>
-      <c r="N78" s="16" t="inlineStr"/>
+      <c r="N78" s="16" t="inlineStr">
+        <is>
+          <t>Digitalisation has drawn the attention of empirical trade economists, but robotisation largely has not. This paper examines the impact of robotisation on trade and finds that it raises total exports, on both the extensive and the intensive margin.</t>
+        </is>
+      </c>
       <c r="O78" s="16" t="inlineStr"/>
       <c r="P78" s="16" t="inlineStr"/>
       <c r="Q78" s="16" t="inlineStr"/>
@@ -8243,7 +8751,7 @@
       <c r="T78" s="16" t="inlineStr"/>
       <c r="U78" s="16" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V78" s="16" t="inlineStr"/>
@@ -8254,18 +8762,16 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Informal innovations in urban Ghana: data set and descriptive analysis</t>
+          <t>Informal sector innovation in Ghana: data set and descriptive analysis</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>UNU-MERIT Working Paper</t>
-        </is>
-      </c>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>UNU-MERIT Working Paper 2018-030</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
@@ -8283,9 +8789,9 @@
         </is>
       </c>
       <c r="H79" s="15" t="inlineStr"/>
-      <c r="I79" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>https://merit.unu.edu/publications/working-papers/abstract/?id=7864</t>
         </is>
       </c>
       <c r="J79" s="17" t="inlineStr">
@@ -8294,9 +8800,17 @@
         </is>
       </c>
       <c r="K79" s="16" t="inlineStr"/>
-      <c r="L79" s="16" t="inlineStr"/>
+      <c r="L79" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M79" s="16" t="inlineStr"/>
-      <c r="N79" s="16" t="inlineStr"/>
+      <c r="N79" s="16" t="inlineStr">
+        <is>
+          <t>The paper presents descriptive statistics from a 2016 survey of the innovations informal firms adopt or adapt in Accra and Tema. It finds that informal enterprises do innovate: their innovations are incremental rather than radical, occur over several years, and matter for their survival.</t>
+        </is>
+      </c>
       <c r="O79" s="16" t="inlineStr"/>
       <c r="P79" s="16" t="inlineStr"/>
       <c r="Q79" s="16" t="inlineStr"/>
@@ -8316,47 +8830,49 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Solid mineral development in Nigeria: evidence from Ebonyi, Ekiti and Taraba states</t>
+          <t>Tracking trends in innovation and mobility (UNESCO Science Report: Towards 2030)</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Centre LSD</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>UNESCO Science Report: Towards 2030, Global Overview</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="n">
+        <v>2015</v>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Avenyo, Chien, Hollanders, Marins, Schaaper, Verspagen</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Book chapter</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
         <is>
-          <t>02 Transition minerals &amp; value chains</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H80" s="15" t="inlineStr"/>
       <c r="I80" s="17" t="inlineStr">
         <is>
-          <t>https://centrelsd.org/news-and-updates/publications/solid-mineral-development-in-nigeria-evidence-from-ebonyi-ekiti-and-taraba-states</t>
+          <t>https://unesdoc.unesco.org/ark:/48223/pf0000235446</t>
         </is>
       </c>
       <c r="J80" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/solid-mineral-development-in-nigeria-evidence-from-ebonyi-ekiti-and</t>
+          <t>https://rita-woad.vercel.app/research/publications/unesco-science-report-towards-2030-ch-2-tracking-trends-in-innovation</t>
         </is>
       </c>
       <c r="K80" s="16" t="inlineStr"/>
-      <c r="L80" s="16" t="inlineStr"/>
+      <c r="L80" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M80" s="16" t="inlineStr"/>
       <c r="N80" s="16" t="inlineStr"/>
       <c r="O80" s="16" t="inlineStr"/>
@@ -8367,7 +8883,7 @@
       <c r="T80" s="16" t="inlineStr"/>
       <c r="U80" s="16" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V80" s="16" t="inlineStr"/>
@@ -8378,12 +8894,12 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Taking stock of Africa’s economic transformation: rethinking sources of productivity growth</t>
+          <t>Contribution (JRC111430)</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>World Bank Research Observer (forthcoming)</t>
+          <t>European Commission Joint Research Centre</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
@@ -8393,12 +8909,12 @@
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, McMillan, Gollin, Owusu, Mensah</t>
+          <t>Ndubuisi</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="G81" s="15" t="inlineStr">
@@ -8407,14 +8923,14 @@
         </is>
       </c>
       <c r="H81" s="15" t="inlineStr"/>
-      <c r="I81" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC111430</t>
         </is>
       </c>
       <c r="J81" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/taking-stock-of-africas-economic-transformation-rethinking-sources-of</t>
+          <t>https://rita-woad.vercel.app/research/publications/contribution-jrc111430</t>
         </is>
       </c>
       <c r="K81" s="16" t="inlineStr"/>
@@ -8427,11 +8943,7 @@
       <c r="R81" s="16" t="inlineStr"/>
       <c r="S81" s="16" t="inlineStr"/>
       <c r="T81" s="16" t="inlineStr"/>
-      <c r="U81" s="16" t="inlineStr">
-        <is>
-          <t>Africa-wide</t>
-        </is>
-      </c>
+      <c r="U81" s="16" t="inlineStr"/>
       <c r="V81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
@@ -8440,12 +8952,12 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Trust and R&amp;D investment: evidence from OECD countries</t>
+          <t>Solid mineral development in Nigeria: evidence from Ebonyi, Ekiti and Taraba states</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Journal of Institutional Economics 16(6)</t>
+          <t>Centre LSD</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
@@ -8460,27 +8972,31 @@
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
-          <t>04 Innovation, firms &amp; work</t>
+          <t>02 Transition minerals &amp; value chains</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr"/>
-      <c r="I82" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>https://centrelsd.org/news-and-updates/publications/solid-mineral-development-in-nigeria-evidence-from-ebonyi-ekiti-and-taraba-states</t>
         </is>
       </c>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/trust-and-r-and-d-investment-evidence-from-oecd-countries</t>
+          <t>https://rita-woad.vercel.app/research/publications/solid-mineral-development-in-nigeria-evidence-from-ebonyi-ekiti-and</t>
         </is>
       </c>
       <c r="K82" s="16" t="inlineStr"/>
-      <c r="L82" s="16" t="inlineStr"/>
+      <c r="L82" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M82" s="16" t="inlineStr"/>
       <c r="N82" s="16" t="inlineStr"/>
       <c r="O82" s="16" t="inlineStr"/>
@@ -8491,7 +9007,7 @@
       <c r="T82" s="16" t="inlineStr"/>
       <c r="U82" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="V82" s="16" t="inlineStr"/>
@@ -8502,20 +9018,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Coherency and predictability between stocks of AI and energy corporations</t>
+          <t>PGP for portfolio optimization: application to ESG index family</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Financial Innovation 10:128</t>
+          <t>Annals of Operations Research 347(1), 405–417</t>
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Mzoughi, Guesmi</t>
+          <t>Abid, Urom, Peillex, Karmani, Ndubuisi</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
@@ -8533,20 +9049,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I83" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/a/spr/annopr/v347y2025i1d10.1007_s10479-023-05460-w.html</t>
         </is>
       </c>
       <c r="J83" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/coherency-and-predictability-between-stocks-of-ai-and-energy</t>
+          <t>https://rita-woad.vercel.app/research/publications/pgp-for-portfolio-optimization-esg-index-family</t>
         </is>
       </c>
       <c r="K83" s="16" t="inlineStr"/>
-      <c r="L83" s="16" t="inlineStr"/>
+      <c r="L83" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M83" s="16" t="inlineStr"/>
-      <c r="N83" s="16" t="inlineStr"/>
+      <c r="N83" s="16" t="inlineStr">
+        <is>
+          <t>Conventional portfolio design assumes Gaussian returns, but asymmetric and heavy-tailed returns call for higher-order moments. The paper proposes a mean-variance-skewness-kurtosis model, optimised with parametrised polynomial goal programming (PGP), to build diversified portfolios.</t>
+        </is>
+      </c>
       <c r="O83" s="16" t="inlineStr"/>
       <c r="P83" s="16" t="inlineStr"/>
       <c r="Q83" s="16" t="inlineStr"/>
@@ -8566,12 +9090,12 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Dependence of green energy markets on big data and other 4IR technologies</t>
+          <t>Dependence of green energy markets on big data and other fourth industrial revolution technologies</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Journal of International Financial Markets, Institutions &amp; Money 96</t>
+          <t>Journal of International Financial Markets, Institutions &amp; Money 96, 102061</t>
         </is>
       </c>
       <c r="D84" s="15" t="n">
@@ -8579,7 +9103,7 @@
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Benkraiem, Guesmi, Urom, Vigne</t>
+          <t>Benkraiem, Guesmi, Ndubuisi, Urom, Vigne</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -8608,9 +9132,17 @@
         </is>
       </c>
       <c r="K84" s="16" t="inlineStr"/>
-      <c r="L84" s="16" t="inlineStr"/>
+      <c r="L84" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M84" s="16" t="inlineStr"/>
-      <c r="N84" s="16" t="inlineStr"/>
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>The paper analyses dependence and connectedness between fourth industrial revolution technology markets (big data and artificial intelligence, blockchain, financial technology) and global and regional green energy markets, and the roles of market and macroeconomic factors in shock propagation.</t>
+        </is>
+      </c>
       <c r="O84" s="16" t="inlineStr"/>
       <c r="P84" s="16" t="inlineStr"/>
       <c r="Q84" s="16" t="inlineStr"/>
@@ -8630,12 +9162,12 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Global macroeconomic factors and connectedness among NFTs and (un)conventional assets</t>
+          <t>Exploring the coherency and predictability between the stocks of artificial intelligence and energy corporations</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Research in International Business &amp; Finance 71</t>
+          <t>Financial Innovation 10(1), 128</t>
         </is>
       </c>
       <c r="D85" s="15" t="n">
@@ -8643,7 +9175,7 @@
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom</t>
+          <t>Urom, Ndubuisi, Mzoughi, Guesmi</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
@@ -8661,20 +9193,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s40854-024-00609-3</t>
         </is>
       </c>
       <c r="J85" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/global-macroeconomic-factors-and-connectedness-among-nfts-and-un</t>
+          <t>https://rita-woad.vercel.app/research/publications/coherency-and-predictability-between-stocks-of-ai-and-energy</t>
         </is>
       </c>
       <c r="K85" s="16" t="inlineStr"/>
-      <c r="L85" s="16" t="inlineStr"/>
+      <c r="L85" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M85" s="16" t="inlineStr"/>
-      <c r="N85" s="16" t="inlineStr"/>
+      <c r="N85" s="16" t="inlineStr">
+        <is>
+          <t>The paper studies links between artificial intelligence investments and eight energy-focused sectors. It finds significant dependence and connectedness, especially over intermediate and long-term investment horizons, and a relationship that has grown stronger since the COVID-19 pandemic.</t>
+        </is>
+      </c>
       <c r="O85" s="16" t="inlineStr"/>
       <c r="P85" s="16" t="inlineStr"/>
       <c r="Q85" s="16" t="inlineStr"/>
@@ -8694,20 +9234,20 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Clean cryptocurrencies and media environmental attention</t>
+          <t>Global macroeconomic factors and the connectedness among NFTs and (un)conventional assets</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Research in International Business &amp; Finance 65</t>
+          <t>Research in International Business and Finance 71, 102429</t>
         </is>
       </c>
       <c r="D86" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom</t>
+          <t>Urom, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -8725,20 +9265,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/a/eee/riibaf/v71y2024ics0275531924002228.html</t>
         </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/clean-cryptocurrencies-and-media-environmental-attention</t>
+          <t>https://rita-woad.vercel.app/research/publications/global-macroeconomic-factors-and-connectedness-among-nfts-and-un</t>
         </is>
       </c>
       <c r="K86" s="16" t="inlineStr"/>
-      <c r="L86" s="16" t="inlineStr"/>
+      <c r="L86" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M86" s="16" t="inlineStr"/>
-      <c r="N86" s="16" t="inlineStr"/>
+      <c r="N86" s="16" t="inlineStr">
+        <is>
+          <t>The paper measures how returns and volatility move between NFTs and conventional and unconventional assets under different market conditions, and tests whether global macroeconomic and geopolitical indicators predict that connectedness.</t>
+        </is>
+      </c>
       <c r="O86" s="16" t="inlineStr"/>
       <c r="P86" s="16" t="inlineStr"/>
       <c r="Q86" s="16" t="inlineStr"/>
@@ -8758,12 +9306,12 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Geopolitical risks, global market factors and dependence among regional sustainable investments and commodities</t>
+          <t>Dependence and risk spillovers among clean cryptocurrencies prices and media environmental attention</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Quarterly Review of Economics and Finance 91</t>
+          <t>Research in International Business and Finance 65, 101953</t>
         </is>
       </c>
       <c r="D87" s="15" t="n">
@@ -8789,20 +9337,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I87" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.ribaf.2023.101953</t>
         </is>
       </c>
       <c r="J87" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/geopolitical-risks-global-market-factors-and-dependence-among-regional</t>
+          <t>https://rita-woad.vercel.app/research/publications/clean-cryptocurrencies-and-media-environmental-attention</t>
         </is>
       </c>
       <c r="K87" s="16" t="inlineStr"/>
-      <c r="L87" s="16" t="inlineStr"/>
+      <c r="L87" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M87" s="16" t="inlineStr"/>
-      <c r="N87" s="16" t="inlineStr"/>
+      <c r="N87" s="16" t="inlineStr">
+        <is>
+          <t>The study examines the link between media attention to cryptocurrencies' environmental impact and the prices of clean cryptocurrencies. It finds strong connectedness, implying that clean cryptocurrency prices are influenced by attention on cryptocurrency sustainability.</t>
+        </is>
+      </c>
       <c r="O87" s="16" t="inlineStr"/>
       <c r="P87" s="16" t="inlineStr"/>
       <c r="Q87" s="16" t="inlineStr"/>
@@ -8822,12 +9378,12 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>PGP for portfolio optimization: ESG index family</t>
+          <t>Geopolitical risks, global market factors and dependence among regional sustainable investments and commodities</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Annals of Operations Research</t>
+          <t>Quarterly Review of Economics and Finance 91, 94–111</t>
         </is>
       </c>
       <c r="D88" s="15" t="n">
@@ -8835,7 +9391,7 @@
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Abid, Urom, Peillex, Karmani</t>
+          <t>Urom, Ndubuisi</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -8853,20 +9409,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I88" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.qref.2023.07.007</t>
         </is>
       </c>
       <c r="J88" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/pgp-for-portfolio-optimization-esg-index-family</t>
+          <t>https://rita-woad.vercel.app/research/publications/geopolitical-risks-global-market-factors-and-dependence-among-regional</t>
         </is>
       </c>
       <c r="K88" s="16" t="inlineStr"/>
-      <c r="L88" s="16" t="inlineStr"/>
+      <c r="L88" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M88" s="16" t="inlineStr"/>
-      <c r="N88" s="16" t="inlineStr"/>
+      <c r="N88" s="16" t="inlineStr">
+        <is>
+          <t>The paper studies how sustainable investment indices for North America, Europe and Asia-Pacific connect with energy, precious metal and industrial metal commodities. It finds asymmetric connectedness, significantly stronger during extreme downside and upside market conditions.</t>
+        </is>
+      </c>
       <c r="O88" s="16" t="inlineStr"/>
       <c r="P88" s="16" t="inlineStr"/>
       <c r="Q88" s="16" t="inlineStr"/>
@@ -8886,20 +9450,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Clean energy sectors and oil price uncertainty</t>
+          <t>Global commodity and equity markets spillovers to Africa during the COVID-19 pandemic</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Quarterly Review of Economics and Finance 85</t>
+          <t>Emerging Markets Review 55, 100948</t>
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Mzoughi, Guesmi</t>
+          <t>Urom, Ndubuisi, Del Lo, Yuni</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
@@ -8917,20 +9481,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/a/eee/ememar/v55y2023ics1566014122000656.html</t>
         </is>
       </c>
       <c r="J89" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/clean-energy-sectors-and-oil-price-uncertainty</t>
+          <t>https://rita-woad.vercel.app/research/publications/global-commodity-and-equity-spillovers-to-africa-during-covid-19</t>
         </is>
       </c>
       <c r="K89" s="16" t="inlineStr"/>
-      <c r="L89" s="16" t="inlineStr"/>
+      <c r="L89" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M89" s="16" t="inlineStr"/>
-      <c r="N89" s="16" t="inlineStr"/>
+      <c r="N89" s="16" t="inlineStr">
+        <is>
+          <t>The study examines connectedness between 12 African equity markets and global commodity and developed equity markets, with a focus on the peak of the COVID-19 pandemic.</t>
+        </is>
+      </c>
       <c r="O89" s="16" t="inlineStr"/>
       <c r="P89" s="16" t="inlineStr"/>
       <c r="Q89" s="16" t="inlineStr"/>
@@ -8939,7 +9511,7 @@
       <c r="T89" s="16" t="inlineStr"/>
       <c r="U89" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V89" s="16" t="inlineStr"/>
@@ -8950,12 +9522,12 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Economic sentiment and climate transition during COVID-19</t>
+          <t>Directional predictability and time-frequency spillovers among clean energy sectors and oil price uncertainty</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Financial Market Dynamics (book chapter)</t>
+          <t>Quarterly Review of Economics and Finance 85, 326–341</t>
         </is>
       </c>
       <c r="D90" s="15" t="n">
@@ -8963,12 +9535,12 @@
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Yuni, Tingum</t>
+          <t>Urom, Mzoughi, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>Book chapter</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -8981,20 +9553,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I90" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/a/eee/quaeco/v85y2022icp326-341.html</t>
         </is>
       </c>
       <c r="J90" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/economic-sentiment-and-climate-transition-during-covid-19</t>
+          <t>https://rita-woad.vercel.app/research/publications/clean-energy-sectors-and-oil-price-uncertainty</t>
         </is>
       </c>
       <c r="K90" s="16" t="inlineStr"/>
-      <c r="L90" s="16" t="inlineStr"/>
+      <c r="L90" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M90" s="16" t="inlineStr"/>
-      <c r="N90" s="16" t="inlineStr"/>
+      <c r="N90" s="16" t="inlineStr">
+        <is>
+          <t>The paper analyses the dependence between clean energy sectors and oil price uncertainty. Sector responses differ in direction and size depending on the sector, market conditions and investment horizon.</t>
+        </is>
+      </c>
       <c r="O90" s="16" t="inlineStr"/>
       <c r="P90" s="16" t="inlineStr"/>
       <c r="Q90" s="16" t="inlineStr"/>
@@ -9014,12 +9594,12 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Energy-focused sectors and artificial intelligence</t>
+          <t>Dynamic dependence and predictability between volume and return of non-fungible tokens (NFTs): the roles of market factors and geopolitical risks</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Technological Forecasting &amp; Social Change 183</t>
+          <t>Finance Research Letters 50, 103188</t>
         </is>
       </c>
       <c r="D91" s="15" t="n">
@@ -9027,7 +9607,7 @@
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Guesmi, Benkraiem</t>
+          <t>Urom, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
@@ -9045,20 +9625,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I91" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.frl.2022.103188</t>
         </is>
       </c>
       <c r="J91" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/energy-focused-sectors-and-artificial-intelligence</t>
+          <t>https://rita-woad.vercel.app/research/publications/nft-volume-and-returns</t>
         </is>
       </c>
       <c r="K91" s="16" t="inlineStr"/>
-      <c r="L91" s="16" t="inlineStr"/>
+      <c r="L91" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M91" s="16" t="inlineStr"/>
-      <c r="N91" s="16" t="inlineStr"/>
+      <c r="N91" s="16" t="inlineStr">
+        <is>
+          <t>The paper studies the volume–return relationship for the overall NFT market and three sub-markets (Cryptokitties, Cryptopunks and Decentraland). It finds significant dependence between NFT return and volume, weakest for Cryptopunks.</t>
+        </is>
+      </c>
       <c r="O91" s="16" t="inlineStr"/>
       <c r="P91" s="16" t="inlineStr"/>
       <c r="Q91" s="16" t="inlineStr"/>
@@ -9078,12 +9666,12 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Financial and commodity market volatility and real activity</t>
+          <t>Dynamic dependence between clean investments and economic policy uncertainty</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Finance Research Letters</t>
+          <t>UNU-MERIT Working Paper 2022-027</t>
         </is>
       </c>
       <c r="D92" s="15" t="n">
@@ -9091,12 +9679,12 @@
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Guesmi</t>
+          <t>Urom, Mzoughi, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -9109,20 +9697,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>https://merit.unu.edu/publications/working-papers/abstract/?id=9378</t>
         </is>
       </c>
       <c r="J92" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/financial-and-commodity-market-volatility-and-real-activity</t>
+          <t>https://rita-woad.vercel.app/research/publications/clean-investments-and-economic-policy-uncertainty</t>
         </is>
       </c>
       <c r="K92" s="16" t="inlineStr"/>
-      <c r="L92" s="16" t="inlineStr"/>
+      <c r="L92" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M92" s="16" t="inlineStr"/>
-      <c r="N92" s="16" t="inlineStr"/>
+      <c r="N92" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines how clean investments across sectors respond to economic policy uncertainty, using the NASDAQ OMX Green Economy sectoral indexes. Dependence and predictability vary across market conditions and horizons, so the diversification benefits of clean energy stocks depend on sector, market conditions and horizon.</t>
+        </is>
+      </c>
       <c r="O92" s="16" t="inlineStr"/>
       <c r="P92" s="16" t="inlineStr"/>
       <c r="Q92" s="16" t="inlineStr"/>
@@ -9142,12 +9738,12 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Global commodity and equity spillovers to Africa during COVID-19</t>
+          <t>Economic sentiment and climate transition during the COVID-19 pandemic</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Emerging Markets Review</t>
+          <t>In Goutte, Guesmi and Urom (eds), Financial Market Dynamics after COVID 19, Springer, ch. 8</t>
         </is>
       </c>
       <c r="D93" s="15" t="n">
@@ -9155,12 +9751,12 @@
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Del Lo, Yuni</t>
+          <t>Ndubuisi, Yuni, Tingum</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Book chapter</t>
         </is>
       </c>
       <c r="G93" s="15" t="inlineStr">
@@ -9173,20 +9769,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>https://www.springerprofessional.de/en/economic-sentiment-and-climate-transition-during-the-covid-19-pa/20350390</t>
         </is>
       </c>
       <c r="J93" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/global-commodity-and-equity-spillovers-to-africa-during-covid-19</t>
+          <t>https://rita-woad.vercel.app/research/publications/economic-sentiment-and-climate-transition-during-covid-19</t>
         </is>
       </c>
       <c r="K93" s="16" t="inlineStr"/>
-      <c r="L93" s="16" t="inlineStr"/>
+      <c r="L93" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M93" s="16" t="inlineStr"/>
-      <c r="N93" s="16" t="inlineStr"/>
+      <c r="N93" s="16" t="inlineStr">
+        <is>
+          <t>The chapter examines how a newspaper-based US economic sentiment index relates to four climate-themed financial indices after COVID-19 began. Dependence varies across time horizons and market conditions.</t>
+        </is>
+      </c>
       <c r="O93" s="16" t="inlineStr"/>
       <c r="P93" s="16" t="inlineStr"/>
       <c r="Q93" s="16" t="inlineStr"/>
@@ -9206,12 +9810,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>NFT volume and returns</t>
+          <t>How do financial and commodity markets volatility react to real economic activity?</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Finance Research Letters 50</t>
+          <t>Finance Research Letters 47(B), 102733</t>
         </is>
       </c>
       <c r="D94" s="15" t="n">
@@ -9219,7 +9823,7 @@
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Guesmi</t>
+          <t>Urom, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -9237,20 +9841,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/a/eee/finlet/v47y2022ipbs1544612322000563.html</t>
         </is>
       </c>
       <c r="J94" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/nft-volume-and-returns</t>
+          <t>https://rita-woad.vercel.app/research/publications/financial-and-commodity-market-volatility-and-real-activity</t>
         </is>
       </c>
       <c r="K94" s="16" t="inlineStr"/>
-      <c r="L94" s="16" t="inlineStr"/>
+      <c r="L94" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M94" s="16" t="inlineStr"/>
-      <c r="N94" s="16" t="inlineStr"/>
+      <c r="N94" s="16" t="inlineStr">
+        <is>
+          <t>The paper tests lead-lag links and integration between real economic activity and financial and commodity market volatility. Real activity shocks co-move with these markets, but the markets led that co-movement during downturns such as the COVID-19 pandemic.</t>
+        </is>
+      </c>
       <c r="O94" s="16" t="inlineStr"/>
       <c r="P94" s="16" t="inlineStr"/>
       <c r="Q94" s="16" t="inlineStr"/>
@@ -9270,20 +9882,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Global, regional and national mortality among young people aged 10–24 years, 1950–2019 (GBD 2019)</t>
+          <t>Quantile co-movement and dependence between energy-focused sectors and artificial intelligence</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>The Lancet 398</t>
+          <t>Technological Forecasting and Social Change 183, 121842</t>
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>Ward, et al., Avenyo</t>
+          <t>Urom, Ndubuisi, Guesmi, Benkraien</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
@@ -9293,28 +9905,36 @@
       </c>
       <c r="G95" s="15" t="inlineStr">
         <is>
+          <t>01 Green industrialisation &amp; policy</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
           <t>Archive</t>
         </is>
       </c>
-      <c r="H95" s="15" t="inlineStr">
-        <is>
-          <t>Archive</t>
-        </is>
-      </c>
       <c r="I95" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0140673621015464</t>
+          <t>https://doi.org/10.1016/j.techfore.2022.121842</t>
         </is>
       </c>
       <c r="J95" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/global-regional-and-national-mortality-among-young-people-aged-10-24</t>
+          <t>https://rita-woad.vercel.app/research/publications/energy-focused-sectors-and-artificial-intelligence</t>
         </is>
       </c>
       <c r="K95" s="16" t="inlineStr"/>
-      <c r="L95" s="16" t="inlineStr"/>
+      <c r="L95" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M95" s="16" t="inlineStr"/>
-      <c r="N95" s="16" t="inlineStr"/>
+      <c r="N95" s="16" t="inlineStr">
+        <is>
+          <t>The paper studies links between artificial intelligence and eight energy-focused sectors. The performance of energy-focused corporations, especially in renewable energy, depends strongly on the performance of AI.</t>
+        </is>
+      </c>
       <c r="O95" s="16" t="inlineStr"/>
       <c r="P95" s="16" t="inlineStr"/>
       <c r="Q95" s="16" t="inlineStr"/>
@@ -9334,12 +9954,12 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Implied volatility indexes</t>
+          <t>Economic activity, and financial and commodity markets’ shocks: an analysis of implied volatility indexes</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>International Economics 165</t>
+          <t>International Economics 165, 51–66</t>
         </is>
       </c>
       <c r="D96" s="15" t="n">
@@ -9347,7 +9967,7 @@
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Ozor</t>
+          <t>Urom, Ndubuisi, Ozor</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -9365,9 +9985,9 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/a/eee/inteco/v165y2021icp51-66.html</t>
         </is>
       </c>
       <c r="J96" s="17" t="inlineStr">
@@ -9376,9 +9996,17 @@
         </is>
       </c>
       <c r="K96" s="16" t="inlineStr"/>
-      <c r="L96" s="16" t="inlineStr"/>
+      <c r="L96" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M96" s="16" t="inlineStr"/>
-      <c r="N96" s="16" t="inlineStr"/>
+      <c r="N96" s="16" t="inlineStr">
+        <is>
+          <t>The paper examines short- and long-run asymmetric interactions and causality between real economic activity and volatility shocks in stock, energy and gold markets. The relationships are asymmetric at both horizons.</t>
+        </is>
+      </c>
       <c r="O96" s="16" t="inlineStr"/>
       <c r="P96" s="16" t="inlineStr"/>
       <c r="Q96" s="16" t="inlineStr"/>
@@ -9398,32 +10026,30 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Clean investments and economic policy uncertainty</t>
+          <t>Global, regional, and national mortality among young people aged 10–24 years, 1950–2019: a systematic analysis for the Global Burden of Disease Study 2019</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>UNU-MERIT Working Paper</t>
-        </is>
-      </c>
-      <c r="D97" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>The Lancet 398(10311), 1593–1618</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="n">
+        <v>2021</v>
       </c>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom, Guesmi, Mzoughi</t>
+          <t>GBD 2019 Adolescent Mortality Collaborators</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="H97" s="15" t="inlineStr">
@@ -9431,20 +10057,28 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I97" s="17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/S0140-6736(21)01546-4</t>
         </is>
       </c>
       <c r="J97" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/clean-investments-and-economic-policy-uncertainty</t>
+          <t>https://rita-woad.vercel.app/research/publications/global-regional-and-national-mortality-among-young-people-aged-10-24</t>
         </is>
       </c>
       <c r="K97" s="16" t="inlineStr"/>
-      <c r="L97" s="16" t="inlineStr"/>
+      <c r="L97" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M97" s="16" t="inlineStr"/>
-      <c r="N97" s="16" t="inlineStr"/>
+      <c r="N97" s="16" t="inlineStr">
+        <is>
+          <t>Using GBD 2019 estimates, the study examines deaths and mortality rates among 10–24-year-olds in 204 countries and territories from 1950 to 2019. Variation in adolescent mortality between countries and by sex is widening.</t>
+        </is>
+      </c>
       <c r="O97" s="16" t="inlineStr"/>
       <c r="P97" s="16" t="inlineStr"/>
       <c r="Q97" s="16" t="inlineStr"/>
@@ -9464,7 +10098,7 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>The past and the present: the Nigerian Ebola experience and COVID-19</t>
+          <t>The past and the present: the Nigerian Ebola experience and the Covid-19 pandemic</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -9479,7 +10113,7 @@
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Konte, Ndubuisi, Okafor</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -9497,9 +10131,9 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>https://includeplatform.net/publications/the-past-and-the-present-the-nigerian-ebola-experience-and-the-covid-19-pandemic-2/</t>
         </is>
       </c>
       <c r="J98" s="17" t="inlineStr">
@@ -9508,9 +10142,17 @@
         </is>
       </c>
       <c r="K98" s="16" t="inlineStr"/>
-      <c r="L98" s="16" t="inlineStr"/>
+      <c r="L98" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M98" s="16" t="inlineStr"/>
-      <c r="N98" s="16" t="inlineStr"/>
+      <c r="N98" s="16" t="inlineStr">
+        <is>
+          <t>The paper compares Nigeria's success against Ebola with its country-wide response to COVID-19, and assesses which factors may have prevented the country from repeating that success.</t>
+        </is>
+      </c>
       <c r="O98" s="16" t="inlineStr"/>
       <c r="P98" s="16" t="inlineStr"/>
       <c r="Q98" s="16" t="inlineStr"/>
@@ -9568,130 +10210,164 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11475,7 +12151,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>The Argument</t>
+          <t>African Arguments</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -11493,9 +12169,9 @@
           <t>Ndubuisi, Avenyo</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>https://africanarguments.org/?p=48463</t>
         </is>
       </c>
       <c r="G4" s="16" t="inlineStr"/>
@@ -12393,25 +13069,26 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12619,7 +13296,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Jobs, investments and exporting: the real effects of electricity crises in South Africa | Dancing on the grid: electricity crises, manufacturing energy vulnerability and jobs in South Africa</t>
+          <t>Jobs, investments, and exporting: the real effects of electricity crisis in South Africa | Dancing on the grid: Electricity crises, energy vulnerability, and manufacturing jobs in South Africa</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr"/>

--- a/docs/content-input/RITA-website-content-to-fill.xlsx
+++ b/docs/content-input/RITA-website-content-to-fill.xlsx
@@ -20,8 +20,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1 Institute &amp; legal'!$A$2:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 People'!$A$2:$D$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3 Publications'!$A$2:$V$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 People'!$A$2:$D$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3 Publications'!$A$2:$V$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4 Policy Insights'!$A$2:$L$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5 Op-eds &amp; blogs'!$A$2:$K$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6 Policy briefs'!$A$2:$M$9</definedName>
@@ -2615,7 +2615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3166,7 +3166,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>Fellows, associates and staff to list (only with their written consent)</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B32" s="14" t="n"/>
@@ -3176,17 +3176,17 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Solomon Owusu</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Short bio (about 60 words)</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr"/>
@@ -3194,17 +3194,17 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Woubet Kassa</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Long bio (about 150 words): confirm or correct the current one</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>Marcel Kempers curates and runs the RITA website. His research looks at e-mobility and informal transport work in African cities, including electric motorcycle taxis (boda bodas) in Nairobi. MSc, Delft University of Technology.</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr"/>
@@ -3212,17 +3212,17 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Emmanuel B. Mensah</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Role title</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>Curator &amp; website lead</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr"/>
@@ -3230,17 +3230,17 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Rexford Asiamah</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Base (city)</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr"/>
@@ -3248,17 +3248,17 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Christian Urom</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Email to show on profile</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr"/>
@@ -3266,17 +3266,17 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Maty Konte</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>LinkedIn URL</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr"/>
@@ -3284,17 +3284,17 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>Fiona Tregenna</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Google Scholar URL</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr"/>
@@ -3302,17 +3302,17 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Antonio Andreoni</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>ORCID iD</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr"/>
@@ -3320,17 +3320,17 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Shingie Chisoro</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Personal website</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr"/>
@@ -3338,17 +3338,17 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Jason Bell</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Focus tags (5 keywords)</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>E-mobility · Boda bodas · Nairobi · Informal work · Transport</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr"/>
@@ -3356,17 +3356,17 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>Julius Nyamwena</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Topics for media comment</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr"/>
@@ -3374,17 +3374,17 @@
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Keyi Tang</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Awards (confirm)</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr"/>
@@ -3392,55 +3392,299 @@
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>Xiaolan Fu</t>
+          <t>Marcel Kempers</t>
         </is>
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
+          <t>Portrait photo sent? (4:5, at least 1600×2000 px, with photo release)</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Frequent co-author (not listed on the site)</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Erika Kraemer-Mbula</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>Invite as associate? (Yes / No) + role, email</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Frequent co-author (not listed on the site)</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr"/>
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>Fellows, associates and staff to list (only with their written consent)</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
+          <t>Solomon Owusu</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Woubet Kassa</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>Emmanuel B. Mensah</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>Rexford Asiamah</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Christian Urom</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Maty Konte</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Fiona Tregenna</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Antonio Andreoni</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Shingie Chisoro</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>Jason Bell</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Julius Nyamwena</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>Keyi Tang</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>Xiaolan Fu</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>Erika Kraemer-Mbula</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Invite as associate? (Yes / No) + role, email</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>Frequent co-author (not listed on the site)</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
           <t>(Add any other person)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>Name, group (fellow / associate / staff), role, base, email</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr"/>
-      <c r="D47" s="16" t="inlineStr"/>
+      <c r="C61" s="15" t="inlineStr"/>
+      <c r="D61" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D47"/>
+  <autoFilter ref="A2:D61"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3458,7 +3702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3488,7 +3732,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>All 95 publications in the research library. Start with rows marked "Flagship". "In brief" is prefilled where we already had text: correct it if needed. Archive items are hidden by default on the site.</t>
+          <t>All 96 publications in the research library. Start with rows marked "Flagship". "In brief" is prefilled where we already had text: correct it if needed. Archive items are hidden by default on the site.</t>
         </is>
       </c>
     </row>
@@ -8894,12 +9138,12 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Contribution (JRC111430)</t>
+          <t>Being a boda isn’t easy</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>European Commission Joint Research Centre</t>
+          <t>Delft University of Technology, MSc thesis</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
@@ -8909,32 +9153,36 @@
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi</t>
+          <t>Kempers</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>thesis</t>
         </is>
       </c>
       <c r="G81" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
+          <t>04 Innovation, firms &amp; work</t>
         </is>
       </c>
       <c r="H81" s="15" t="inlineStr"/>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC111430</t>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>TBC</t>
         </is>
       </c>
       <c r="J81" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/contribution-jrc111430</t>
+          <t>https://rita-woad.vercel.app/research/publications/being-a-boda-isnt-easy</t>
         </is>
       </c>
       <c r="K81" s="16" t="inlineStr"/>
-      <c r="L81" s="16" t="inlineStr"/>
+      <c r="L81" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M81" s="16" t="inlineStr"/>
       <c r="N81" s="16" t="inlineStr"/>
       <c r="O81" s="16" t="inlineStr"/>
@@ -8943,7 +9191,11 @@
       <c r="R81" s="16" t="inlineStr"/>
       <c r="S81" s="16" t="inlineStr"/>
       <c r="T81" s="16" t="inlineStr"/>
-      <c r="U81" s="16" t="inlineStr"/>
+      <c r="U81" s="16" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
       <c r="V81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
@@ -8952,12 +9204,12 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Solid mineral development in Nigeria: evidence from Ebonyi, Ekiti and Taraba states</t>
+          <t>Contribution (JRC111430)</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Centre LSD</t>
+          <t>European Commission Joint Research Centre</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
@@ -8977,26 +9229,22 @@
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
-          <t>02 Transition minerals &amp; value chains</t>
+          <t>01 Green industrialisation &amp; policy</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr"/>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>https://centrelsd.org/news-and-updates/publications/solid-mineral-development-in-nigeria-evidence-from-ebonyi-ekiti-and-taraba-states</t>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC111430</t>
         </is>
       </c>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/solid-mineral-development-in-nigeria-evidence-from-ebonyi-ekiti-and</t>
+          <t>https://rita-woad.vercel.app/research/publications/contribution-jrc111430</t>
         </is>
       </c>
       <c r="K82" s="16" t="inlineStr"/>
-      <c r="L82" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="L82" s="16" t="inlineStr"/>
       <c r="M82" s="16" t="inlineStr"/>
       <c r="N82" s="16" t="inlineStr"/>
       <c r="O82" s="16" t="inlineStr"/>
@@ -9005,11 +9253,7 @@
       <c r="R82" s="16" t="inlineStr"/>
       <c r="S82" s="16" t="inlineStr"/>
       <c r="T82" s="16" t="inlineStr"/>
-      <c r="U82" s="16" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
+      <c r="U82" s="16" t="inlineStr"/>
       <c r="V82" s="16" t="inlineStr"/>
     </row>
     <row r="83">
@@ -9018,45 +9262,43 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>PGP for portfolio optimization: application to ESG index family</t>
+          <t>Solid mineral development in Nigeria: evidence from Ebonyi, Ekiti and Taraba states</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Annals of Operations Research 347(1), 405–417</t>
-        </is>
-      </c>
-      <c r="D83" s="15" t="n">
-        <v>2025</v>
+          <t>Centre LSD</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>Abid, Urom, Peillex, Karmani, Ndubuisi</t>
+          <t>Ndubuisi</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="G83" s="15" t="inlineStr">
         <is>
-          <t>01 Green industrialisation &amp; policy</t>
-        </is>
-      </c>
-      <c r="H83" s="15" t="inlineStr">
-        <is>
-          <t>Archive</t>
-        </is>
-      </c>
+          <t>02 Transition minerals &amp; value chains</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr"/>
       <c r="I83" s="17" t="inlineStr">
         <is>
-          <t>https://ideas.repec.org/a/spr/annopr/v347y2025i1d10.1007_s10479-023-05460-w.html</t>
+          <t>https://centrelsd.org/news-and-updates/publications/solid-mineral-development-in-nigeria-evidence-from-ebonyi-ekiti-and-taraba-states</t>
         </is>
       </c>
       <c r="J83" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/pgp-for-portfolio-optimization-esg-index-family</t>
+          <t>https://rita-woad.vercel.app/research/publications/solid-mineral-development-in-nigeria-evidence-from-ebonyi-ekiti-and</t>
         </is>
       </c>
       <c r="K83" s="16" t="inlineStr"/>
@@ -9066,11 +9308,7 @@
         </is>
       </c>
       <c r="M83" s="16" t="inlineStr"/>
-      <c r="N83" s="16" t="inlineStr">
-        <is>
-          <t>Conventional portfolio design assumes Gaussian returns, but asymmetric and heavy-tailed returns call for higher-order moments. The paper proposes a mean-variance-skewness-kurtosis model, optimised with parametrised polynomial goal programming (PGP), to build diversified portfolios.</t>
-        </is>
-      </c>
+      <c r="N83" s="16" t="inlineStr"/>
       <c r="O83" s="16" t="inlineStr"/>
       <c r="P83" s="16" t="inlineStr"/>
       <c r="Q83" s="16" t="inlineStr"/>
@@ -9079,7 +9317,7 @@
       <c r="T83" s="16" t="inlineStr"/>
       <c r="U83" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="V83" s="16" t="inlineStr"/>
@@ -9090,20 +9328,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Dependence of green energy markets on big data and other fourth industrial revolution technologies</t>
+          <t>PGP for portfolio optimization: application to ESG index family</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Journal of International Financial Markets, Institutions &amp; Money 96, 102061</t>
+          <t>Annals of Operations Research 347(1), 405–417</t>
         </is>
       </c>
       <c r="D84" s="15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Benkraiem, Guesmi, Ndubuisi, Urom, Vigne</t>
+          <t>Abid, Urom, Peillex, Karmani, Ndubuisi</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -9123,12 +9361,12 @@
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S1042443124001276</t>
+          <t>https://ideas.repec.org/a/spr/annopr/v347y2025i1d10.1007_s10479-023-05460-w.html</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/dependence-of-green-energy-markets-on-big-data-and-other-4ir</t>
+          <t>https://rita-woad.vercel.app/research/publications/pgp-for-portfolio-optimization-esg-index-family</t>
         </is>
       </c>
       <c r="K84" s="16" t="inlineStr"/>
@@ -9140,7 +9378,7 @@
       <c r="M84" s="16" t="inlineStr"/>
       <c r="N84" s="16" t="inlineStr">
         <is>
-          <t>The paper analyses dependence and connectedness between fourth industrial revolution technology markets (big data and artificial intelligence, blockchain, financial technology) and global and regional green energy markets, and the roles of market and macroeconomic factors in shock propagation.</t>
+          <t>Conventional portfolio design assumes Gaussian returns, but asymmetric and heavy-tailed returns call for higher-order moments. The paper proposes a mean-variance-skewness-kurtosis model, optimised with parametrised polynomial goal programming (PGP), to build diversified portfolios.</t>
         </is>
       </c>
       <c r="O84" s="16" t="inlineStr"/>
@@ -9162,12 +9400,12 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Exploring the coherency and predictability between the stocks of artificial intelligence and energy corporations</t>
+          <t>Dependence of green energy markets on big data and other fourth industrial revolution technologies</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Financial Innovation 10(1), 128</t>
+          <t>Journal of International Financial Markets, Institutions &amp; Money 96, 102061</t>
         </is>
       </c>
       <c r="D85" s="15" t="n">
@@ -9175,7 +9413,7 @@
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>Urom, Ndubuisi, Mzoughi, Guesmi</t>
+          <t>Benkraiem, Guesmi, Ndubuisi, Urom, Vigne</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
@@ -9195,12 +9433,12 @@
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s40854-024-00609-3</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S1042443124001276</t>
         </is>
       </c>
       <c r="J85" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/coherency-and-predictability-between-stocks-of-ai-and-energy</t>
+          <t>https://rita-woad.vercel.app/research/publications/dependence-of-green-energy-markets-on-big-data-and-other-4ir</t>
         </is>
       </c>
       <c r="K85" s="16" t="inlineStr"/>
@@ -9212,7 +9450,7 @@
       <c r="M85" s="16" t="inlineStr"/>
       <c r="N85" s="16" t="inlineStr">
         <is>
-          <t>The paper studies links between artificial intelligence investments and eight energy-focused sectors. It finds significant dependence and connectedness, especially over intermediate and long-term investment horizons, and a relationship that has grown stronger since the COVID-19 pandemic.</t>
+          <t>The paper analyses dependence and connectedness between fourth industrial revolution technology markets (big data and artificial intelligence, blockchain, financial technology) and global and regional green energy markets, and the roles of market and macroeconomic factors in shock propagation.</t>
         </is>
       </c>
       <c r="O85" s="16" t="inlineStr"/>
@@ -9234,12 +9472,12 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Global macroeconomic factors and the connectedness among NFTs and (un)conventional assets</t>
+          <t>Exploring the coherency and predictability between the stocks of artificial intelligence and energy corporations</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Research in International Business and Finance 71, 102429</t>
+          <t>Financial Innovation 10(1), 128</t>
         </is>
       </c>
       <c r="D86" s="15" t="n">
@@ -9247,7 +9485,7 @@
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Urom, Ndubuisi, Guesmi</t>
+          <t>Urom, Ndubuisi, Mzoughi, Guesmi</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -9267,12 +9505,12 @@
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>https://ideas.repec.org/a/eee/riibaf/v71y2024ics0275531924002228.html</t>
+          <t>https://doi.org/10.1186/s40854-024-00609-3</t>
         </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/global-macroeconomic-factors-and-connectedness-among-nfts-and-un</t>
+          <t>https://rita-woad.vercel.app/research/publications/coherency-and-predictability-between-stocks-of-ai-and-energy</t>
         </is>
       </c>
       <c r="K86" s="16" t="inlineStr"/>
@@ -9284,7 +9522,7 @@
       <c r="M86" s="16" t="inlineStr"/>
       <c r="N86" s="16" t="inlineStr">
         <is>
-          <t>The paper measures how returns and volatility move between NFTs and conventional and unconventional assets under different market conditions, and tests whether global macroeconomic and geopolitical indicators predict that connectedness.</t>
+          <t>The paper studies links between artificial intelligence investments and eight energy-focused sectors. It finds significant dependence and connectedness, especially over intermediate and long-term investment horizons, and a relationship that has grown stronger since the COVID-19 pandemic.</t>
         </is>
       </c>
       <c r="O86" s="16" t="inlineStr"/>
@@ -9306,20 +9544,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Dependence and risk spillovers among clean cryptocurrencies prices and media environmental attention</t>
+          <t>Global macroeconomic factors and the connectedness among NFTs and (un)conventional assets</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Research in International Business and Finance 65, 101953</t>
+          <t>Research in International Business and Finance 71, 102429</t>
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Urom</t>
+          <t>Urom, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F87" s="15" t="inlineStr">
@@ -9339,12 +9577,12 @@
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ribaf.2023.101953</t>
+          <t>https://ideas.repec.org/a/eee/riibaf/v71y2024ics0275531924002228.html</t>
         </is>
       </c>
       <c r="J87" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/clean-cryptocurrencies-and-media-environmental-attention</t>
+          <t>https://rita-woad.vercel.app/research/publications/global-macroeconomic-factors-and-connectedness-among-nfts-and-un</t>
         </is>
       </c>
       <c r="K87" s="16" t="inlineStr"/>
@@ -9356,7 +9594,7 @@
       <c r="M87" s="16" t="inlineStr"/>
       <c r="N87" s="16" t="inlineStr">
         <is>
-          <t>The study examines the link between media attention to cryptocurrencies' environmental impact and the prices of clean cryptocurrencies. It finds strong connectedness, implying that clean cryptocurrency prices are influenced by attention on cryptocurrency sustainability.</t>
+          <t>The paper measures how returns and volatility move between NFTs and conventional and unconventional assets under different market conditions, and tests whether global macroeconomic and geopolitical indicators predict that connectedness.</t>
         </is>
       </c>
       <c r="O87" s="16" t="inlineStr"/>
@@ -9378,12 +9616,12 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Geopolitical risks, global market factors and dependence among regional sustainable investments and commodities</t>
+          <t>Dependence and risk spillovers among clean cryptocurrencies prices and media environmental attention</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Quarterly Review of Economics and Finance 91, 94–111</t>
+          <t>Research in International Business and Finance 65, 101953</t>
         </is>
       </c>
       <c r="D88" s="15" t="n">
@@ -9391,7 +9629,7 @@
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Urom, Ndubuisi</t>
+          <t>Ndubuisi, Urom</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -9411,12 +9649,12 @@
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.qref.2023.07.007</t>
+          <t>https://doi.org/10.1016/j.ribaf.2023.101953</t>
         </is>
       </c>
       <c r="J88" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/geopolitical-risks-global-market-factors-and-dependence-among-regional</t>
+          <t>https://rita-woad.vercel.app/research/publications/clean-cryptocurrencies-and-media-environmental-attention</t>
         </is>
       </c>
       <c r="K88" s="16" t="inlineStr"/>
@@ -9428,7 +9666,7 @@
       <c r="M88" s="16" t="inlineStr"/>
       <c r="N88" s="16" t="inlineStr">
         <is>
-          <t>The paper studies how sustainable investment indices for North America, Europe and Asia-Pacific connect with energy, precious metal and industrial metal commodities. It finds asymmetric connectedness, significantly stronger during extreme downside and upside market conditions.</t>
+          <t>The study examines the link between media attention to cryptocurrencies' environmental impact and the prices of clean cryptocurrencies. It finds strong connectedness, implying that clean cryptocurrency prices are influenced by attention on cryptocurrency sustainability.</t>
         </is>
       </c>
       <c r="O88" s="16" t="inlineStr"/>
@@ -9450,12 +9688,12 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Global commodity and equity markets spillovers to Africa during the COVID-19 pandemic</t>
+          <t>Geopolitical risks, global market factors and dependence among regional sustainable investments and commodities</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Emerging Markets Review 55, 100948</t>
+          <t>Quarterly Review of Economics and Finance 91, 94–111</t>
         </is>
       </c>
       <c r="D89" s="15" t="n">
@@ -9463,7 +9701,7 @@
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>Urom, Ndubuisi, Del Lo, Yuni</t>
+          <t>Urom, Ndubuisi</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
@@ -9483,12 +9721,12 @@
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
-          <t>https://ideas.repec.org/a/eee/ememar/v55y2023ics1566014122000656.html</t>
+          <t>https://doi.org/10.1016/j.qref.2023.07.007</t>
         </is>
       </c>
       <c r="J89" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/global-commodity-and-equity-spillovers-to-africa-during-covid-19</t>
+          <t>https://rita-woad.vercel.app/research/publications/geopolitical-risks-global-market-factors-and-dependence-among-regional</t>
         </is>
       </c>
       <c r="K89" s="16" t="inlineStr"/>
@@ -9500,7 +9738,7 @@
       <c r="M89" s="16" t="inlineStr"/>
       <c r="N89" s="16" t="inlineStr">
         <is>
-          <t>The study examines connectedness between 12 African equity markets and global commodity and developed equity markets, with a focus on the peak of the COVID-19 pandemic.</t>
+          <t>The paper studies how sustainable investment indices for North America, Europe and Asia-Pacific connect with energy, precious metal and industrial metal commodities. It finds asymmetric connectedness, significantly stronger during extreme downside and upside market conditions.</t>
         </is>
       </c>
       <c r="O89" s="16" t="inlineStr"/>
@@ -9511,7 +9749,7 @@
       <c r="T89" s="16" t="inlineStr"/>
       <c r="U89" s="16" t="inlineStr">
         <is>
-          <t>Africa-wide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="V89" s="16" t="inlineStr"/>
@@ -9522,20 +9760,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Directional predictability and time-frequency spillovers among clean energy sectors and oil price uncertainty</t>
+          <t>Global commodity and equity markets spillovers to Africa during the COVID-19 pandemic</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Quarterly Review of Economics and Finance 85, 326–341</t>
+          <t>Emerging Markets Review 55, 100948</t>
         </is>
       </c>
       <c r="D90" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Urom, Mzoughi, Ndubuisi, Guesmi</t>
+          <t>Urom, Ndubuisi, Del Lo, Yuni</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -9555,12 +9793,12 @@
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
-          <t>https://ideas.repec.org/a/eee/quaeco/v85y2022icp326-341.html</t>
+          <t>https://ideas.repec.org/a/eee/ememar/v55y2023ics1566014122000656.html</t>
         </is>
       </c>
       <c r="J90" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/clean-energy-sectors-and-oil-price-uncertainty</t>
+          <t>https://rita-woad.vercel.app/research/publications/global-commodity-and-equity-spillovers-to-africa-during-covid-19</t>
         </is>
       </c>
       <c r="K90" s="16" t="inlineStr"/>
@@ -9572,7 +9810,7 @@
       <c r="M90" s="16" t="inlineStr"/>
       <c r="N90" s="16" t="inlineStr">
         <is>
-          <t>The paper analyses the dependence between clean energy sectors and oil price uncertainty. Sector responses differ in direction and size depending on the sector, market conditions and investment horizon.</t>
+          <t>The study examines connectedness between 12 African equity markets and global commodity and developed equity markets, with a focus on the peak of the COVID-19 pandemic.</t>
         </is>
       </c>
       <c r="O90" s="16" t="inlineStr"/>
@@ -9583,7 +9821,7 @@
       <c r="T90" s="16" t="inlineStr"/>
       <c r="U90" s="16" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Africa-wide</t>
         </is>
       </c>
       <c r="V90" s="16" t="inlineStr"/>
@@ -9594,12 +9832,12 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Dynamic dependence and predictability between volume and return of non-fungible tokens (NFTs): the roles of market factors and geopolitical risks</t>
+          <t>Directional predictability and time-frequency spillovers among clean energy sectors and oil price uncertainty</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Finance Research Letters 50, 103188</t>
+          <t>Quarterly Review of Economics and Finance 85, 326–341</t>
         </is>
       </c>
       <c r="D91" s="15" t="n">
@@ -9607,7 +9845,7 @@
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>Urom, Ndubuisi, Guesmi</t>
+          <t>Urom, Mzoughi, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
@@ -9627,12 +9865,12 @@
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.frl.2022.103188</t>
+          <t>https://ideas.repec.org/a/eee/quaeco/v85y2022icp326-341.html</t>
         </is>
       </c>
       <c r="J91" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/nft-volume-and-returns</t>
+          <t>https://rita-woad.vercel.app/research/publications/clean-energy-sectors-and-oil-price-uncertainty</t>
         </is>
       </c>
       <c r="K91" s="16" t="inlineStr"/>
@@ -9644,7 +9882,7 @@
       <c r="M91" s="16" t="inlineStr"/>
       <c r="N91" s="16" t="inlineStr">
         <is>
-          <t>The paper studies the volume–return relationship for the overall NFT market and three sub-markets (Cryptokitties, Cryptopunks and Decentraland). It finds significant dependence between NFT return and volume, weakest for Cryptopunks.</t>
+          <t>The paper analyses the dependence between clean energy sectors and oil price uncertainty. Sector responses differ in direction and size depending on the sector, market conditions and investment horizon.</t>
         </is>
       </c>
       <c r="O91" s="16" t="inlineStr"/>
@@ -9666,12 +9904,12 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Dynamic dependence between clean investments and economic policy uncertainty</t>
+          <t>Dynamic dependence and predictability between volume and return of non-fungible tokens (NFTs): the roles of market factors and geopolitical risks</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>UNU-MERIT Working Paper 2022-027</t>
+          <t>Finance Research Letters 50, 103188</t>
         </is>
       </c>
       <c r="D92" s="15" t="n">
@@ -9679,12 +9917,12 @@
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Urom, Mzoughi, Ndubuisi, Guesmi</t>
+          <t>Urom, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>Working paper</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -9699,12 +9937,12 @@
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
-          <t>https://merit.unu.edu/publications/working-papers/abstract/?id=9378</t>
+          <t>https://doi.org/10.1016/j.frl.2022.103188</t>
         </is>
       </c>
       <c r="J92" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/clean-investments-and-economic-policy-uncertainty</t>
+          <t>https://rita-woad.vercel.app/research/publications/nft-volume-and-returns</t>
         </is>
       </c>
       <c r="K92" s="16" t="inlineStr"/>
@@ -9716,7 +9954,7 @@
       <c r="M92" s="16" t="inlineStr"/>
       <c r="N92" s="16" t="inlineStr">
         <is>
-          <t>The paper examines how clean investments across sectors respond to economic policy uncertainty, using the NASDAQ OMX Green Economy sectoral indexes. Dependence and predictability vary across market conditions and horizons, so the diversification benefits of clean energy stocks depend on sector, market conditions and horizon.</t>
+          <t>The paper studies the volume–return relationship for the overall NFT market and three sub-markets (Cryptokitties, Cryptopunks and Decentraland). It finds significant dependence between NFT return and volume, weakest for Cryptopunks.</t>
         </is>
       </c>
       <c r="O92" s="16" t="inlineStr"/>
@@ -9738,12 +9976,12 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Economic sentiment and climate transition during the COVID-19 pandemic</t>
+          <t>Dynamic dependence between clean investments and economic policy uncertainty</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>In Goutte, Guesmi and Urom (eds), Financial Market Dynamics after COVID 19, Springer, ch. 8</t>
+          <t>UNU-MERIT Working Paper 2022-027</t>
         </is>
       </c>
       <c r="D93" s="15" t="n">
@@ -9751,12 +9989,12 @@
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Yuni, Tingum</t>
+          <t>Urom, Mzoughi, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>Book chapter</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="G93" s="15" t="inlineStr">
@@ -9771,12 +10009,12 @@
       </c>
       <c r="I93" s="17" t="inlineStr">
         <is>
-          <t>https://www.springerprofessional.de/en/economic-sentiment-and-climate-transition-during-the-covid-19-pa/20350390</t>
+          <t>https://merit.unu.edu/publications/working-papers/abstract/?id=9378</t>
         </is>
       </c>
       <c r="J93" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/economic-sentiment-and-climate-transition-during-covid-19</t>
+          <t>https://rita-woad.vercel.app/research/publications/clean-investments-and-economic-policy-uncertainty</t>
         </is>
       </c>
       <c r="K93" s="16" t="inlineStr"/>
@@ -9788,7 +10026,7 @@
       <c r="M93" s="16" t="inlineStr"/>
       <c r="N93" s="16" t="inlineStr">
         <is>
-          <t>The chapter examines how a newspaper-based US economic sentiment index relates to four climate-themed financial indices after COVID-19 began. Dependence varies across time horizons and market conditions.</t>
+          <t>The paper examines how clean investments across sectors respond to economic policy uncertainty, using the NASDAQ OMX Green Economy sectoral indexes. Dependence and predictability vary across market conditions and horizons, so the diversification benefits of clean energy stocks depend on sector, market conditions and horizon.</t>
         </is>
       </c>
       <c r="O93" s="16" t="inlineStr"/>
@@ -9810,12 +10048,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>How do financial and commodity markets volatility react to real economic activity?</t>
+          <t>Economic sentiment and climate transition during the COVID-19 pandemic</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Finance Research Letters 47(B), 102733</t>
+          <t>In Goutte, Guesmi and Urom (eds), Financial Market Dynamics after COVID 19, Springer, ch. 8</t>
         </is>
       </c>
       <c r="D94" s="15" t="n">
@@ -9823,12 +10061,12 @@
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Urom, Ndubuisi, Guesmi</t>
+          <t>Ndubuisi, Yuni, Tingum</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>Journal article</t>
+          <t>Book chapter</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
@@ -9843,12 +10081,12 @@
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
-          <t>https://ideas.repec.org/a/eee/finlet/v47y2022ipbs1544612322000563.html</t>
+          <t>https://www.springerprofessional.de/en/economic-sentiment-and-climate-transition-during-the-covid-19-pa/20350390</t>
         </is>
       </c>
       <c r="J94" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/financial-and-commodity-market-volatility-and-real-activity</t>
+          <t>https://rita-woad.vercel.app/research/publications/economic-sentiment-and-climate-transition-during-covid-19</t>
         </is>
       </c>
       <c r="K94" s="16" t="inlineStr"/>
@@ -9860,7 +10098,7 @@
       <c r="M94" s="16" t="inlineStr"/>
       <c r="N94" s="16" t="inlineStr">
         <is>
-          <t>The paper tests lead-lag links and integration between real economic activity and financial and commodity market volatility. Real activity shocks co-move with these markets, but the markets led that co-movement during downturns such as the COVID-19 pandemic.</t>
+          <t>The chapter examines how a newspaper-based US economic sentiment index relates to four climate-themed financial indices after COVID-19 began. Dependence varies across time horizons and market conditions.</t>
         </is>
       </c>
       <c r="O94" s="16" t="inlineStr"/>
@@ -9882,12 +10120,12 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Quantile co-movement and dependence between energy-focused sectors and artificial intelligence</t>
+          <t>How do financial and commodity markets volatility react to real economic activity?</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Technological Forecasting and Social Change 183, 121842</t>
+          <t>Finance Research Letters 47(B), 102733</t>
         </is>
       </c>
       <c r="D95" s="15" t="n">
@@ -9895,7 +10133,7 @@
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>Urom, Ndubuisi, Guesmi, Benkraien</t>
+          <t>Urom, Ndubuisi, Guesmi</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
@@ -9915,12 +10153,12 @@
       </c>
       <c r="I95" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.techfore.2022.121842</t>
+          <t>https://ideas.repec.org/a/eee/finlet/v47y2022ipbs1544612322000563.html</t>
         </is>
       </c>
       <c r="J95" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/energy-focused-sectors-and-artificial-intelligence</t>
+          <t>https://rita-woad.vercel.app/research/publications/financial-and-commodity-market-volatility-and-real-activity</t>
         </is>
       </c>
       <c r="K95" s="16" t="inlineStr"/>
@@ -9932,7 +10170,7 @@
       <c r="M95" s="16" t="inlineStr"/>
       <c r="N95" s="16" t="inlineStr">
         <is>
-          <t>The paper studies links between artificial intelligence and eight energy-focused sectors. The performance of energy-focused corporations, especially in renewable energy, depends strongly on the performance of AI.</t>
+          <t>The paper tests lead-lag links and integration between real economic activity and financial and commodity market volatility. Real activity shocks co-move with these markets, but the markets led that co-movement during downturns such as the COVID-19 pandemic.</t>
         </is>
       </c>
       <c r="O95" s="16" t="inlineStr"/>
@@ -9954,20 +10192,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Economic activity, and financial and commodity markets’ shocks: an analysis of implied volatility indexes</t>
+          <t>Quantile co-movement and dependence between energy-focused sectors and artificial intelligence</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>International Economics 165, 51–66</t>
+          <t>Technological Forecasting and Social Change 183, 121842</t>
         </is>
       </c>
       <c r="D96" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Urom, Ndubuisi, Ozor</t>
+          <t>Urom, Ndubuisi, Guesmi, Benkraien</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -9987,12 +10225,12 @@
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
-          <t>https://ideas.repec.org/a/eee/inteco/v165y2021icp51-66.html</t>
+          <t>https://doi.org/10.1016/j.techfore.2022.121842</t>
         </is>
       </c>
       <c r="J96" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/implied-volatility-indexes</t>
+          <t>https://rita-woad.vercel.app/research/publications/energy-focused-sectors-and-artificial-intelligence</t>
         </is>
       </c>
       <c r="K96" s="16" t="inlineStr"/>
@@ -10004,7 +10242,7 @@
       <c r="M96" s="16" t="inlineStr"/>
       <c r="N96" s="16" t="inlineStr">
         <is>
-          <t>The paper examines short- and long-run asymmetric interactions and causality between real economic activity and volatility shocks in stock, energy and gold markets. The relationships are asymmetric at both horizons.</t>
+          <t>The paper studies links between artificial intelligence and eight energy-focused sectors. The performance of energy-focused corporations, especially in renewable energy, depends strongly on the performance of AI.</t>
         </is>
       </c>
       <c r="O96" s="16" t="inlineStr"/>
@@ -10026,12 +10264,12 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Global, regional, and national mortality among young people aged 10–24 years, 1950–2019: a systematic analysis for the Global Burden of Disease Study 2019</t>
+          <t>Economic activity, and financial and commodity markets’ shocks: an analysis of implied volatility indexes</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>The Lancet 398(10311), 1593–1618</t>
+          <t>International Economics 165, 51–66</t>
         </is>
       </c>
       <c r="D97" s="15" t="n">
@@ -10039,7 +10277,7 @@
       </c>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>GBD 2019 Adolescent Mortality Collaborators</t>
+          <t>Urom, Ndubuisi, Ozor</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
@@ -10049,22 +10287,22 @@
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
+          <t>01 Green industrialisation &amp; policy</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
           <t>Archive</t>
         </is>
       </c>
-      <c r="H97" s="15" t="inlineStr">
-        <is>
-          <t>Archive</t>
-        </is>
-      </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/S0140-6736(21)01546-4</t>
+          <t>https://ideas.repec.org/a/eee/inteco/v165y2021icp51-66.html</t>
         </is>
       </c>
       <c r="J97" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/global-regional-and-national-mortality-among-young-people-aged-10-24</t>
+          <t>https://rita-woad.vercel.app/research/publications/implied-volatility-indexes</t>
         </is>
       </c>
       <c r="K97" s="16" t="inlineStr"/>
@@ -10076,7 +10314,7 @@
       <c r="M97" s="16" t="inlineStr"/>
       <c r="N97" s="16" t="inlineStr">
         <is>
-          <t>Using GBD 2019 estimates, the study examines deaths and mortality rates among 10–24-year-olds in 204 countries and territories from 1950 to 2019. Variation in adolescent mortality between countries and by sex is widening.</t>
+          <t>The paper examines short- and long-run asymmetric interactions and causality between real economic activity and volatility shocks in stock, energy and gold markets. The relationships are asymmetric at both horizons.</t>
         </is>
       </c>
       <c r="O97" s="16" t="inlineStr"/>
@@ -10098,27 +10336,25 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>The past and the present: the Nigerian Ebola experience and the Covid-19 pandemic</t>
+          <t>Global, regional, and national mortality among young people aged 10–24 years, 1950–2019: a systematic analysis for the Global Burden of Disease Study 2019</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>INCLUDE Platform</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>The Lancet 398(10311), 1593–1618</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="n">
+        <v>2021</v>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Konte, Ndubuisi, Okafor</t>
+          <t>GBD 2019 Adolescent Mortality Collaborators</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Journal article</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr">
@@ -10133,12 +10369,12 @@
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
-          <t>https://includeplatform.net/publications/the-past-and-the-present-the-nigerian-ebola-experience-and-the-covid-19-pandemic-2/</t>
+          <t>https://doi.org/10.1016/S0140-6736(21)01546-4</t>
         </is>
       </c>
       <c r="J98" s="17" t="inlineStr">
         <is>
-          <t>https://rita-woad.vercel.app/research/publications/the-past-and-the-present-the-nigerian-ebola-experience-and-covid-19</t>
+          <t>https://rita-woad.vercel.app/research/publications/global-regional-and-national-mortality-among-young-people-aged-10-24</t>
         </is>
       </c>
       <c r="K98" s="16" t="inlineStr"/>
@@ -10150,7 +10386,7 @@
       <c r="M98" s="16" t="inlineStr"/>
       <c r="N98" s="16" t="inlineStr">
         <is>
-          <t>The paper compares Nigeria's success against Ebola with its country-wide response to COVID-19, and assesses which factors may have prevented the country from repeating that success.</t>
+          <t>Using GBD 2019 estimates, the study examines deaths and mortality rates among 10–24-year-olds in 204 countries and territories from 1950 to 2019. Variation in adolescent mortality between countries and by sex is widening.</t>
         </is>
       </c>
       <c r="O98" s="16" t="inlineStr"/>
@@ -10161,21 +10397,95 @@
       <c r="T98" s="16" t="inlineStr"/>
       <c r="U98" s="16" t="inlineStr">
         <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="V98" s="16" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>The past and the present: the Nigerian Ebola experience and the Covid-19 pandemic</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>INCLUDE Platform</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>Konte, Ndubuisi, Okafor</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>https://includeplatform.net/publications/the-past-and-the-present-the-nigerian-ebola-experience-and-the-covid-19-pandemic-2/</t>
+        </is>
+      </c>
+      <c r="J99" s="17" t="inlineStr">
+        <is>
+          <t>https://rita-woad.vercel.app/research/publications/the-past-and-the-present-the-nigerian-ebola-experience-and-covid-19</t>
+        </is>
+      </c>
+      <c r="K99" s="16" t="inlineStr"/>
+      <c r="L99" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M99" s="16" t="inlineStr"/>
+      <c r="N99" s="16" t="inlineStr">
+        <is>
+          <t>The paper compares Nigeria's success against Ebola with its country-wide response to COVID-19, and assesses which factors may have prevented the country from repeating that success.</t>
+        </is>
+      </c>
+      <c r="O99" s="16" t="inlineStr"/>
+      <c r="P99" s="16" t="inlineStr"/>
+      <c r="Q99" s="16" t="inlineStr"/>
+      <c r="R99" s="16" t="inlineStr"/>
+      <c r="S99" s="16" t="inlineStr"/>
+      <c r="T99" s="16" t="inlineStr"/>
+      <c r="U99" s="16" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="V98" s="16" t="inlineStr"/>
+      <c r="V99" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V98"/>
+  <autoFilter ref="A2:V99"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L4:L98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L4:L99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,Not sure"</formula1>
     </dataValidation>
-    <dataValidation sqref="T4:T98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T4:T99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,Not sure"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10332,42 +10642,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12179,7 +12490,7 @@
       <c r="I4" s="16" t="inlineStr"/>
       <c r="J4" s="16" t="inlineStr">
         <is>
-          <t>Outages cut jobs, investment and exports; restoring power doesn't restore capabilities, so treat electricity as productive infrastructure.</t>
+          <t>Load shedding has ended, but the damage to manufacturing has not. Drawing on two studies in Energy Policy and Energy Economics, the authors show that outages cut jobs, postponed investment and cost export opportunities, and argue that restoring power does not restore lost capabilities.</t>
         </is>
       </c>
       <c r="K4" s="16" t="inlineStr"/>
@@ -12187,7 +12498,7 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Africa’s mineral strength is wasted if countries don’t work together</t>
+          <t>Africa’s mineral strength is wasted if countries don’t work together – new report</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -12220,7 +12531,7 @@
       <c r="I5" s="16" t="inlineStr"/>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>No single country has every input; regional coordination turns geology into value chains.</t>
+          <t>Transition minerals are found in 48 African countries, but most still export them raw and capture little value. Drawing on a World Bank–commissioned study, the authors argue that only regional cooperation, shared infrastructure and coordinated policy can turn mineral wealth into regional value chains.</t>
         </is>
       </c>
       <c r="K5" s="16" t="inlineStr"/>
@@ -12257,11 +12568,15 @@
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr"/>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>Please confirm</t>
+        </is>
+      </c>
       <c r="I6" s="16" t="inlineStr"/>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>GVCs create and destroy jobs; gains go to new, small, young firms.</t>
+          <t>Global value chains both create and destroy jobs in South Africa. Net gains come from new, small and young firms entering GVCs, while long-standing participants shed jobs.</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr"/>
@@ -12302,7 +12617,7 @@
       <c r="I7" s="16" t="inlineStr"/>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>Aligned strategies aren't enough; build system coherence around productive bottlenecks.</t>
+          <t>South Africa has one of Africa’s most sophisticated industrial policy architectures, yet transformation remains elusive. Aligned strategies and institutions are not enough: coherence must be built around the productive bottlenecks that hold firms back.</t>
         </is>
       </c>
       <c r="K7" s="16" t="inlineStr"/>
@@ -12339,11 +12654,15 @@
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>Please confirm</t>
+        </is>
+      </c>
       <c r="I8" s="16" t="inlineStr"/>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>What matters is technological fit with local capabilities, not where imports come from.</t>
+          <t>Drawing on their study of 52 African countries (2000–2022), the authors argue that what drives structural change is not whether imported inputs come from the North or the South, but how well they fit local capabilities.</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr"/>
@@ -12384,7 +12703,7 @@
       <c r="I9" s="16" t="inlineStr"/>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>Energy reform must become productive reconstruction.</t>
+          <t>Years of power cuts left productive scars: lost manufacturing capacity, investment, export capability and learning that persist after supply improves. A green transition that ignores them may deliver cleaner electricity while reproducing industrial weakness.</t>
         </is>
       </c>
       <c r="K9" s="16" t="inlineStr"/>
@@ -12392,12 +12711,12 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>More about the melody, less about the volume: financing industrial transformation</t>
+          <t>More melody, less volume: financing industrial transformation across Africa</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>OPEC Fund Quarterly</t>
+          <t>OPEC Fund Quarterly, 2026 Q2</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -12425,7 +12744,7 @@
       <c r="I10" s="16" t="inlineStr"/>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>The structure of finance matters: temporal, currency and structural alignment.</t>
+          <t>The debate on financing Africa’s green industrial shift focuses too much on the size of the funding gap. The authors argue the deeper constraint is the structure, quality and purpose of finance, and how well it is aligned with industrial development.</t>
         </is>
       </c>
       <c r="K10" s="16" t="inlineStr"/>
@@ -12438,7 +12757,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Growth Research Platform (STEG)</t>
+          <t>STEG Policy Brief, Growth Research Platform (CEPR)</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -12466,7 +12785,7 @@
       <c r="I11" s="16" t="inlineStr"/>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>Net job gains overall; continuous participants shed jobs.</t>
+          <t>Using data on the universe of formal manufacturing firms in South Africa, the brief finds that joining global value chains brings a net job gain. The gain is driven by firms entering GVCs, largely younger and smaller ones; firms that stay in GVCs shed jobs overall.</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr"/>
@@ -12503,11 +12822,15 @@
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr"/>
-      <c r="H12" s="16" t="inlineStr"/>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>Please confirm</t>
+        </is>
+      </c>
       <c r="I12" s="16" t="inlineStr"/>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>Enter feasible segments (design, ATP, power electronics) collectively via AfCFTA.</t>
+          <t>Africa cannot power its green and digital future without a place in the semiconductor value chain. The brief argues for entering feasible segments, such as chip design, assembly, testing and packaging, and power electronics, collectively through the AfCFTA.</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr"/>
@@ -12520,7 +12843,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>UNIDO Policy Brief</t>
+          <t>UNIDO IID Policy Brief 20</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -12535,18 +12858,26 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Asiama, Avenyo, Habiyaremye, Ncube, Tregenna, Donnelly, Lavopa</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>https://lnkd.in/dn7BiAnG</t>
+          <t>https://www.unido.org/publications/policy-briefs</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr"/>
-      <c r="H13" s="16" t="inlineStr"/>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>Please confirm</t>
+        </is>
+      </c>
       <c r="I13" s="16" t="inlineStr"/>
-      <c r="J13" s="16" t="inlineStr"/>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>Linked to the Africa launch of UNIDO’s Industrial Development Report 2024, the brief assesses Africa’s progress on the industry-related SDGs and argues that industrial policy aligned with the SDGs can drive innovation, decent jobs and climate mitigation.</t>
+        </is>
+      </c>
       <c r="K13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
@@ -12572,7 +12903,7 @@
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Ndubuisi, Tang, Owusu</t>
+          <t>Owusu, Tang, Ndubuisi</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -12585,7 +12916,7 @@
       <c r="I14" s="16" t="inlineStr"/>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>Chinese FDI raises emissions in resource-intensive sectors; reshape it, don't discourage it.</t>
+          <t>Chinese greenfield manufacturing investment raised industrial carbon emissions in Africa, especially when it went into labour- and resource-intensive manufacturing; the same effect does not appear for OECD investment. The authors argue for reshaping Chinese FDI, not discouraging it.</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr"/>
@@ -12598,7 +12929,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>SARChI Industrial Development Policy Brief</t>
+          <t>SARChI Industrial Development Policy Brief 2024-03</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -12626,7 +12957,7 @@
       <c r="I15" s="16" t="inlineStr"/>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Capabilities spill over borders through intra-African trade.</t>
+          <t>Little is known about how technological capability shapes industrialisation in Africa. The brief measures capability along four dimensions (preconditions, infrastructure, technology imports and technological effort) and shows that capabilities spill over borders through intra-African trade.</t>
         </is>
       </c>
       <c r="K15" s="16" t="inlineStr"/>
@@ -12634,12 +12965,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Catastrophic effects of COVID-19 health expenditure shocks and poverty in Ghana</t>
+          <t>Catastrophic effects of COVID-19 health expenditure shocks and multidimensional poverty in Ghana: what financing mechanisms mattered?</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>AERC Policy Brief</t>
+          <t>AERC Policy Brief AHCV-PB-007</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -12654,7 +12985,7 @@
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Ayanore, Avenyo, Osei</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -12665,18 +12996,22 @@
       <c r="G16" s="16" t="inlineStr"/>
       <c r="H16" s="16" t="inlineStr"/>
       <c r="I16" s="16" t="inlineStr"/>
-      <c r="J16" s="16" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>More than half of Ghanaian households in the sample spent over 5% of their total expenditure on COVID-19-related health costs. Multidimensional poverty made these catastrophic payments worse, while insurance, remittances and government assistance softened the shock.</t>
+        </is>
+      </c>
       <c r="K16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Climate change mitigation for late industrialisers: technology intensity in manufacturing</t>
+          <t>Financing digital industrialisation in South Africa: emerging issues</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>CBDS, Copenhagen Business School</t>
+          <t>CCRED-IDTT Policy Brief 2023/5</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -12686,34 +13021,38 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Nyamwena, Avenyo</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>https://research.cbs.dk/files/89602649/elvis_korku_avenyo_et_al_climate_change_mitigation_for_late_industrialisers_publishersversion.pdf</t>
+          <t>https://www.competition.org.za/s/IDTT-2022-2023-PB5_Finance-and-digitalisation.pdf</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr"/>
       <c r="H17" s="16" t="inlineStr"/>
       <c r="I17" s="16" t="inlineStr"/>
-      <c r="J17" s="16" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Survey evidence from South African manufacturers shows that finance matters for the adoption of digital technologies. The brief sets out the emerging issues in financing digital industrialisation.</t>
+        </is>
+      </c>
       <c r="K17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Financing digital industrialisation in South Africa: emerging issues</t>
+          <t>Localisation and industrialisation nexus: lessons for South Africa</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>CCRED-IDTT Policy Brief 2023/05</t>
+          <t>CCRED-IDTT Policy Brief 2023/1</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -12723,38 +13062,38 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Nyamwena, Avenyo, Bosiu</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>https://www.competition.org.za/s/IDTT-2022-2023-PB5_Finance-and-digitalisation.pdf</t>
+          <t>https://www.competition.org.za/s/IDTT-2022-2023-PB1_Localisation-and-Industrialisation-Nexus.pdf</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr"/>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>Please confirm</t>
-        </is>
-      </c>
+      <c r="H18" s="16" t="inlineStr"/>
       <c r="I18" s="16" t="inlineStr"/>
-      <c r="J18" s="16" t="inlineStr"/>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>A policy brief on how localisation policy connects to industrialisation, and what South Africa can learn from it.</t>
+        </is>
+      </c>
       <c r="K18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Localisation and industrialisation nexus: lessons for South Africa</t>
+          <t>Climate change mitigation for late industrialisers: technology intensity in manufacturing</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>CCRED-IDTT Policy Brief 2023/01</t>
+          <t>SARChI Industrial Development Policy Brief 2023-01 (with CBDS, Copenhagen Business School)</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -12764,27 +13103,27 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Avenyo, Tregenna</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>https://www.competition.org.za/s/IDTT-2022-2023-PB1_Localisation-and-Industrialisation-Nexus.pdf</t>
+          <t>https://www.uj.ac.za/wp-content/uploads/2021/10/sarchi-id-pb-2023-01-avenyo-e--tregenna-f--january-2023.pdf</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr"/>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>Please confirm</t>
-        </is>
-      </c>
+      <c r="H19" s="16" t="inlineStr"/>
       <c r="I19" s="16" t="inlineStr"/>
-      <c r="J19" s="16" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>Late industrialisers need manufacturing to grow, but heavy industrialisation can raise emissions. Drawing on evidence from 56 developing economies, the brief asks whether greener industrial policy, shifting towards higher-technology manufacturing, lets countries industrialise while limiting emissions.</t>
+        </is>
+      </c>
       <c r="K19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
@@ -12805,38 +13144,38 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>Chisoro-Dube, Avenyo</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>https://www.competition.org.za/s/IDTT5-PB9-Digital-Industrilisation-of-freshness_Final_06072022.pdf</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr"/>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>Please confirm</t>
-        </is>
-      </c>
+      <c r="H20" s="16" t="inlineStr"/>
       <c r="I20" s="16" t="inlineStr"/>
-      <c r="J20" s="16" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>A policy brief on how digital technologies are changing fresh-produce value chains in South Africa, part of the Industrial Development Think Tank’s series on climate change and green industrialisation.</t>
+        </is>
+      </c>
       <c r="K20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Digital technology adoption and performance in South African manufacturing: early evidence</t>
+          <t>Implications of COVID-19 on digital transformation in South Africa</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>AERC Policy Brief 2022/004</t>
+          <t>CCRED-IDTT Policy Brief 2022/08</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -12846,38 +13185,38 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Avenyo, Bell, Nyamwena</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>http://publication.aercafricalibrary.org/handle/123456789/3404</t>
+          <t>https://www.competition.org.za/s/IDTT5-PB8-Implications-of-COVID-19-on-digital-transformation-in-South-Africa.pdf</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr"/>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>Please confirm</t>
-        </is>
-      </c>
+      <c r="H21" s="16" t="inlineStr"/>
       <c r="I21" s="16" t="inlineStr"/>
-      <c r="J21" s="16" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>Drawing on a survey of 516 South African manufacturing firms, the brief shows how COVID-19 interacted with the shift to digital technologies. Uneven digital uptake weakens the resilience of the firms and industries most exposed to shocks.</t>
+        </is>
+      </c>
       <c r="K21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Implications of COVID-19 on digital transformation in South Africa</t>
+          <t>Digital technology adoption and performance in South African manufacturing firms: early evidence for policy</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>CCRED-IDTT Policy Brief 2022/07</t>
+          <t>AERC Policy Brief</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -12887,27 +13226,27 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>Avenyo, Bell</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>https://publication.aercafricalibrary.org/handle/123456789/3404</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr"/>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>Please confirm</t>
-        </is>
-      </c>
+      <c r="H22" s="16" t="inlineStr"/>
       <c r="I22" s="16" t="inlineStr"/>
-      <c r="J22" s="16" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>South Africa is a technological follower, and the recovery of its manufacturing may depend on faster digital adoption. The brief shows that the effects of new technologies differ across firms and industries, so digital industrial policy must weigh firm-level factors.</t>
+        </is>
+      </c>
       <c r="K22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
@@ -12944,13 +13283,17 @@
       <c r="G23" s="16" t="inlineStr"/>
       <c r="H23" s="16" t="inlineStr"/>
       <c r="I23" s="16" t="inlineStr"/>
-      <c r="J23" s="16" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>A survey of 516 South African firms shows the uptake of digital technologies has been slow and uneven. Premature deindustrialisation has left a small, undiversified production base, which makes it harder to meet the basics: connectivity, energy and digital skills.</t>
+        </is>
+      </c>
       <c r="K23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Informal workers in Senegal, Mali and Burkina Faso hit harder by COVID-19</t>
+          <t>Informal workers in Senegal, Mali and Burkina Faso have been hit harder by COVID-19</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -12970,7 +13313,7 @@
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
+          <t>Balde, Boly, Avenyo</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -12981,7 +13324,11 @@
       <c r="G24" s="16" t="inlineStr"/>
       <c r="H24" s="16" t="inlineStr"/>
       <c r="I24" s="16" t="inlineStr"/>
-      <c r="J24" s="16" t="inlineStr"/>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>A survey of 900 people in Senegal, Mali and Burkina Faso in spring 2020 found that informal workers were more likely to lose their jobs, see their earnings fall and struggle to meet basic needs. The authors set out what this means for social protection and support for small businesses.</t>
+        </is>
+      </c>
       <c r="K24" s="16" t="inlineStr"/>
     </row>
     <row r="25">
@@ -13007,18 +13354,22 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Avenyo</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>Avenyo, Bell, Nyamwena, Robb</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>https://www.competition.org.za/s/IDTT4_PB_Awakening_industrial_economic_recovery_in_South_Africa_202107.pdf</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr"/>
       <c r="H25" s="16" t="inlineStr"/>
       <c r="I25" s="16" t="inlineStr"/>
-      <c r="J25" s="16" t="inlineStr"/>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>A policy brief from the Industrial Development Think Tank on reviving South Africa’s industrial economy after the COVID-19 shock.</t>
+        </is>
+      </c>
       <c r="K25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
@@ -13053,9 +13404,17 @@
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr"/>
-      <c r="H26" s="16" t="inlineStr"/>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>Please confirm</t>
+        </is>
+      </c>
       <c r="I26" s="16" t="inlineStr"/>
-      <c r="J26" s="16" t="inlineStr"/>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>For a middle-income technological follower like South Africa, the challenge is to modernise existing capabilities and infrastructure. The Industrial Development Think Tank argues that building digital skills in manufacturing is central to that.</t>
+        </is>
+      </c>
       <c r="K26" s="16" t="inlineStr"/>
     </row>
   </sheetData>
@@ -13085,10 +13444,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13267,7 +13629,7 @@
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>Regionalizing green transition minerals for structural transformation in Africa | Africa’s mineral strength is wasted if countries don’t work together</t>
+          <t>Regionalizing green transition minerals for structural transformation in Africa | Africa’s mineral strength is wasted if countries don’t work together – new report</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr"/>
@@ -13677,7 +14039,11 @@
       </c>
       <c r="H5" s="16" t="inlineStr"/>
       <c r="I5" s="16" t="inlineStr"/>
-      <c r="J5" s="16" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>African Economic Research Consortium (AERC)</t>
+        </is>
+      </c>
       <c r="K5" s="16" t="inlineStr"/>
       <c r="L5" s="16" t="inlineStr"/>
       <c r="M5" s="16" t="inlineStr"/>
@@ -13723,7 +14089,7 @@
       <c r="I6" s="16" t="inlineStr"/>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>Wits School of Geosciences, Wits Mining Institute, SCIS, SARChI Industrial Development</t>
+          <t>Southern Centre for Inequality Studies (SCIS), Wits, Wits School of Geosciences, Wits Mining Institute, SARChI Industrial Development, University of Johannesburg</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr"/>
@@ -13749,7 +14115,7 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -13768,8 +14134,14 @@
         </is>
       </c>
       <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-      <c r="J7" s="16" t="inlineStr"/>
+      <c r="I7" s="16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>African Economic Research Consortium (AERC)</t>
+        </is>
+      </c>
       <c r="K7" s="16" t="inlineStr"/>
       <c r="L7" s="16" t="inlineStr"/>
       <c r="M7" s="16" t="inlineStr"/>
@@ -13793,7 +14165,7 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -13812,8 +14184,14 @@
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr"/>
+      <c r="I8" s="16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>UNU-WIDER, SA-TIED</t>
+        </is>
+      </c>
       <c r="K8" s="16" t="inlineStr"/>
       <c r="L8" s="16" t="inlineStr"/>
       <c r="M8" s="16" t="inlineStr"/>
@@ -13837,7 +14215,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -13856,8 +14234,14 @@
         </is>
       </c>
       <c r="H9" s="16" t="inlineStr"/>
-      <c r="I9" s="16" t="inlineStr"/>
-      <c r="J9" s="16" t="inlineStr"/>
+      <c r="I9" s="16" t="n">
+        <v>2020</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>UNU-WIDER, SA-TIED, National Treasury, South African Revenue Service</t>
+        </is>
+      </c>
       <c r="K9" s="16" t="inlineStr"/>
       <c r="L9" s="16" t="inlineStr"/>
       <c r="M9" s="16" t="inlineStr"/>
@@ -13881,7 +14265,7 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -13900,8 +14284,14 @@
         </is>
       </c>
       <c r="H10" s="16" t="inlineStr"/>
-      <c r="I10" s="16" t="inlineStr"/>
-      <c r="J10" s="16" t="inlineStr"/>
+      <c r="I10" s="16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>African Economic Research Consortium (AERC)</t>
+        </is>
+      </c>
       <c r="K10" s="16" t="inlineStr"/>
       <c r="L10" s="16" t="inlineStr"/>
       <c r="M10" s="16" t="inlineStr"/>
@@ -13947,7 +14337,11 @@
       <c r="I11" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="J11" s="16" t="inlineStr"/>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>UNIDO</t>
+        </is>
+      </c>
       <c r="K11" s="16" t="inlineStr"/>
       <c r="L11" s="16" t="inlineStr"/>
       <c r="M11" s="16" t="inlineStr"/>
@@ -13993,7 +14387,11 @@
       <c r="I12" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="J12" s="16" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>World Bank, Office of the Chief Economist for the Africa Region</t>
+        </is>
+      </c>
       <c r="K12" s="16" t="inlineStr"/>
       <c r="L12" s="16" t="inlineStr"/>
       <c r="M12" s="16" t="inlineStr"/>
@@ -14017,7 +14415,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2020–2025</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -14035,9 +14433,17 @@
           <t>https://rita-woad.vercel.app/research/projects/research-network-sustainable-supply-chains</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr"/>
-      <c r="I13" s="16" t="inlineStr"/>
-      <c r="J13" s="16" t="inlineStr"/>
+      <c r="H13" s="16" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>German Development Institute (DIE/IDOS), German Institute for International and Security Affairs (SWP), GIGA, Kiel Institute for the World Economy (IfW)</t>
+        </is>
+      </c>
       <c r="K13" s="16" t="inlineStr"/>
       <c r="L13" s="16" t="inlineStr"/>
       <c r="M13" s="16" t="inlineStr"/>
@@ -14083,7 +14489,11 @@
       <c r="I14" s="16" t="n">
         <v>2023</v>
       </c>
-      <c r="J14" s="16" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>UNCTAD</t>
+        </is>
+      </c>
       <c r="K14" s="16" t="inlineStr"/>
       <c r="L14" s="16" t="inlineStr"/>
       <c r="M14" s="16" t="inlineStr"/>
@@ -14127,13 +14537,13 @@
       </c>
       <c r="H15" s="16" t="inlineStr"/>
       <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>Department of Science and Innovation, South Africa</t>
+        </is>
+      </c>
       <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>Co-PI</t>
-        </is>
-      </c>
+      <c r="L15" s="16" t="inlineStr"/>
       <c r="M15" s="16" t="inlineStr"/>
       <c r="N15" s="16" t="inlineStr"/>
     </row>
@@ -14155,7 +14565,7 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -14173,9 +14583,17 @@
           <t>https://rita-woad.vercel.app/research/projects/services-sector-acceleration</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr"/>
-      <c r="I16" s="16" t="inlineStr"/>
-      <c r="J16" s="16" t="inlineStr"/>
+      <c r="H16" s="16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>UNU-WIDER, Groningen Growth and Development Centre (GGDC)</t>
+        </is>
+      </c>
       <c r="K16" s="16" t="inlineStr"/>
       <c r="L16" s="16" t="inlineStr"/>
       <c r="M16" s="16" t="inlineStr"/>
@@ -14199,7 +14617,7 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -14218,8 +14636,14 @@
         </is>
       </c>
       <c r="H17" s="16" t="inlineStr"/>
-      <c r="I17" s="16" t="inlineStr"/>
-      <c r="J17" s="16" t="inlineStr"/>
+      <c r="I17" s="16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Africa Policy Research Institute (APRI)</t>
+        </is>
+      </c>
       <c r="K17" s="16" t="inlineStr"/>
       <c r="L17" s="16" t="inlineStr"/>
       <c r="M17" s="16" t="inlineStr"/>
@@ -14243,7 +14667,7 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
@@ -14262,8 +14686,14 @@
         </is>
       </c>
       <c r="H18" s="16" t="inlineStr"/>
-      <c r="I18" s="16" t="inlineStr"/>
-      <c r="J18" s="16" t="inlineStr"/>
+      <c r="I18" s="16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>African Center for Economic Transformation (ACET)</t>
+        </is>
+      </c>
       <c r="K18" s="16" t="inlineStr"/>
       <c r="L18" s="16" t="inlineStr"/>
       <c r="M18" s="16" t="inlineStr"/>
